--- a/V2.0/settings/data_main.xlsx
+++ b/V2.0/settings/data_main.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iagr9\Projekte\MA\MA-Model_2\V2.0\settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAEEBFD-E9F5-48C2-B49C-B5029827188B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3613FEDA-F94C-43F5-900B-C3297FFE8110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="sozh" sheetId="2" r:id="rId2"/>
+    <sheet name="detail_V_dis" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="21">
   <si>
     <t>exp</t>
   </si>
@@ -106,7 +107,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +129,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -143,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -151,15 +160,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -11842,4 +11867,2744 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAD5510-D8B4-41CB-8DB7-8774A6DA7713}">
+  <dimension ref="A1:H105"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>2.0462099999999999E-4</v>
+      </c>
+      <c r="C2">
+        <v>743.10170100000005</v>
+      </c>
+      <c r="D2">
+        <v>0.29701893400000001</v>
+      </c>
+      <c r="E2">
+        <v>3.6502927999999997E-2</v>
+      </c>
+      <c r="F2">
+        <v>9.6633421999999997E-2</v>
+      </c>
+      <c r="G2">
+        <v>4.4652340000000002E-3</v>
+      </c>
+      <c r="H2">
+        <v>0.98750888400000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>6.5725699999999996E-4</v>
+      </c>
+      <c r="C3">
+        <v>748.36788460000002</v>
+      </c>
+      <c r="D3">
+        <v>0.50333939500000002</v>
+      </c>
+      <c r="E3">
+        <v>2.8484735000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>9.2660582000000005E-2</v>
+      </c>
+      <c r="G3">
+        <v>1.528742E-3</v>
+      </c>
+      <c r="H3">
+        <v>0.99108918400000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>3.1127999999999999E-4</v>
+      </c>
+      <c r="C4">
+        <v>749.92972780000002</v>
+      </c>
+      <c r="D4">
+        <v>0.49988101000000001</v>
+      </c>
+      <c r="E4">
+        <v>3.8919571E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.10772396300000001</v>
+      </c>
+      <c r="G4">
+        <v>4.7552549999999999E-3</v>
+      </c>
+      <c r="H4">
+        <v>0.99268671900000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>4.4927699999999999E-4</v>
+      </c>
+      <c r="C5">
+        <v>749.97402599999998</v>
+      </c>
+      <c r="D5">
+        <v>0.399764919</v>
+      </c>
+      <c r="E5">
+        <v>3.8463404E-2</v>
+      </c>
+      <c r="F5">
+        <v>9.5001253999999993E-2</v>
+      </c>
+      <c r="G5">
+        <v>3.785549E-3</v>
+      </c>
+      <c r="H5">
+        <v>0.98653263199999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>5.4967899999999997E-4</v>
+      </c>
+      <c r="C6">
+        <v>750.02556879999997</v>
+      </c>
+      <c r="D6">
+        <v>0.50015754999999995</v>
+      </c>
+      <c r="E6">
+        <v>4.0361706999999997E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.101830843</v>
+      </c>
+      <c r="G6">
+        <v>5.2321299999999998E-3</v>
+      </c>
+      <c r="H6">
+        <v>0.99445781600000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>3.38769E-4</v>
+      </c>
+      <c r="C7">
+        <v>750.05733190000001</v>
+      </c>
+      <c r="D7">
+        <v>0.49989457599999998</v>
+      </c>
+      <c r="E7">
+        <v>3.8023349999999997E-2</v>
+      </c>
+      <c r="F7">
+        <v>0.108397884</v>
+      </c>
+      <c r="G7">
+        <v>4.1389720000000003E-3</v>
+      </c>
+      <c r="H7">
+        <v>0.99176721899999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>2.4194099999999999E-4</v>
+      </c>
+      <c r="C8">
+        <v>750.20782199999996</v>
+      </c>
+      <c r="D8">
+        <v>0.40002338700000001</v>
+      </c>
+      <c r="E8">
+        <v>6.6916982E-2</v>
+      </c>
+      <c r="F8">
+        <v>0.106790285</v>
+      </c>
+      <c r="G8">
+        <v>5.2340670000000002E-3</v>
+      </c>
+      <c r="H8">
+        <v>0.99171526700000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>4.9274500000000005E-4</v>
+      </c>
+      <c r="C9">
+        <v>750.25178530000005</v>
+      </c>
+      <c r="D9">
+        <v>0.29988877800000002</v>
+      </c>
+      <c r="E9">
+        <v>3.6448479999999998E-2</v>
+      </c>
+      <c r="F9">
+        <v>0.10019613600000001</v>
+      </c>
+      <c r="G9">
+        <v>2.8000159999999998E-3</v>
+      </c>
+      <c r="H9">
+        <v>0.98938694400000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>6.1183099999999996E-4</v>
+      </c>
+      <c r="C10">
+        <v>750.71744000000001</v>
+      </c>
+      <c r="D10">
+        <v>0.50033280999999996</v>
+      </c>
+      <c r="E10">
+        <v>3.7521118999999999E-2</v>
+      </c>
+      <c r="F10">
+        <v>9.8495864000000002E-2</v>
+      </c>
+      <c r="G10">
+        <v>3.1483090000000002E-3</v>
+      </c>
+      <c r="H10">
+        <v>0.99218971899999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>3.9097999999999997E-4</v>
+      </c>
+      <c r="C11">
+        <v>750.86723619999998</v>
+      </c>
+      <c r="D11">
+        <v>0.30092750000000001</v>
+      </c>
+      <c r="E11">
+        <v>3.3229887E-2</v>
+      </c>
+      <c r="F11">
+        <v>0.100884113</v>
+      </c>
+      <c r="G11">
+        <v>3.2887580000000001E-3</v>
+      </c>
+      <c r="H11">
+        <v>0.99199386300000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>2.2167000000000001E-4</v>
+      </c>
+      <c r="C12">
+        <v>751.48936860000003</v>
+      </c>
+      <c r="D12">
+        <v>0.40003253100000002</v>
+      </c>
+      <c r="E12">
+        <v>7.0955006000000001E-2</v>
+      </c>
+      <c r="F12">
+        <v>0.11041532699999999</v>
+      </c>
+      <c r="G12">
+        <v>4.5576050000000002E-3</v>
+      </c>
+      <c r="H12">
+        <v>0.99505433700000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>6.7796600000000001E-4</v>
+      </c>
+      <c r="C13">
+        <v>752.85933369999998</v>
+      </c>
+      <c r="D13">
+        <v>0.49949943499999999</v>
+      </c>
+      <c r="E13">
+        <v>4.2382797999999999E-2</v>
+      </c>
+      <c r="F13">
+        <v>9.7580385000000006E-2</v>
+      </c>
+      <c r="G13">
+        <v>3.6210349999999999E-3</v>
+      </c>
+      <c r="H13">
+        <v>0.99436792399999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>2.54348E-4</v>
+      </c>
+      <c r="C14">
+        <v>908.35374130000002</v>
+      </c>
+      <c r="D14">
+        <v>0.27718706700000001</v>
+      </c>
+      <c r="E14">
+        <v>3.6368708E-2</v>
+      </c>
+      <c r="F14">
+        <v>0.103970942</v>
+      </c>
+      <c r="G14">
+        <v>3.6805710000000001E-3</v>
+      </c>
+      <c r="H14">
+        <v>0.99263151500000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>8.0239500000000002E-4</v>
+      </c>
+      <c r="C15">
+        <v>998.44373169999994</v>
+      </c>
+      <c r="D15">
+        <v>0.499859416</v>
+      </c>
+      <c r="E15">
+        <v>1.8851822000000001E-2</v>
+      </c>
+      <c r="F15">
+        <v>0.10280117799999999</v>
+      </c>
+      <c r="G15">
+        <v>3.8602500000000002E-4</v>
+      </c>
+      <c r="H15">
+        <v>0.99546705300000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>5.0275999999999999E-4</v>
+      </c>
+      <c r="C16">
+        <v>999.40820970000004</v>
+      </c>
+      <c r="D16">
+        <v>0.29920427599999999</v>
+      </c>
+      <c r="E16">
+        <v>4.1816536000000001E-2</v>
+      </c>
+      <c r="F16">
+        <v>0.101860464</v>
+      </c>
+      <c r="G16">
+        <v>4.1493759999999998E-3</v>
+      </c>
+      <c r="H16">
+        <v>0.98989876499999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>5.9944000000000002E-4</v>
+      </c>
+      <c r="C17">
+        <v>999.59662909999997</v>
+      </c>
+      <c r="D17">
+        <v>0.40006547100000001</v>
+      </c>
+      <c r="E17">
+        <v>2.4784075999999999E-2</v>
+      </c>
+      <c r="F17">
+        <v>9.7689174000000004E-2</v>
+      </c>
+      <c r="G17">
+        <v>4.8635799999999999E-4</v>
+      </c>
+      <c r="H17">
+        <v>0.99499302099999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>7.1244500000000003E-4</v>
+      </c>
+      <c r="C18">
+        <v>999.64467930000001</v>
+      </c>
+      <c r="D18">
+        <v>0.49991358299999999</v>
+      </c>
+      <c r="E18">
+        <v>1.8550810000000001E-2</v>
+      </c>
+      <c r="F18">
+        <v>9.4884389999999999E-2</v>
+      </c>
+      <c r="G18">
+        <v>2.2179650000000001E-3</v>
+      </c>
+      <c r="H18">
+        <v>0.99704778699999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>3.7785800000000001E-4</v>
+      </c>
+      <c r="C19">
+        <v>999.67359969999995</v>
+      </c>
+      <c r="D19">
+        <v>0.30006925000000001</v>
+      </c>
+      <c r="E19">
+        <v>3.6809690999999999E-2</v>
+      </c>
+      <c r="F19">
+        <v>0.108183192</v>
+      </c>
+      <c r="G19">
+        <v>4.052745E-3</v>
+      </c>
+      <c r="H19">
+        <v>0.98579144299999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>5.6844399999999998E-4</v>
+      </c>
+      <c r="C20">
+        <v>1000.032227</v>
+      </c>
+      <c r="D20">
+        <v>0.29996158899999997</v>
+      </c>
+      <c r="E20">
+        <v>1.9367124999999999E-2</v>
+      </c>
+      <c r="F20">
+        <v>9.7314092000000005E-2</v>
+      </c>
+      <c r="G20">
+        <v>2.175696E-3</v>
+      </c>
+      <c r="H20">
+        <v>0.995888047</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>6.5962200000000001E-4</v>
+      </c>
+      <c r="C21">
+        <v>1000.129858</v>
+      </c>
+      <c r="D21">
+        <v>0.49965211700000001</v>
+      </c>
+      <c r="E21">
+        <v>4.2670694000000002E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.10375522299999999</v>
+      </c>
+      <c r="G21">
+        <v>5.4323920000000003E-3</v>
+      </c>
+      <c r="H21">
+        <v>0.99410157700000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>7.5361500000000001E-4</v>
+      </c>
+      <c r="C22">
+        <v>1000.183129</v>
+      </c>
+      <c r="D22">
+        <v>0.50001522700000001</v>
+      </c>
+      <c r="E22">
+        <v>1.9893559000000002E-2</v>
+      </c>
+      <c r="F22">
+        <v>9.5239508E-2</v>
+      </c>
+      <c r="G22">
+        <v>2.0156449999999999E-3</v>
+      </c>
+      <c r="H22">
+        <v>0.99718886500000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23">
+        <v>3.65507E-4</v>
+      </c>
+      <c r="C23">
+        <v>1000.201091</v>
+      </c>
+      <c r="D23">
+        <v>0.30000356700000003</v>
+      </c>
+      <c r="E23">
+        <v>5.1118615999999999E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.114449734</v>
+      </c>
+      <c r="G23">
+        <v>4.440495E-3</v>
+      </c>
+      <c r="H23">
+        <v>0.99139601200000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>3.21902E-4</v>
+      </c>
+      <c r="C24">
+        <v>1000.303949</v>
+      </c>
+      <c r="D24">
+        <v>0.50013415000000006</v>
+      </c>
+      <c r="E24">
+        <v>5.7089112999999997E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.11521322000000001</v>
+      </c>
+      <c r="G24">
+        <v>4.8777610000000004E-3</v>
+      </c>
+      <c r="H24">
+        <v>0.99550441999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>4.4690600000000001E-4</v>
+      </c>
+      <c r="C25">
+        <v>1000.564352</v>
+      </c>
+      <c r="D25">
+        <v>0.40118413600000002</v>
+      </c>
+      <c r="E25">
+        <v>4.5435773999999998E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.10055367599999999</v>
+      </c>
+      <c r="G25">
+        <v>4.5400780000000003E-3</v>
+      </c>
+      <c r="H25">
+        <v>0.98875126400000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>2.6539199999999998E-4</v>
+      </c>
+      <c r="C26">
+        <v>1002.961609</v>
+      </c>
+      <c r="D26">
+        <v>0.30087852900000001</v>
+      </c>
+      <c r="E26">
+        <v>7.5760642000000003E-2</v>
+      </c>
+      <c r="F26">
+        <v>0.10911349100000001</v>
+      </c>
+      <c r="G26">
+        <v>5.1225200000000002E-3</v>
+      </c>
+      <c r="H26">
+        <v>0.99228384400000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>2.7240599999999999E-4</v>
+      </c>
+      <c r="C27">
+        <v>1242.8563799999999</v>
+      </c>
+      <c r="D27">
+        <v>0.29883443599999998</v>
+      </c>
+      <c r="E27">
+        <v>6.6170259999999995E-2</v>
+      </c>
+      <c r="F27">
+        <v>0.11349644</v>
+      </c>
+      <c r="G27">
+        <v>5.5628220000000003E-3</v>
+      </c>
+      <c r="H27">
+        <v>0.99175836900000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>5.6636299999999996E-4</v>
+      </c>
+      <c r="C28">
+        <v>1249.038305</v>
+      </c>
+      <c r="D28">
+        <v>0.50009379399999998</v>
+      </c>
+      <c r="E28">
+        <v>5.5513298000000003E-2</v>
+      </c>
+      <c r="F28">
+        <v>0.114298685</v>
+      </c>
+      <c r="G28">
+        <v>5.8367810000000001E-3</v>
+      </c>
+      <c r="H28">
+        <v>0.99043759600000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>4.4455299999999998E-4</v>
+      </c>
+      <c r="C29">
+        <v>1249.8621929999999</v>
+      </c>
+      <c r="D29">
+        <v>0.29980042600000001</v>
+      </c>
+      <c r="E29">
+        <v>3.1885854999999998E-2</v>
+      </c>
+      <c r="F29">
+        <v>0.10856081200000001</v>
+      </c>
+      <c r="G29">
+        <v>3.8722560000000001E-3</v>
+      </c>
+      <c r="H29">
+        <v>0.98956896599999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30">
+        <v>3.4781999999999999E-4</v>
+      </c>
+      <c r="C30">
+        <v>1249.9720520000001</v>
+      </c>
+      <c r="D30">
+        <v>0.29999618500000003</v>
+      </c>
+      <c r="E30">
+        <v>4.7035642000000003E-2</v>
+      </c>
+      <c r="F30">
+        <v>0.10975439100000001</v>
+      </c>
+      <c r="G30">
+        <v>4.7517119999999999E-3</v>
+      </c>
+      <c r="H30">
+        <v>0.98241363800000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31">
+        <v>3.0862499999999998E-4</v>
+      </c>
+      <c r="C31">
+        <v>1250.009063</v>
+      </c>
+      <c r="D31">
+        <v>0.300016848</v>
+      </c>
+      <c r="E31">
+        <v>4.267257E-2</v>
+      </c>
+      <c r="F31">
+        <v>0.107568497</v>
+      </c>
+      <c r="G31">
+        <v>4.6496790000000003E-3</v>
+      </c>
+      <c r="H31">
+        <v>0.98361751799999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32">
+        <v>3.9580799999999999E-4</v>
+      </c>
+      <c r="C32">
+        <v>1250.0364039999999</v>
+      </c>
+      <c r="D32">
+        <v>0.29999587</v>
+      </c>
+      <c r="E32">
+        <v>4.6113999000000003E-2</v>
+      </c>
+      <c r="F32">
+        <v>0.11548971800000001</v>
+      </c>
+      <c r="G32">
+        <v>4.2850120000000004E-3</v>
+      </c>
+      <c r="H32">
+        <v>0.99005631800000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33">
+        <v>4.85129E-4</v>
+      </c>
+      <c r="C33">
+        <v>1250.056002</v>
+      </c>
+      <c r="D33">
+        <v>0.30007985999999998</v>
+      </c>
+      <c r="E33">
+        <v>3.1432143000000003E-2</v>
+      </c>
+      <c r="F33">
+        <v>0.11381099</v>
+      </c>
+      <c r="G33">
+        <v>4.0394979999999999E-3</v>
+      </c>
+      <c r="H33">
+        <v>0.99273382399999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34">
+        <v>4.7428800000000001E-4</v>
+      </c>
+      <c r="C34">
+        <v>1250.0886849999999</v>
+      </c>
+      <c r="D34">
+        <v>0.30001281800000001</v>
+      </c>
+      <c r="E34">
+        <v>3.3010744000000002E-2</v>
+      </c>
+      <c r="F34">
+        <v>0.11308117199999999</v>
+      </c>
+      <c r="G34">
+        <v>5.2047889999999996E-3</v>
+      </c>
+      <c r="H34">
+        <v>0.99108814999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>3.4672300000000001E-4</v>
+      </c>
+      <c r="C35">
+        <v>1250.9434040000001</v>
+      </c>
+      <c r="D35">
+        <v>0.39999618199999998</v>
+      </c>
+      <c r="E35">
+        <v>6.9506928999999995E-2</v>
+      </c>
+      <c r="F35">
+        <v>0.110695898</v>
+      </c>
+      <c r="G35">
+        <v>6.4767380000000001E-3</v>
+      </c>
+      <c r="H35">
+        <v>0.99251876100000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36">
+        <v>5.7827599999999996E-4</v>
+      </c>
+      <c r="C36">
+        <v>1252.670832</v>
+      </c>
+      <c r="D36">
+        <v>0.49995556099999999</v>
+      </c>
+      <c r="E36">
+        <v>4.8558603999999998E-2</v>
+      </c>
+      <c r="F36">
+        <v>9.5985962999999994E-2</v>
+      </c>
+      <c r="G36">
+        <v>5.6972220000000001E-3</v>
+      </c>
+      <c r="H36">
+        <v>0.98525604600000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>4.6433100000000001E-4</v>
+      </c>
+      <c r="C37">
+        <v>1255.424561</v>
+      </c>
+      <c r="D37">
+        <v>0.39989443400000002</v>
+      </c>
+      <c r="E37">
+        <v>4.1705930000000002E-2</v>
+      </c>
+      <c r="F37">
+        <v>0.10475915299999999</v>
+      </c>
+      <c r="G37">
+        <v>4.4100290000000002E-3</v>
+      </c>
+      <c r="H37">
+        <v>0.98489914300000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <v>4.11395E-4</v>
+      </c>
+      <c r="C38">
+        <v>1267.5140690000001</v>
+      </c>
+      <c r="D38">
+        <v>0.49920661399999999</v>
+      </c>
+      <c r="E38">
+        <v>4.8344787E-2</v>
+      </c>
+      <c r="F38">
+        <v>0.12562072899999999</v>
+      </c>
+      <c r="G38">
+        <v>3.9256580000000003E-3</v>
+      </c>
+      <c r="H38">
+        <v>0.99312282299999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39">
+        <v>3.13467E-4</v>
+      </c>
+      <c r="C39">
+        <v>1271.3936630000001</v>
+      </c>
+      <c r="D39">
+        <v>0.40056073800000003</v>
+      </c>
+      <c r="E39">
+        <v>7.1139833E-2</v>
+      </c>
+      <c r="F39">
+        <v>0.11312243299999999</v>
+      </c>
+      <c r="G39">
+        <v>5.9295399999999996E-3</v>
+      </c>
+      <c r="H39">
+        <v>0.99374623100000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40">
+        <v>7.2654800000000004E-4</v>
+      </c>
+      <c r="C40">
+        <v>1455.6305829999999</v>
+      </c>
+      <c r="D40">
+        <v>0.49692148400000002</v>
+      </c>
+      <c r="E40">
+        <v>2.3973168999999999E-2</v>
+      </c>
+      <c r="F40">
+        <v>9.1711663999999998E-2</v>
+      </c>
+      <c r="G40">
+        <v>2.966729E-3</v>
+      </c>
+      <c r="H40">
+        <v>0.99718670099999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41">
+        <v>8.1662800000000002E-4</v>
+      </c>
+      <c r="C41">
+        <v>1492.737848</v>
+      </c>
+      <c r="D41">
+        <v>0.50025813699999999</v>
+      </c>
+      <c r="E41">
+        <v>2.6577284999999999E-2</v>
+      </c>
+      <c r="F41">
+        <v>9.2475197999999995E-2</v>
+      </c>
+      <c r="G41">
+        <v>2.9827109999999999E-3</v>
+      </c>
+      <c r="H41">
+        <v>0.99533773199999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>8.5975099999999996E-4</v>
+      </c>
+      <c r="C42">
+        <v>1494.673636</v>
+      </c>
+      <c r="D42">
+        <v>0.50000099099999995</v>
+      </c>
+      <c r="E42">
+        <v>2.6915963000000001E-2</v>
+      </c>
+      <c r="F42">
+        <v>9.1934420000000003E-2</v>
+      </c>
+      <c r="G42">
+        <v>2.846627E-3</v>
+      </c>
+      <c r="H42">
+        <v>0.99697522500000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43">
+        <v>7.0617800000000001E-4</v>
+      </c>
+      <c r="C43">
+        <v>1497.1705119999999</v>
+      </c>
+      <c r="D43">
+        <v>0.49990232400000001</v>
+      </c>
+      <c r="E43">
+        <v>2.4668497000000001E-2</v>
+      </c>
+      <c r="F43">
+        <v>9.1588153000000005E-2</v>
+      </c>
+      <c r="G43">
+        <v>3.0430520000000001E-3</v>
+      </c>
+      <c r="H43">
+        <v>0.99707969600000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44">
+        <v>6.3737199999999998E-4</v>
+      </c>
+      <c r="C44">
+        <v>1500.051467</v>
+      </c>
+      <c r="D44">
+        <v>0.29994249899999997</v>
+      </c>
+      <c r="E44">
+        <v>2.6047677000000002E-2</v>
+      </c>
+      <c r="F44">
+        <v>0.10857765</v>
+      </c>
+      <c r="G44">
+        <v>7.1048200000000002E-4</v>
+      </c>
+      <c r="H44">
+        <v>0.99349073799999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45">
+        <v>5.2616900000000005E-4</v>
+      </c>
+      <c r="C45">
+        <v>1500.0874120000001</v>
+      </c>
+      <c r="D45">
+        <v>0.30007125099999998</v>
+      </c>
+      <c r="E45">
+        <v>1.9110674000000001E-2</v>
+      </c>
+      <c r="F45">
+        <v>0.12915310899999999</v>
+      </c>
+      <c r="G45">
+        <v>7.8471699999999999E-4</v>
+      </c>
+      <c r="H45">
+        <v>0.99525415699999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>7.4180700000000003E-4</v>
+      </c>
+      <c r="C46">
+        <v>1500.215265</v>
+      </c>
+      <c r="D46">
+        <v>0.39993976599999997</v>
+      </c>
+      <c r="E46">
+        <v>2.7369943000000001E-2</v>
+      </c>
+      <c r="F46">
+        <v>9.7766817000000006E-2</v>
+      </c>
+      <c r="G46">
+        <v>4.3964299999999998E-4</v>
+      </c>
+      <c r="H46">
+        <v>0.99480906899999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47">
+        <v>9.1292700000000001E-4</v>
+      </c>
+      <c r="C47">
+        <v>1500.5413000000001</v>
+      </c>
+      <c r="D47">
+        <v>0.50044513199999996</v>
+      </c>
+      <c r="E47">
+        <v>2.0620128000000001E-2</v>
+      </c>
+      <c r="F47">
+        <v>0.103834646</v>
+      </c>
+      <c r="G47">
+        <v>4.4096199999999998E-4</v>
+      </c>
+      <c r="H47">
+        <v>0.99445706499999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48">
+        <v>9.4360899999999998E-4</v>
+      </c>
+      <c r="C48">
+        <v>1500.993866</v>
+      </c>
+      <c r="D48">
+        <v>0.499986655</v>
+      </c>
+      <c r="E48">
+        <v>2.1720821000000001E-2</v>
+      </c>
+      <c r="F48">
+        <v>0.103615651</v>
+      </c>
+      <c r="G48">
+        <v>8.3131500000000001E-4</v>
+      </c>
+      <c r="H48">
+        <v>0.99464200000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <v>6.1466400000000001E-4</v>
+      </c>
+      <c r="C49">
+        <v>1502.4972680000001</v>
+      </c>
+      <c r="D49">
+        <v>0.40017336999999997</v>
+      </c>
+      <c r="E49">
+        <v>2.0735538000000001E-2</v>
+      </c>
+      <c r="F49">
+        <v>9.4777095000000006E-2</v>
+      </c>
+      <c r="G49">
+        <v>2.47956E-3</v>
+      </c>
+      <c r="H49">
+        <v>0.99691817900000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50">
+        <v>6.6162899999999995E-4</v>
+      </c>
+      <c r="C50">
+        <v>1504.5464079999999</v>
+      </c>
+      <c r="D50">
+        <v>0.40074769799999999</v>
+      </c>
+      <c r="E50">
+        <v>2.2464746000000001E-2</v>
+      </c>
+      <c r="F50">
+        <v>9.4852504000000004E-2</v>
+      </c>
+      <c r="G50">
+        <v>2.9607710000000001E-3</v>
+      </c>
+      <c r="H50">
+        <v>0.99641502000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51">
+        <v>7.2370699999999997E-4</v>
+      </c>
+      <c r="C51">
+        <v>1752.5926159999999</v>
+      </c>
+      <c r="D51">
+        <v>0.50002069100000002</v>
+      </c>
+      <c r="E51">
+        <v>2.4334100000000001E-2</v>
+      </c>
+      <c r="F51">
+        <v>9.0262732999999998E-2</v>
+      </c>
+      <c r="G51">
+        <v>2.7651020000000002E-3</v>
+      </c>
+      <c r="H51">
+        <v>0.99688110399999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52">
+        <v>8.0128199999999995E-4</v>
+      </c>
+      <c r="C52">
+        <v>1995.9935250000001</v>
+      </c>
+      <c r="D52">
+        <v>0.49970003499999999</v>
+      </c>
+      <c r="E52">
+        <v>2.3888031000000001E-2</v>
+      </c>
+      <c r="F52">
+        <v>0.101849986</v>
+      </c>
+      <c r="G52">
+        <v>6.1271999999999997E-4</v>
+      </c>
+      <c r="H52">
+        <v>0.99330616800000004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53">
+        <v>6.8117199999999996E-4</v>
+      </c>
+      <c r="C53">
+        <v>1999.6194820000001</v>
+      </c>
+      <c r="D53">
+        <v>0.49998881699999997</v>
+      </c>
+      <c r="E53">
+        <v>2.6883537999999998E-2</v>
+      </c>
+      <c r="F53">
+        <v>8.8787929000000002E-2</v>
+      </c>
+      <c r="G53">
+        <v>2.7722139999999998E-3</v>
+      </c>
+      <c r="H53">
+        <v>0.99639685600000005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54">
+        <v>6.1575900000000001E-4</v>
+      </c>
+      <c r="C54">
+        <v>1999.9767119999999</v>
+      </c>
+      <c r="D54">
+        <v>0.40001579300000001</v>
+      </c>
+      <c r="E54">
+        <v>2.3810701E-2</v>
+      </c>
+      <c r="F54">
+        <v>9.3052383000000002E-2</v>
+      </c>
+      <c r="G54">
+        <v>1.4778720000000001E-3</v>
+      </c>
+      <c r="H54">
+        <v>0.99505876199999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55">
+        <v>5.7284199999999995E-4</v>
+      </c>
+      <c r="C55">
+        <v>2000.4061589999999</v>
+      </c>
+      <c r="D55">
+        <v>0.40002267499999999</v>
+      </c>
+      <c r="E55">
+        <v>2.5438157999999999E-2</v>
+      </c>
+      <c r="F55">
+        <v>8.9342075000000007E-2</v>
+      </c>
+      <c r="G55">
+        <v>1.5362749999999999E-3</v>
+      </c>
+      <c r="H55">
+        <v>0.99545406299999994</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56">
+        <v>7.3430900000000005E-4</v>
+      </c>
+      <c r="C56">
+        <v>2000.6603399999999</v>
+      </c>
+      <c r="D56">
+        <v>0.50012684799999996</v>
+      </c>
+      <c r="E56">
+        <v>2.6662858000000001E-2</v>
+      </c>
+      <c r="F56">
+        <v>8.9674559000000001E-2</v>
+      </c>
+      <c r="G56">
+        <v>3.0504239999999999E-3</v>
+      </c>
+      <c r="H56">
+        <v>0.99543250999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="C57">
+        <v>160</v>
+      </c>
+      <c r="D57">
+        <v>0.2</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>9.6295699999999996E-4</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58">
+        <v>2.81E-4</v>
+      </c>
+      <c r="C58">
+        <v>160</v>
+      </c>
+      <c r="D58">
+        <v>0.2</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>5.4068499999999995E-4</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <v>3.0699999999999998E-4</v>
+      </c>
+      <c r="C59">
+        <v>160</v>
+      </c>
+      <c r="D59">
+        <v>0.2</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>5.7356200000000001E-4</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="C60">
+        <v>160</v>
+      </c>
+      <c r="D60">
+        <v>0.2</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1.609114E-3</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>4.3100000000000001E-4</v>
+      </c>
+      <c r="C61">
+        <v>160</v>
+      </c>
+      <c r="D61">
+        <v>0.2</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>2.0221039999999998E-3</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62">
+        <v>5.3200000000000003E-4</v>
+      </c>
+      <c r="C62">
+        <v>160</v>
+      </c>
+      <c r="D62">
+        <v>0.2</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>1.858317E-3</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>6.8900000000000005E-4</v>
+      </c>
+      <c r="C63">
+        <v>160</v>
+      </c>
+      <c r="D63">
+        <v>0.2</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1.541461E-3</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>1.281E-3</v>
+      </c>
+      <c r="C64">
+        <v>160</v>
+      </c>
+      <c r="D64">
+        <v>0.2</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1.2030529999999999E-3</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <v>2.52E-4</v>
+      </c>
+      <c r="C65">
+        <v>200</v>
+      </c>
+      <c r="D65">
+        <v>0.2</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>2.27729E-4</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66">
+        <v>2.8299999999999999E-4</v>
+      </c>
+      <c r="C66">
+        <v>200</v>
+      </c>
+      <c r="D66">
+        <v>0.2</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1.347741E-3</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="C67">
+        <v>200</v>
+      </c>
+      <c r="D67">
+        <v>0.2</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1.48168E-3</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68">
+        <v>3.8299999999999999E-4</v>
+      </c>
+      <c r="C68">
+        <v>200</v>
+      </c>
+      <c r="D68">
+        <v>0.2</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>1.5823530000000001E-3</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69">
+        <v>4.64E-4</v>
+      </c>
+      <c r="C69">
+        <v>200</v>
+      </c>
+      <c r="D69">
+        <v>0.2</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1.264077E-3</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70">
+        <v>5.8399999999999999E-4</v>
+      </c>
+      <c r="C70">
+        <v>200</v>
+      </c>
+      <c r="D70">
+        <v>0.2</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1.7501089999999999E-3</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71">
+        <v>7.8799999999999996E-4</v>
+      </c>
+      <c r="C71">
+        <v>200</v>
+      </c>
+      <c r="D71">
+        <v>0.2</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1.2385709999999999E-3</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72">
+        <v>1.0950000000000001E-3</v>
+      </c>
+      <c r="C72">
+        <v>200</v>
+      </c>
+      <c r="D72">
+        <v>0.2</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>9.1166800000000003E-4</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73">
+        <v>1.5E-3</v>
+      </c>
+      <c r="C73">
+        <v>200</v>
+      </c>
+      <c r="D73">
+        <v>0.2</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>4.5693399999999999E-4</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>2.7099999999999997E-4</v>
+      </c>
+      <c r="C74">
+        <v>240</v>
+      </c>
+      <c r="D74">
+        <v>0.2</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>5.6943599999999999E-4</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>2.9799999999999998E-4</v>
+      </c>
+      <c r="C75">
+        <v>240</v>
+      </c>
+      <c r="D75">
+        <v>0.2</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>1.764112E-3</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>3.4299999999999999E-4</v>
+      </c>
+      <c r="C76">
+        <v>240</v>
+      </c>
+      <c r="D76">
+        <v>0.2</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>2.7815829999999998E-3</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77">
+        <v>4.0400000000000001E-4</v>
+      </c>
+      <c r="C77">
+        <v>240</v>
+      </c>
+      <c r="D77">
+        <v>0.2</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>3.124384E-3</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>5.0299999999999997E-4</v>
+      </c>
+      <c r="C78">
+        <v>240</v>
+      </c>
+      <c r="D78">
+        <v>0.2</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>3.5047860000000002E-3</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79">
+        <v>6.0999999999999997E-4</v>
+      </c>
+      <c r="C79">
+        <v>240</v>
+      </c>
+      <c r="D79">
+        <v>0.2</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>3.015471E-3</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>8.0400000000000003E-4</v>
+      </c>
+      <c r="C80">
+        <v>240</v>
+      </c>
+      <c r="D80">
+        <v>0.2</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>2.3056370000000001E-3</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81">
+        <v>1.0920000000000001E-3</v>
+      </c>
+      <c r="C81">
+        <v>240</v>
+      </c>
+      <c r="D81">
+        <v>0.2</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>1.8617429999999999E-3</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82">
+        <v>1.4159999999999999E-3</v>
+      </c>
+      <c r="C82">
+        <v>240</v>
+      </c>
+      <c r="D82">
+        <v>0.2</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>9.7170399999999999E-4</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83">
+        <v>2.5399999999999999E-4</v>
+      </c>
+      <c r="C83">
+        <v>280</v>
+      </c>
+      <c r="D83">
+        <v>0.2</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>6.6906099999999998E-4</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>2.9399999999999999E-4</v>
+      </c>
+      <c r="C84">
+        <v>280</v>
+      </c>
+      <c r="D84">
+        <v>0.2</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>2.4819130000000001E-3</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85">
+        <v>3.3700000000000001E-4</v>
+      </c>
+      <c r="C85">
+        <v>280</v>
+      </c>
+      <c r="D85">
+        <v>0.2</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>3.5047860000000002E-3</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>4.0200000000000001E-4</v>
+      </c>
+      <c r="C86">
+        <v>280</v>
+      </c>
+      <c r="D86">
+        <v>0.2</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>3.5300269999999998E-3</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>4.9700000000000005E-4</v>
+      </c>
+      <c r="C87">
+        <v>280</v>
+      </c>
+      <c r="D87">
+        <v>0.2</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>3.7511160000000001E-3</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>6.1700000000000004E-4</v>
+      </c>
+      <c r="C88">
+        <v>280</v>
+      </c>
+      <c r="D88">
+        <v>0.2</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>3.7918209999999999E-3</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="C89">
+        <v>280</v>
+      </c>
+      <c r="D89">
+        <v>0.2</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>2.9280959999999998E-3</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90">
+        <v>1.0989999999999999E-3</v>
+      </c>
+      <c r="C90">
+        <v>280</v>
+      </c>
+      <c r="D90">
+        <v>0.2</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>2.4002030000000001E-3</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <v>1.2780000000000001E-3</v>
+      </c>
+      <c r="C91">
+        <v>280</v>
+      </c>
+      <c r="D91">
+        <v>0.2</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1.534342E-3</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="C92">
+        <v>2050</v>
+      </c>
+      <c r="D92">
+        <v>0.3</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93">
+        <v>9.0499999999999999E-4</v>
+      </c>
+      <c r="C93">
+        <v>2350</v>
+      </c>
+      <c r="D93">
+        <v>0.5</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94">
+        <v>6.3250000000000003E-4</v>
+      </c>
+      <c r="C94">
+        <v>1600</v>
+      </c>
+      <c r="D94">
+        <v>0.3</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95">
+        <v>6.0749999999999997E-4</v>
+      </c>
+      <c r="C95">
+        <v>1500</v>
+      </c>
+      <c r="D95">
+        <v>0.3</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96">
+        <v>7.3800000000000005E-4</v>
+      </c>
+      <c r="C96">
+        <v>1450</v>
+      </c>
+      <c r="D96">
+        <v>0.5</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97">
+        <v>8.6499999999999999E-4</v>
+      </c>
+      <c r="C97">
+        <v>1850</v>
+      </c>
+      <c r="D97">
+        <v>0.5</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98">
+        <v>6.2750000000000002E-4</v>
+      </c>
+      <c r="C98">
+        <v>1600</v>
+      </c>
+      <c r="D98">
+        <v>0.3</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99">
+        <v>5.8500000000000002E-4</v>
+      </c>
+      <c r="C99">
+        <v>1450</v>
+      </c>
+      <c r="D99">
+        <v>0.3</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100">
+        <v>7.0750000000000001E-4</v>
+      </c>
+      <c r="C100">
+        <v>1400</v>
+      </c>
+      <c r="D100">
+        <v>0.5</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101">
+        <v>6.3500000000000004E-4</v>
+      </c>
+      <c r="C101">
+        <v>1150</v>
+      </c>
+      <c r="D101">
+        <v>0.5</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102">
+        <v>6.6750000000000002E-4</v>
+      </c>
+      <c r="C102">
+        <v>1600</v>
+      </c>
+      <c r="D102">
+        <v>0.3</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103">
+        <v>6.3029999999999998E-4</v>
+      </c>
+      <c r="C103">
+        <v>1500</v>
+      </c>
+      <c r="D103">
+        <v>0.3</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104">
+        <v>7.2250000000000005E-4</v>
+      </c>
+      <c r="C104">
+        <v>1350</v>
+      </c>
+      <c r="D104">
+        <v>0.5</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105">
+        <v>6.7250000000000003E-4</v>
+      </c>
+      <c r="C105">
+        <v>1200</v>
+      </c>
+      <c r="D105">
+        <v>0.5</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/V2.0/settings/data_main.xlsx
+++ b/V2.0/settings/data_main.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iagr9\Projekte\MA\MA-Model_2\V2.0\settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3613FEDA-F94C-43F5-900B-C3297FFE8110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0908B36A-92F1-4A61-9244-679E30654EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="sozh" sheetId="2" r:id="rId2"/>
     <sheet name="detail_V_dis" sheetId="3" r:id="rId3"/>
+    <sheet name="detail_lambda" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="21">
   <si>
     <t>exp</t>
   </si>
@@ -14607,4 +14608,592 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57E61B2-62D9-4C9D-8993-F37D4A7C0058}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C2">
+        <v>160</v>
+      </c>
+      <c r="D2">
+        <v>0.2</v>
+      </c>
+      <c r="E2">
+        <v>0.99572192500000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C3">
+        <v>160</v>
+      </c>
+      <c r="D3">
+        <v>0.2</v>
+      </c>
+      <c r="E3">
+        <v>0.99572192500000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C4">
+        <v>160</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>0.99572192500000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C5">
+        <v>160</v>
+      </c>
+      <c r="D5">
+        <v>0.2</v>
+      </c>
+      <c r="E5">
+        <v>0.996256684</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C6">
+        <v>160</v>
+      </c>
+      <c r="D6">
+        <v>0.2</v>
+      </c>
+      <c r="E6">
+        <v>0.996256684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>0.2</v>
+      </c>
+      <c r="E7">
+        <v>0.95080213899999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8">
+        <v>0.2</v>
+      </c>
+      <c r="E8">
+        <v>0.98930481299999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>0.99358288800000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C10">
+        <v>200</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+      <c r="E10">
+        <v>0.99518716600000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
+      </c>
+      <c r="D11">
+        <v>0.2</v>
+      </c>
+      <c r="E11">
+        <v>0.99732620299999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
+        <v>0.96243386200000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C13">
+        <v>240</v>
+      </c>
+      <c r="D13">
+        <v>0.2</v>
+      </c>
+      <c r="E13">
+        <v>0.74973261999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C14">
+        <v>240</v>
+      </c>
+      <c r="D14">
+        <v>0.2</v>
+      </c>
+      <c r="E14">
+        <v>0.97433155100000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C15">
+        <v>240</v>
+      </c>
+      <c r="D15">
+        <v>0.2</v>
+      </c>
+      <c r="E15">
+        <v>0.98609625700000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C16">
+        <v>240</v>
+      </c>
+      <c r="D16">
+        <v>0.2</v>
+      </c>
+      <c r="E16">
+        <v>0.99144385000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C17">
+        <v>240</v>
+      </c>
+      <c r="D17">
+        <v>0.2</v>
+      </c>
+      <c r="E17">
+        <v>0.99518716600000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C18">
+        <v>240</v>
+      </c>
+      <c r="D18">
+        <v>0.05</v>
+      </c>
+      <c r="E18">
+        <v>0.93015873000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C19">
+        <v>240</v>
+      </c>
+      <c r="D19">
+        <v>0.05</v>
+      </c>
+      <c r="E19">
+        <v>0.94973545000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C20">
+        <v>240</v>
+      </c>
+      <c r="D20">
+        <v>0.05</v>
+      </c>
+      <c r="E20">
+        <v>0.97566137600000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C21">
+        <v>240</v>
+      </c>
+      <c r="D21">
+        <v>0.05</v>
+      </c>
+      <c r="E21">
+        <v>0.98783068799999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C22">
+        <v>240</v>
+      </c>
+      <c r="D22">
+        <v>0.05</v>
+      </c>
+      <c r="E22">
+        <v>0.99523809500000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C23">
+        <v>240</v>
+      </c>
+      <c r="D23">
+        <v>0.1</v>
+      </c>
+      <c r="E23">
+        <v>0.92751322800000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C24">
+        <v>280</v>
+      </c>
+      <c r="D24">
+        <v>0.2</v>
+      </c>
+      <c r="E24">
+        <v>0.64973261999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C25">
+        <v>280</v>
+      </c>
+      <c r="D25">
+        <v>0.2</v>
+      </c>
+      <c r="E25">
+        <v>0.91657754000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C26">
+        <v>280</v>
+      </c>
+      <c r="D26">
+        <v>0.2</v>
+      </c>
+      <c r="E26">
+        <v>0.97754010700000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C27">
+        <v>280</v>
+      </c>
+      <c r="D27">
+        <v>0.2</v>
+      </c>
+      <c r="E27">
+        <v>0.98716577500000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C28">
+        <v>280</v>
+      </c>
+      <c r="D28">
+        <v>0.2</v>
+      </c>
+      <c r="E28">
+        <v>0.99251336899999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C29">
+        <v>280</v>
+      </c>
+      <c r="D29">
+        <v>0.05</v>
+      </c>
+      <c r="E29">
+        <v>0.89470899500000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C30">
+        <v>280</v>
+      </c>
+      <c r="D30">
+        <v>0.05</v>
+      </c>
+      <c r="E30">
+        <v>0.91216931199999995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C31">
+        <v>280</v>
+      </c>
+      <c r="D31">
+        <v>0.05</v>
+      </c>
+      <c r="E31">
+        <v>0.96137566100000005</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C32">
+        <v>280</v>
+      </c>
+      <c r="D32">
+        <v>0.05</v>
+      </c>
+      <c r="E32">
+        <v>0.98148148099999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C33">
+        <v>280</v>
+      </c>
+      <c r="D33">
+        <v>0.05</v>
+      </c>
+      <c r="E33">
+        <v>0.98994709000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C34">
+        <v>280</v>
+      </c>
+      <c r="D34">
+        <v>0.1</v>
+      </c>
+      <c r="E34">
+        <v>0.89894179900000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/V2.0/settings/data_main.xlsx
+++ b/V2.0/settings/data_main.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iagr9\Projekte\MA\MA-Model_2\V2.0\settings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Projekte\MA-Model_2\V2.0\settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0908B36A-92F1-4A61-9244-679E30654EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AD5B08-6594-4397-9751-6C4FDCE29170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="22">
   <si>
     <t>exp</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>h_c_0</t>
+  </si>
+  <si>
+    <t>h_dis_0</t>
   </si>
 </sst>
 </file>
@@ -11889,7 +11892,7 @@
         <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>20</v>
@@ -11915,7 +11918,7 @@
         <v>0.29701893400000001</v>
       </c>
       <c r="E2">
-        <v>3.6502927999999997E-2</v>
+        <v>3.55819E-2</v>
       </c>
       <c r="F2">
         <v>9.6633421999999997E-2</v>
@@ -11941,7 +11944,7 @@
         <v>0.50333939500000002</v>
       </c>
       <c r="E3">
-        <v>2.8484735000000001E-2</v>
+        <v>2.2846333E-2</v>
       </c>
       <c r="F3">
         <v>9.2660582000000005E-2</v>
@@ -11967,7 +11970,7 @@
         <v>0.49988101000000001</v>
       </c>
       <c r="E4">
-        <v>3.8919571E-2</v>
+        <v>3.3656999999999999E-2</v>
       </c>
       <c r="F4">
         <v>0.10772396300000001</v>
@@ -11993,7 +11996,7 @@
         <v>0.399764919</v>
       </c>
       <c r="E5">
-        <v>3.8463404E-2</v>
+        <v>3.2073999999999998E-2</v>
       </c>
       <c r="F5">
         <v>9.5001253999999993E-2</v>
@@ -12019,7 +12022,7 @@
         <v>0.50015754999999995</v>
       </c>
       <c r="E6">
-        <v>4.0361706999999997E-2</v>
+        <v>3.8374125000000002E-2</v>
       </c>
       <c r="F6">
         <v>0.101830843</v>
@@ -12045,7 +12048,7 @@
         <v>0.49989457599999998</v>
       </c>
       <c r="E7">
-        <v>3.8023349999999997E-2</v>
+        <v>3.2000428999999997E-2</v>
       </c>
       <c r="F7">
         <v>0.108397884</v>
@@ -12071,7 +12074,7 @@
         <v>0.40002338700000001</v>
       </c>
       <c r="E8">
-        <v>6.6916982E-2</v>
+        <v>2.9817666999999999E-2</v>
       </c>
       <c r="F8">
         <v>0.106790285</v>
@@ -12097,7 +12100,7 @@
         <v>0.29988877800000002</v>
       </c>
       <c r="E9">
-        <v>3.6448479999999998E-2</v>
+        <v>2.9670385000000001E-2</v>
       </c>
       <c r="F9">
         <v>0.10019613600000001</v>
@@ -12123,7 +12126,7 @@
         <v>0.50033280999999996</v>
       </c>
       <c r="E10">
-        <v>3.7521118999999999E-2</v>
+        <v>2.9766384999999999E-2</v>
       </c>
       <c r="F10">
         <v>9.8495864000000002E-2</v>
@@ -12149,7 +12152,7 @@
         <v>0.30092750000000001</v>
       </c>
       <c r="E11">
-        <v>3.3229887E-2</v>
+        <v>3.4920187999999998E-2</v>
       </c>
       <c r="F11">
         <v>0.100884113</v>
@@ -12175,7 +12178,7 @@
         <v>0.40003253100000002</v>
       </c>
       <c r="E12">
-        <v>7.0955006000000001E-2</v>
+        <v>1.9631529000000002E-2</v>
       </c>
       <c r="F12">
         <v>0.11041532699999999</v>
@@ -12201,7 +12204,7 @@
         <v>0.49949943499999999</v>
       </c>
       <c r="E13">
-        <v>4.2382797999999999E-2</v>
+        <v>4.1055332999999999E-2</v>
       </c>
       <c r="F13">
         <v>9.7580385000000006E-2</v>
@@ -12227,7 +12230,7 @@
         <v>0.27718706700000001</v>
       </c>
       <c r="E14">
-        <v>3.6368708E-2</v>
+        <v>1.9585846000000001E-2</v>
       </c>
       <c r="F14">
         <v>0.103970942</v>
@@ -12253,7 +12256,7 @@
         <v>0.499859416</v>
       </c>
       <c r="E15">
-        <v>1.8851822000000001E-2</v>
+        <v>1.5360333E-2</v>
       </c>
       <c r="F15">
         <v>0.10280117799999999</v>
@@ -12279,7 +12282,7 @@
         <v>0.29920427599999999</v>
       </c>
       <c r="E16">
-        <v>4.1816536000000001E-2</v>
+        <v>3.5955842000000002E-2</v>
       </c>
       <c r="F16">
         <v>0.101860464</v>
@@ -12305,7 +12308,7 @@
         <v>0.40006547100000001</v>
       </c>
       <c r="E17">
-        <v>2.4784075999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>9.7689174000000004E-2</v>
@@ -12331,7 +12334,7 @@
         <v>0.49991358299999999</v>
       </c>
       <c r="E18">
-        <v>1.8550810000000001E-2</v>
+        <v>1.5761217000000001E-2</v>
       </c>
       <c r="F18">
         <v>9.4884389999999999E-2</v>
@@ -12357,7 +12360,7 @@
         <v>0.30006925000000001</v>
       </c>
       <c r="E19">
-        <v>3.6809690999999999E-2</v>
+        <v>2.6276999999999998E-2</v>
       </c>
       <c r="F19">
         <v>0.108183192</v>
@@ -12383,7 +12386,7 @@
         <v>0.29996158899999997</v>
       </c>
       <c r="E20">
-        <v>1.9367124999999999E-2</v>
+        <v>1.6771635999999999E-2</v>
       </c>
       <c r="F20">
         <v>9.7314092000000005E-2</v>
@@ -12409,7 +12412,7 @@
         <v>0.49965211700000001</v>
       </c>
       <c r="E21">
-        <v>4.2670694000000002E-2</v>
+        <v>3.9373499999999999E-2</v>
       </c>
       <c r="F21">
         <v>0.10375522299999999</v>
@@ -12435,7 +12438,7 @@
         <v>0.50001522700000001</v>
       </c>
       <c r="E22">
-        <v>1.9893559000000002E-2</v>
+        <v>1.5923438000000002E-2</v>
       </c>
       <c r="F22">
         <v>9.5239508E-2</v>
@@ -12461,7 +12464,7 @@
         <v>0.30000356700000003</v>
       </c>
       <c r="E23">
-        <v>5.1118615999999999E-2</v>
+        <v>2.9010142999999999E-2</v>
       </c>
       <c r="F23">
         <v>0.114449734</v>
@@ -12487,7 +12490,7 @@
         <v>0.50013415000000006</v>
       </c>
       <c r="E24">
-        <v>5.7089112999999997E-2</v>
+        <v>2.9240461999999998E-2</v>
       </c>
       <c r="F24">
         <v>0.11521322000000001</v>
@@ -12513,7 +12516,7 @@
         <v>0.40118413600000002</v>
       </c>
       <c r="E25">
-        <v>4.5435773999999998E-2</v>
+        <v>3.6132938000000003E-2</v>
       </c>
       <c r="F25">
         <v>0.10055367599999999</v>
@@ -12539,7 +12542,7 @@
         <v>0.30087852900000001</v>
       </c>
       <c r="E26">
-        <v>7.5760642000000003E-2</v>
+        <v>2.4022870000000002E-2</v>
       </c>
       <c r="F26">
         <v>0.10911349100000001</v>
@@ -12565,7 +12568,7 @@
         <v>0.29883443599999998</v>
       </c>
       <c r="E27">
-        <v>6.6170259999999995E-2</v>
+        <v>2.9332111000000001E-2</v>
       </c>
       <c r="F27">
         <v>0.11349644</v>
@@ -12591,7 +12594,7 @@
         <v>0.50009379399999998</v>
       </c>
       <c r="E28">
-        <v>5.5513298000000003E-2</v>
+        <v>3.3174416999999998E-2</v>
       </c>
       <c r="F28">
         <v>0.114298685</v>
@@ -12617,7 +12620,7 @@
         <v>0.29980042600000001</v>
       </c>
       <c r="E29">
-        <v>3.1885854999999998E-2</v>
+        <v>2.8255058999999999E-2</v>
       </c>
       <c r="F29">
         <v>0.10856081200000001</v>
@@ -12643,7 +12646,7 @@
         <v>0.29999618500000003</v>
       </c>
       <c r="E30">
-        <v>4.7035642000000003E-2</v>
+        <v>4.2983100000000003E-2</v>
       </c>
       <c r="F30">
         <v>0.10975439100000001</v>
@@ -12669,7 +12672,7 @@
         <v>0.300016848</v>
       </c>
       <c r="E31">
-        <v>4.267257E-2</v>
+        <v>3.03678E-2</v>
       </c>
       <c r="F31">
         <v>0.107568497</v>
@@ -12695,7 +12698,7 @@
         <v>0.29999587</v>
       </c>
       <c r="E32">
-        <v>4.6113999000000003E-2</v>
+        <v>2.3775000000000001E-2</v>
       </c>
       <c r="F32">
         <v>0.11548971800000001</v>
@@ -12721,7 +12724,7 @@
         <v>0.30007985999999998</v>
       </c>
       <c r="E33">
-        <v>3.1432143000000003E-2</v>
+        <v>2.7580614999999999E-2</v>
       </c>
       <c r="F33">
         <v>0.11381099</v>
@@ -12747,7 +12750,7 @@
         <v>0.30001281800000001</v>
       </c>
       <c r="E34">
-        <v>3.3010744000000002E-2</v>
+        <v>2.8364166999999999E-2</v>
       </c>
       <c r="F34">
         <v>0.11308117199999999</v>
@@ -12773,7 +12776,7 @@
         <v>0.39999618199999998</v>
       </c>
       <c r="E35">
-        <v>6.9506928999999995E-2</v>
+        <v>3.9580443999999999E-2</v>
       </c>
       <c r="F35">
         <v>0.110695898</v>
@@ -12799,7 +12802,7 @@
         <v>0.49995556099999999</v>
       </c>
       <c r="E36">
-        <v>4.8558603999999998E-2</v>
+        <v>4.6688437999999999E-2</v>
       </c>
       <c r="F36">
         <v>9.5985962999999994E-2</v>
@@ -12825,7 +12828,7 @@
         <v>0.39989443400000002</v>
       </c>
       <c r="E37">
-        <v>4.1705930000000002E-2</v>
+        <v>3.2895832999999999E-2</v>
       </c>
       <c r="F37">
         <v>0.10475915299999999</v>
@@ -12851,7 +12854,7 @@
         <v>0.49920661399999999</v>
       </c>
       <c r="E38">
-        <v>4.8344787E-2</v>
+        <v>2.7389750000000001E-2</v>
       </c>
       <c r="F38">
         <v>0.12562072899999999</v>
@@ -12877,7 +12880,7 @@
         <v>0.40056073800000003</v>
       </c>
       <c r="E39">
-        <v>7.1139833E-2</v>
+        <v>3.3499599999999997E-2</v>
       </c>
       <c r="F39">
         <v>0.11312243299999999</v>
@@ -12903,7 +12906,7 @@
         <v>0.49692148400000002</v>
       </c>
       <c r="E40">
-        <v>2.3973168999999999E-2</v>
+        <v>1.6203833000000001E-2</v>
       </c>
       <c r="F40">
         <v>9.1711663999999998E-2</v>
@@ -12929,7 +12932,7 @@
         <v>0.50025813699999999</v>
       </c>
       <c r="E41">
-        <v>2.6577284999999999E-2</v>
+        <v>2.5555333E-2</v>
       </c>
       <c r="F41">
         <v>9.2475197999999995E-2</v>
@@ -12955,7 +12958,7 @@
         <v>0.50000099099999995</v>
       </c>
       <c r="E42">
-        <v>2.6915963000000001E-2</v>
+        <v>2.7710216999999999E-2</v>
       </c>
       <c r="F42">
         <v>9.1934420000000003E-2</v>
@@ -12981,7 +12984,7 @@
         <v>0.49990232400000001</v>
       </c>
       <c r="E43">
-        <v>2.4668497000000001E-2</v>
+        <v>1.9429286E-2</v>
       </c>
       <c r="F43">
         <v>9.1588153000000005E-2</v>
@@ -13007,7 +13010,7 @@
         <v>0.29994249899999997</v>
       </c>
       <c r="E44">
-        <v>2.6047677000000002E-2</v>
+        <v>2.6298999999999999E-2</v>
       </c>
       <c r="F44">
         <v>0.10857765</v>
@@ -13033,7 +13036,7 @@
         <v>0.30007125099999998</v>
       </c>
       <c r="E45">
-        <v>1.9110674000000001E-2</v>
+        <v>1.9176444000000001E-2</v>
       </c>
       <c r="F45">
         <v>0.12915310899999999</v>
@@ -13059,7 +13062,7 @@
         <v>0.39993976599999997</v>
       </c>
       <c r="E46">
-        <v>2.7369943000000001E-2</v>
+        <v>4.5705333000000001E-2</v>
       </c>
       <c r="F46">
         <v>9.7766817000000006E-2</v>
@@ -13085,7 +13088,7 @@
         <v>0.50044513199999996</v>
       </c>
       <c r="E47">
-        <v>2.0620128000000001E-2</v>
+        <v>2.2795666999999999E-2</v>
       </c>
       <c r="F47">
         <v>0.103834646</v>
@@ -13111,7 +13114,7 @@
         <v>0.499986655</v>
       </c>
       <c r="E48">
-        <v>2.1720821000000001E-2</v>
+        <v>2.3137000000000001E-2</v>
       </c>
       <c r="F48">
         <v>0.103615651</v>
@@ -13137,7 +13140,7 @@
         <v>0.40017336999999997</v>
       </c>
       <c r="E49">
-        <v>2.0735538000000001E-2</v>
+        <v>1.6598000000000002E-2</v>
       </c>
       <c r="F49">
         <v>9.4777095000000006E-2</v>
@@ -13163,7 +13166,7 @@
         <v>0.40074769799999999</v>
       </c>
       <c r="E50">
-        <v>2.2464746000000001E-2</v>
+        <v>1.9850666999999999E-2</v>
       </c>
       <c r="F50">
         <v>9.4852504000000004E-2</v>
@@ -13189,7 +13192,7 @@
         <v>0.50002069100000002</v>
       </c>
       <c r="E51">
-        <v>2.4334100000000001E-2</v>
+        <v>2.4327778000000001E-2</v>
       </c>
       <c r="F51">
         <v>9.0262732999999998E-2</v>
@@ -13215,7 +13218,7 @@
         <v>0.49970003499999999</v>
       </c>
       <c r="E52">
-        <v>2.3888031000000001E-2</v>
+        <v>2.9573833000000001E-2</v>
       </c>
       <c r="F52">
         <v>0.101849986</v>
@@ -13241,7 +13244,7 @@
         <v>0.49998881699999997</v>
       </c>
       <c r="E53">
-        <v>2.6883537999999998E-2</v>
+        <v>2.3282932999999999E-2</v>
       </c>
       <c r="F53">
         <v>8.8787929000000002E-2</v>
@@ -13267,7 +13270,7 @@
         <v>0.40001579300000001</v>
       </c>
       <c r="E54">
-        <v>2.3810701E-2</v>
+        <v>3.4569500000000003E-2</v>
       </c>
       <c r="F54">
         <v>9.3052383000000002E-2</v>
@@ -13293,7 +13296,7 @@
         <v>0.40002267499999999</v>
       </c>
       <c r="E55">
-        <v>2.5438157999999999E-2</v>
+        <v>2.1106E-2</v>
       </c>
       <c r="F55">
         <v>8.9342075000000007E-2</v>
@@ -13319,7 +13322,7 @@
         <v>0.50012684799999996</v>
       </c>
       <c r="E56">
-        <v>2.6662858000000001E-2</v>
+        <v>2.0743889000000001E-2</v>
       </c>
       <c r="F56">
         <v>8.9674559000000001E-2</v>

--- a/V2.0/settings/data_main.xlsx
+++ b/V2.0/settings/data_main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Projekte\MA-Model_2\V2.0\settings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iagr9\Projekte\MA\MA-Model_2\V2.0\settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AD5B08-6594-4397-9751-6C4FDCE29170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465784A3-1C29-40C1-B000-A00B5EA2EA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="21">
   <si>
     <t>exp</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>lambda</t>
-  </si>
-  <si>
-    <t>h_dis_max</t>
   </si>
   <si>
     <t>2mmol_21C</t>
@@ -2444,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>8.0239500000000002E-4</v>
@@ -2470,7 +2467,7 @@
         <v>0.499859416</v>
       </c>
       <c r="E2">
-        <v>1.8851822000000001E-2</v>
+        <v>2.1230160000000001E-2</v>
       </c>
       <c r="F2">
         <v>0.10280117799999999</v>
@@ -2484,7 +2481,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>6.91448E-4</v>
@@ -2496,7 +2493,7 @@
         <v>0.50028585699999994</v>
       </c>
       <c r="E3">
-        <v>1.3759564E-2</v>
+        <v>1.3507819000000001E-2</v>
       </c>
       <c r="F3">
         <v>0.10897448</v>
@@ -2510,7 +2507,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>5.95906E-4</v>
@@ -2522,7 +2519,7 @@
         <v>0.49989870199999997</v>
       </c>
       <c r="E4">
-        <v>1.88165E-2</v>
+        <v>2.9982749999999999E-2</v>
       </c>
       <c r="F4">
         <v>0.105020287</v>
@@ -2536,7 +2533,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>6.2088699999999998E-4</v>
@@ -2548,7 +2545,7 @@
         <v>0.39951593400000002</v>
       </c>
       <c r="E5">
-        <v>1.9607932000000002E-2</v>
+        <v>3.2247999999999999E-2</v>
       </c>
       <c r="F5">
         <v>0.101170475</v>
@@ -2562,7 +2559,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>5.9944000000000002E-4</v>
@@ -2574,7 +2571,7 @@
         <v>0.40006547100000001</v>
       </c>
       <c r="E6">
-        <v>2.4784075999999999E-2</v>
+        <v>2.9244124999999999E-2</v>
       </c>
       <c r="F6">
         <v>9.7689174000000004E-2</v>
@@ -2588,7 +2585,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>6.1677100000000001E-4</v>
@@ -2600,7 +2597,7 @@
         <v>0.40038251800000002</v>
       </c>
       <c r="E7">
-        <v>2.4416123000000001E-2</v>
+        <v>2.2417833000000002E-2</v>
       </c>
       <c r="F7">
         <v>0.10059602300000001</v>
@@ -2614,7 +2611,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>5.9561800000000002E-4</v>
@@ -2626,7 +2623,7 @@
         <v>0.30056323600000001</v>
       </c>
       <c r="E8">
-        <v>2.3324444999999999E-2</v>
+        <v>2.6593250999999998E-2</v>
       </c>
       <c r="F8">
         <v>0.10011885500000001</v>
@@ -2640,7 +2637,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>5.7893599999999995E-4</v>
@@ -2652,7 +2649,7 @@
         <v>0.29840094900000003</v>
       </c>
       <c r="E9">
-        <v>2.4321518E-2</v>
+        <v>3.2670375000000001E-2</v>
       </c>
       <c r="F9">
         <v>9.9362308999999996E-2</v>
@@ -2666,7 +2663,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>4.9265500000000005E-4</v>
@@ -2678,7 +2675,7 @@
         <v>0.29859516600000002</v>
       </c>
       <c r="E10">
-        <v>1.9255773E-2</v>
+        <v>2.7105875000000001E-2</v>
       </c>
       <c r="F10">
         <v>0.10421707400000001</v>
@@ -2692,7 +2689,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>9.1292700000000001E-4</v>
@@ -2704,7 +2701,7 @@
         <v>0.50044513199999996</v>
       </c>
       <c r="E11">
-        <v>2.0620128000000001E-2</v>
+        <v>1.7934950000000002E-2</v>
       </c>
       <c r="F11">
         <v>0.103834646</v>
@@ -2718,7 +2715,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>9.8825999999999992E-4</v>
@@ -2730,7 +2727,7 @@
         <v>0.50003061599999998</v>
       </c>
       <c r="E12">
-        <v>1.7689674999999998E-2</v>
+        <v>1.5783320999999999E-2</v>
       </c>
       <c r="F12">
         <v>0.105810825</v>
@@ -2744,7 +2741,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>9.4360899999999998E-4</v>
@@ -2756,7 +2753,7 @@
         <v>0.499986655</v>
       </c>
       <c r="E13">
-        <v>2.1720821000000001E-2</v>
+        <v>1.8001669000000001E-2</v>
       </c>
       <c r="F13">
         <v>0.103615651</v>
@@ -2770,7 +2767,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>7.7894200000000002E-4</v>
@@ -2782,7 +2779,7 @@
         <v>0.39986995600000003</v>
       </c>
       <c r="E14">
-        <v>2.3848424E-2</v>
+        <v>3.5990666999999997E-2</v>
       </c>
       <c r="F14">
         <v>9.8667576000000007E-2</v>
@@ -2796,7 +2793,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>7.8108599999999995E-4</v>
@@ -2808,7 +2805,7 @@
         <v>0.400039439</v>
       </c>
       <c r="E15">
-        <v>2.7791891999999999E-2</v>
+        <v>3.6748999999999997E-2</v>
       </c>
       <c r="F15">
         <v>9.5854441999999998E-2</v>
@@ -2822,7 +2819,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>7.4180700000000003E-4</v>
@@ -2834,7 +2831,7 @@
         <v>0.39993976599999997</v>
       </c>
       <c r="E16">
-        <v>2.7369943000000001E-2</v>
+        <v>3.4538167000000002E-2</v>
       </c>
       <c r="F16">
         <v>9.7766817000000006E-2</v>
@@ -2848,7 +2845,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>6.3737199999999998E-4</v>
@@ -2860,7 +2857,7 @@
         <v>0.29994249899999997</v>
       </c>
       <c r="E17">
-        <v>2.6047677000000002E-2</v>
+        <v>3.5846000000000003E-2</v>
       </c>
       <c r="F17">
         <v>0.10857765</v>
@@ -2874,7 +2871,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>6.3181200000000004E-4</v>
@@ -2886,7 +2883,7 @@
         <v>0.30004935199999999</v>
       </c>
       <c r="E18">
-        <v>4.0719331999999997E-2</v>
+        <v>4.6222433E-2</v>
       </c>
       <c r="F18">
         <v>0.11202986400000001</v>
@@ -2900,7 +2897,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>5.6106099999999996E-4</v>
@@ -2912,7 +2909,7 @@
         <v>0.29996400200000001</v>
       </c>
       <c r="E19">
-        <v>3.9184578999999997E-2</v>
+        <v>2.1847999999999999E-2</v>
       </c>
       <c r="F19">
         <v>0.118530145</v>
@@ -2926,7 +2923,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>8.0128199999999995E-4</v>
@@ -2938,7 +2935,7 @@
         <v>0.49970003499999999</v>
       </c>
       <c r="E20">
-        <v>2.3888031000000001E-2</v>
+        <v>2.58175E-2</v>
       </c>
       <c r="F20">
         <v>0.101849986</v>
@@ -2952,7 +2949,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21">
         <v>8.1002600000000004E-4</v>
@@ -2964,7 +2961,7 @@
         <v>0.499961184</v>
       </c>
       <c r="E21">
-        <v>2.9039611999999999E-2</v>
+        <v>3.2184616999999999E-2</v>
       </c>
       <c r="F21">
         <v>0.100430336</v>
@@ -2978,7 +2975,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22">
         <v>7.8814599999999999E-4</v>
@@ -2990,7 +2987,7 @@
         <v>0.49996919899999998</v>
       </c>
       <c r="E22">
-        <v>2.8992381000000001E-2</v>
+        <v>3.1879774999999999E-2</v>
       </c>
       <c r="F22">
         <v>0.10043384299999999</v>
@@ -3004,7 +3001,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23">
         <v>7.1302300000000002E-4</v>
@@ -3016,7 +3013,7 @@
         <v>0.39980531400000002</v>
       </c>
       <c r="E23">
-        <v>2.5204135999999999E-2</v>
+        <v>3.5233417000000003E-2</v>
       </c>
       <c r="F23">
         <v>0.10164448500000001</v>
@@ -3030,7 +3027,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24">
         <v>6.9510100000000005E-4</v>
@@ -3042,7 +3039,7 @@
         <v>0.40003263300000003</v>
       </c>
       <c r="E24">
-        <v>3.1842178999999998E-2</v>
+        <v>4.6955999999999998E-2</v>
       </c>
       <c r="F24">
         <v>9.9360454000000001E-2</v>
@@ -3056,7 +3053,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25">
         <v>7.0127399999999999E-4</v>
@@ -3068,7 +3065,7 @@
         <v>0.40519286300000001</v>
       </c>
       <c r="E25">
-        <v>3.2997344999999997E-2</v>
+        <v>4.4401749999999997E-2</v>
       </c>
       <c r="F25">
         <v>9.6816929999999995E-2</v>
@@ -3082,7 +3079,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26">
         <v>7.3645500000000001E-4</v>
@@ -3094,7 +3091,7 @@
         <v>0.499857828</v>
       </c>
       <c r="E26">
-        <v>1.7182822E-2</v>
+        <v>1.7695522000000002E-2</v>
       </c>
       <c r="F26">
         <v>9.4951860999999999E-2</v>
@@ -3108,7 +3105,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27">
         <v>7.2969899999999999E-4</v>
@@ -3120,7 +3117,7 @@
         <v>0.49970384000000001</v>
       </c>
       <c r="E27">
-        <v>1.8852822000000002E-2</v>
+        <v>2.0651935E-2</v>
       </c>
       <c r="F27">
         <v>9.4908577999999993E-2</v>
@@ -3134,7 +3131,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28">
         <v>6.9667700000000004E-4</v>
@@ -3146,7 +3143,7 @@
         <v>0.49938961599999998</v>
       </c>
       <c r="E28">
-        <v>2.2076011E-2</v>
+        <v>2.2757346000000001E-2</v>
       </c>
       <c r="F28">
         <v>9.4442905999999993E-2</v>
@@ -3160,7 +3157,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>6.4236199999999995E-4</v>
@@ -3172,7 +3169,7 @@
         <v>0.40010973</v>
       </c>
       <c r="E29">
-        <v>1.7214279999999998E-2</v>
+        <v>2.0670075E-2</v>
       </c>
       <c r="F29">
         <v>9.6245902999999994E-2</v>
@@ -3186,7 +3183,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30">
         <v>6.8012400000000005E-4</v>
@@ -3198,7 +3195,7 @@
         <v>0.39954061600000002</v>
       </c>
       <c r="E30">
-        <v>1.9736321000000001E-2</v>
+        <v>2.0283136E-2</v>
       </c>
       <c r="F30">
         <v>9.6185945999999994E-2</v>
@@ -3212,7 +3209,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31">
         <v>5.9216200000000003E-4</v>
@@ -3224,7 +3221,7 @@
         <v>0.40100802200000002</v>
       </c>
       <c r="E31">
-        <v>2.0059832E-2</v>
+        <v>1.9446093000000001E-2</v>
       </c>
       <c r="F31">
         <v>9.6083401999999998E-2</v>
@@ -3238,7 +3235,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>5.9390400000000002E-4</v>
@@ -3250,7 +3247,7 @@
         <v>0.30137491399999999</v>
       </c>
       <c r="E32">
-        <v>1.7153650999999999E-2</v>
+        <v>1.8841891999999999E-2</v>
       </c>
       <c r="F32">
         <v>9.7575882000000003E-2</v>
@@ -3264,7 +3261,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33">
         <v>5.8364699999999996E-4</v>
@@ -3276,7 +3273,7 @@
         <v>0.29930047500000001</v>
       </c>
       <c r="E33">
-        <v>1.9624798999999998E-2</v>
+        <v>2.1772928E-2</v>
       </c>
       <c r="F33">
         <v>9.6670351000000002E-2</v>
@@ -3290,7 +3287,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>5.1002800000000004E-4</v>
@@ -3302,7 +3299,7 @@
         <v>0.30168805199999998</v>
       </c>
       <c r="E34">
-        <v>1.704373E-2</v>
+        <v>1.7340412999999999E-2</v>
       </c>
       <c r="F34">
         <v>9.6635620000000005E-2</v>
@@ -3316,7 +3313,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>8.0508499999999998E-4</v>
@@ -3328,7 +3325,7 @@
         <v>0.50017696099999998</v>
       </c>
       <c r="E35">
-        <v>2.3555221000000001E-2</v>
+        <v>2.3462375000000001E-2</v>
       </c>
       <c r="F35">
         <v>9.2545870000000002E-2</v>
@@ -3342,7 +3339,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>7.6724599999999997E-4</v>
@@ -3354,7 +3351,7 @@
         <v>0.49995857100000002</v>
       </c>
       <c r="E36">
-        <v>2.3109550999999999E-2</v>
+        <v>2.4965339E-2</v>
       </c>
       <c r="F36">
         <v>9.2378648999999993E-2</v>
@@ -3368,7 +3365,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>7.0617800000000001E-4</v>
@@ -3380,7 +3377,7 @@
         <v>0.49990232400000001</v>
       </c>
       <c r="E37">
-        <v>2.4668497000000001E-2</v>
+        <v>2.6471788999999999E-2</v>
       </c>
       <c r="F37">
         <v>9.1588153000000005E-2</v>
@@ -3394,7 +3391,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>6.90491E-4</v>
@@ -3406,7 +3403,7 @@
         <v>0.39997470200000002</v>
       </c>
       <c r="E38">
-        <v>2.0796281999999999E-2</v>
+        <v>2.2536453000000001E-2</v>
       </c>
       <c r="F38">
         <v>9.4995364999999998E-2</v>
@@ -3420,7 +3417,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>6.6872600000000002E-4</v>
@@ -3432,7 +3429,7 @@
         <v>0.40031847300000001</v>
       </c>
       <c r="E39">
-        <v>2.0327868999999998E-2</v>
+        <v>2.0575774000000002E-2</v>
       </c>
       <c r="F39">
         <v>9.4793715000000001E-2</v>
@@ -3446,7 +3443,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>6.0886200000000005E-4</v>
@@ -3458,7 +3455,7 @@
         <v>0.40016497499999998</v>
       </c>
       <c r="E40">
-        <v>2.1022189E-2</v>
+        <v>1.9551636000000001E-2</v>
       </c>
       <c r="F40">
         <v>9.3850811000000006E-2</v>
@@ -3472,7 +3469,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41">
         <v>5.8638600000000005E-4</v>
@@ -3484,7 +3481,7 @@
         <v>0.299993344</v>
       </c>
       <c r="E41">
-        <v>1.8880043999999999E-2</v>
+        <v>2.0140444E-2</v>
       </c>
       <c r="F41">
         <v>0.106182606</v>
@@ -3498,7 +3495,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42">
         <v>5.8743599999999999E-4</v>
@@ -3510,7 +3507,7 @@
         <v>0.300089995</v>
       </c>
       <c r="E42">
-        <v>1.7454754999999999E-2</v>
+        <v>1.6236285999999999E-2</v>
       </c>
       <c r="F42">
         <v>0.117572011</v>
@@ -3524,7 +3521,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43">
         <v>5.2147200000000004E-4</v>
@@ -3536,7 +3533,7 @@
         <v>0.300294854</v>
       </c>
       <c r="E43">
-        <v>1.8037182999999998E-2</v>
+        <v>1.6603903E-2</v>
       </c>
       <c r="F43">
         <v>0.126666367</v>
@@ -3550,7 +3547,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44">
         <v>7.3430900000000005E-4</v>
@@ -3562,7 +3559,7 @@
         <v>0.50012684799999996</v>
       </c>
       <c r="E44">
-        <v>2.6662858000000001E-2</v>
+        <v>2.9320511E-2</v>
       </c>
       <c r="F44">
         <v>8.9674559000000001E-2</v>
@@ -3576,7 +3573,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45">
         <v>6.9824100000000005E-4</v>
@@ -3588,7 +3585,7 @@
         <v>0.50011176499999999</v>
       </c>
       <c r="E45">
-        <v>2.5932647999999999E-2</v>
+        <v>2.84383E-2</v>
       </c>
       <c r="F45">
         <v>8.9625669000000005E-2</v>
@@ -3602,7 +3599,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46">
         <v>6.8666599999999995E-4</v>
@@ -3614,7 +3611,7 @@
         <v>0.50005669699999999</v>
       </c>
       <c r="E46">
-        <v>2.5288621000000001E-2</v>
+        <v>2.5482570999999999E-2</v>
       </c>
       <c r="F46">
         <v>8.9115579E-2</v>
@@ -3628,7 +3625,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>6.0317599999999997E-4</v>
@@ -3640,7 +3637,7 @@
         <v>0.39983770499999999</v>
       </c>
       <c r="E47">
-        <v>2.3257283E-2</v>
+        <v>2.0828599999999999E-2</v>
       </c>
       <c r="F47">
         <v>9.2949599999999993E-2</v>
@@ -3654,7 +3651,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48">
         <v>6.0375999999999995E-4</v>
@@ -3666,7 +3663,7 @@
         <v>0.39993699799999999</v>
       </c>
       <c r="E48">
-        <v>2.3698462999999999E-2</v>
+        <v>2.4302250000000001E-2</v>
       </c>
       <c r="F48">
         <v>9.1868320000000003E-2</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49">
         <v>7.2423300000000002E-4</v>
@@ -3692,7 +3689,7 @@
         <v>0.50497902900000002</v>
       </c>
       <c r="E49">
-        <v>2.2361435999999998E-2</v>
+        <v>2.2087249999999999E-2</v>
       </c>
       <c r="F49">
         <v>9.4290947E-2</v>
@@ -3706,7 +3703,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50">
         <v>8.1175500000000005E-4</v>
@@ -3718,7 +3715,7 @@
         <v>0.50008189700000005</v>
       </c>
       <c r="E50">
-        <v>2.5173661999999999E-2</v>
+        <v>2.8558812999999999E-2</v>
       </c>
       <c r="F50">
         <v>9.1915671000000004E-2</v>
@@ -3732,7 +3729,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51">
         <v>7.9663900000000003E-4</v>
@@ -3744,7 +3741,7 @@
         <v>0.50001988399999997</v>
       </c>
       <c r="E51">
-        <v>2.4801119E-2</v>
+        <v>2.7923136000000001E-2</v>
       </c>
       <c r="F51">
         <v>9.2305313999999999E-2</v>
@@ -3758,7 +3755,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52">
         <v>7.5900900000000005E-4</v>
@@ -3770,7 +3767,7 @@
         <v>0.500010124</v>
       </c>
       <c r="E52">
-        <v>2.4511805000000001E-2</v>
+        <v>2.4887511000000001E-2</v>
       </c>
       <c r="F52">
         <v>9.1771162000000003E-2</v>
@@ -3784,7 +3781,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53">
         <v>7.5096099999999997E-4</v>
@@ -3796,7 +3793,7 @@
         <v>0.49999859899999999</v>
       </c>
       <c r="E53">
-        <v>2.4870665E-2</v>
+        <v>2.7336375999999999E-2</v>
       </c>
       <c r="F53">
         <v>9.0949002000000001E-2</v>
@@ -3810,7 +3807,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54">
         <v>7.63323E-4</v>
@@ -3822,7 +3819,7 @@
         <v>0.50006198700000004</v>
       </c>
       <c r="E54">
-        <v>2.5023548E-2</v>
+        <v>2.5250000000000002E-2</v>
       </c>
       <c r="F54">
         <v>9.1166435000000004E-2</v>
@@ -3836,7 +3833,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55">
         <v>7.2370699999999997E-4</v>
@@ -3848,7 +3845,7 @@
         <v>0.50002069100000002</v>
       </c>
       <c r="E55">
-        <v>2.4334100000000001E-2</v>
+        <v>2.9699555999999998E-2</v>
       </c>
       <c r="F55">
         <v>9.0262732999999998E-2</v>
@@ -3862,7 +3859,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56">
         <v>7.0107399999999999E-4</v>
@@ -3874,7 +3871,7 @@
         <v>0.49981435699999999</v>
       </c>
       <c r="E56">
-        <v>2.5514657E-2</v>
+        <v>2.8491307E-2</v>
       </c>
       <c r="F56">
         <v>8.9684443000000003E-2</v>
@@ -3888,7 +3885,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57">
         <v>7.1206199999999996E-4</v>
@@ -3900,7 +3897,7 @@
         <v>0.50008270300000002</v>
       </c>
       <c r="E57">
-        <v>2.5693543999999999E-2</v>
+        <v>2.7960022000000001E-2</v>
       </c>
       <c r="F57">
         <v>8.9956089000000003E-2</v>
@@ -3914,7 +3911,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B58">
         <v>6.9931300000000002E-4</v>
@@ -3926,7 +3923,7 @@
         <v>0.49992769599999998</v>
       </c>
       <c r="E58">
-        <v>2.5077159000000002E-2</v>
+        <v>2.7482230999999999E-2</v>
       </c>
       <c r="F58">
         <v>8.9725541000000006E-2</v>
@@ -3940,7 +3937,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B59">
         <v>7.7304999999999995E-4</v>
@@ -3952,7 +3949,7 @@
         <v>0.50006005200000003</v>
       </c>
       <c r="E59">
-        <v>2.6129478000000001E-2</v>
+        <v>2.6879742000000002E-2</v>
       </c>
       <c r="F59">
         <v>9.1026439000000001E-2</v>
@@ -3966,7 +3963,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60">
         <v>7.7200999999999995E-4</v>
@@ -3978,7 +3975,7 @@
         <v>0.5000675</v>
       </c>
       <c r="E60">
-        <v>2.5281590999999999E-2</v>
+        <v>2.7285421000000001E-2</v>
       </c>
       <c r="F60">
         <v>9.0902575999999999E-2</v>
@@ -3992,7 +3989,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61">
         <v>7.2866900000000004E-4</v>
@@ -4004,7 +4001,7 @@
         <v>0.50000592099999996</v>
       </c>
       <c r="E61">
-        <v>2.4421463000000001E-2</v>
+        <v>2.5060091999999999E-2</v>
       </c>
       <c r="F61">
         <v>9.0799087000000001E-2</v>
@@ -4018,7 +4015,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>7.7559000000000005E-4</v>
@@ -4030,7 +4027,7 @@
         <v>0.49981272100000002</v>
       </c>
       <c r="E62">
-        <v>2.4078116E-2</v>
+        <v>2.5000455000000001E-2</v>
       </c>
       <c r="F62">
         <v>9.1868149999999996E-2</v>
@@ -4044,7 +4041,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>7.6392500000000004E-4</v>
@@ -4056,7 +4053,7 @@
         <v>0.50003272799999998</v>
       </c>
       <c r="E63">
-        <v>2.4252689000000001E-2</v>
+        <v>2.4585493999999999E-2</v>
       </c>
       <c r="F63">
         <v>9.1987243999999996E-2</v>
@@ -4070,7 +4067,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>7.2654800000000004E-4</v>
@@ -4082,7 +4079,7 @@
         <v>0.49692148400000002</v>
       </c>
       <c r="E64">
-        <v>2.3973168999999999E-2</v>
+        <v>2.5115571E-2</v>
       </c>
       <c r="F64">
         <v>9.1711663999999998E-2</v>
@@ -4096,7 +4093,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65">
         <v>7.2222900000000001E-4</v>
@@ -4108,7 +4105,7 @@
         <v>0.499880084</v>
       </c>
       <c r="E65">
-        <v>1.7030178E-2</v>
+        <v>1.6913991E-2</v>
       </c>
       <c r="F65">
         <v>9.4883205999999998E-2</v>
@@ -4122,7 +4119,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66">
         <v>7.1244500000000003E-4</v>
@@ -4134,7 +4131,7 @@
         <v>0.49991358299999999</v>
       </c>
       <c r="E66">
-        <v>1.8550810000000001E-2</v>
+        <v>1.876069E-2</v>
       </c>
       <c r="F66">
         <v>9.4884389999999999E-2</v>
@@ -4148,7 +4145,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B67">
         <v>7.1245100000000001E-4</v>
@@ -4160,7 +4157,7 @@
         <v>0.50002289600000005</v>
       </c>
       <c r="E67">
-        <v>2.3203320999999999E-2</v>
+        <v>2.2538355999999999E-2</v>
       </c>
       <c r="F67">
         <v>9.4996779000000003E-2</v>
@@ -4174,7 +4171,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B68">
         <v>7.3421300000000005E-4</v>
@@ -4186,7 +4183,7 @@
         <v>0.49965712499999998</v>
       </c>
       <c r="E68">
-        <v>2.2879033999999999E-2</v>
+        <v>2.1872315E-2</v>
       </c>
       <c r="F68">
         <v>9.4441699000000004E-2</v>
@@ -4200,7 +4197,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B69">
         <v>7.4564200000000003E-4</v>
@@ -4212,7 +4209,7 @@
         <v>0.49991707099999999</v>
       </c>
       <c r="E69">
-        <v>2.1350562999999999E-2</v>
+        <v>2.0420974000000001E-2</v>
       </c>
       <c r="F69">
         <v>9.4204745000000006E-2</v>
@@ -4226,7 +4223,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B70">
         <v>7.5361500000000001E-4</v>
@@ -4238,7 +4235,7 @@
         <v>0.50001522700000001</v>
       </c>
       <c r="E70">
-        <v>1.9893559000000002E-2</v>
+        <v>1.8111566999999999E-2</v>
       </c>
       <c r="F70">
         <v>9.5239508E-2</v>
@@ -4252,7 +4249,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71">
         <v>6.6505100000000005E-4</v>
@@ -4264,7 +4261,7 @@
         <v>0.399215879</v>
       </c>
       <c r="E71">
-        <v>1.9550339999999999E-2</v>
+        <v>1.7216344000000001E-2</v>
       </c>
       <c r="F71">
         <v>9.5698076000000007E-2</v>
@@ -4278,7 +4275,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72">
         <v>6.3372099999999996E-4</v>
@@ -4290,7 +4287,7 @@
         <v>0.39906686200000002</v>
       </c>
       <c r="E72">
-        <v>1.9562685999999999E-2</v>
+        <v>1.8789934000000001E-2</v>
       </c>
       <c r="F72">
         <v>9.6278714000000001E-2</v>
@@ -4304,7 +4301,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B73">
         <v>6.1875899999999998E-4</v>
@@ -4316,7 +4313,7 @@
         <v>0.39989831300000001</v>
       </c>
       <c r="E73">
-        <v>2.1604254999999999E-2</v>
+        <v>2.2025092999999999E-2</v>
       </c>
       <c r="F73">
         <v>9.5364194999999999E-2</v>
@@ -4330,7 +4327,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B74">
         <v>6.2012899999999997E-4</v>
@@ -4342,7 +4339,7 @@
         <v>0.39928821199999998</v>
       </c>
       <c r="E74">
-        <v>2.2378535000000001E-2</v>
+        <v>2.1280207999999998E-2</v>
       </c>
       <c r="F74">
         <v>9.5441264999999997E-2</v>
@@ -4356,7 +4353,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B75">
         <v>6.5113400000000004E-4</v>
@@ -4368,7 +4365,7 @@
         <v>0.39950756500000001</v>
       </c>
       <c r="E75">
-        <v>2.3494683999999998E-2</v>
+        <v>2.1074203999999999E-2</v>
       </c>
       <c r="F75">
         <v>9.5445799999999997E-2</v>
@@ -4382,7 +4379,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B76">
         <v>6.6688800000000003E-4</v>
@@ -4394,7 +4391,7 @@
         <v>0.398774242</v>
       </c>
       <c r="E76">
-        <v>2.1653974999999999E-2</v>
+        <v>2.306619E-2</v>
       </c>
       <c r="F76">
         <v>9.5102975000000006E-2</v>
@@ -4408,7 +4405,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B77">
         <v>5.7892299999999996E-4</v>
@@ -4420,7 +4417,7 @@
         <v>0.29963859100000001</v>
       </c>
       <c r="E77">
-        <v>1.6896813E-2</v>
+        <v>1.8974015E-2</v>
       </c>
       <c r="F77">
         <v>9.7863836999999995E-2</v>
@@ -4434,7 +4431,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B78">
         <v>5.6844399999999998E-4</v>
@@ -4446,7 +4443,7 @@
         <v>0.29996158899999997</v>
       </c>
       <c r="E78">
-        <v>1.9367124999999999E-2</v>
+        <v>1.9462601999999999E-2</v>
       </c>
       <c r="F78">
         <v>9.7314092000000005E-2</v>
@@ -4460,7 +4457,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B79">
         <v>5.5183900000000004E-4</v>
@@ -4472,7 +4469,7 @@
         <v>0.30406831400000001</v>
       </c>
       <c r="E79">
-        <v>1.9188990999999999E-2</v>
+        <v>2.0564747000000001E-2</v>
       </c>
       <c r="F79">
         <v>9.7307075000000007E-2</v>
@@ -4486,7 +4483,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B80">
         <v>5.2785099999999997E-4</v>
@@ -4498,7 +4495,7 @@
         <v>0.30089281899999998</v>
       </c>
       <c r="E80">
-        <v>1.8193810000000001E-2</v>
+        <v>1.9941581E-2</v>
       </c>
       <c r="F80">
         <v>9.7334873000000002E-2</v>
@@ -4512,7 +4509,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B81">
         <v>5.4509199999999995E-4</v>
@@ -4524,7 +4521,7 @@
         <v>0.29742201299999999</v>
       </c>
       <c r="E81">
-        <v>2.0483014000000001E-2</v>
+        <v>2.2126839999999998E-2</v>
       </c>
       <c r="F81">
         <v>9.5757468999999998E-2</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B82">
         <v>5.5842000000000001E-4</v>
@@ -4550,7 +4547,7 @@
         <v>0.299342948</v>
       </c>
       <c r="E82">
-        <v>2.0471765999999999E-2</v>
+        <v>2.1342367000000001E-2</v>
       </c>
       <c r="F82">
         <v>9.5767783999999995E-2</v>
@@ -4564,7 +4561,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B83">
         <v>8.1662800000000002E-4</v>
@@ -4576,7 +4573,7 @@
         <v>0.50025813699999999</v>
       </c>
       <c r="E83">
-        <v>2.6577284999999999E-2</v>
+        <v>2.9359783E-2</v>
       </c>
       <c r="F83">
         <v>9.2475197999999995E-2</v>
@@ -4590,7 +4587,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B84">
         <v>8.2480499999999996E-4</v>
@@ -4602,7 +4599,7 @@
         <v>0.50018586899999995</v>
       </c>
       <c r="E84">
-        <v>2.6404024000000002E-2</v>
+        <v>2.8518803999999998E-2</v>
       </c>
       <c r="F84">
         <v>9.2061076000000006E-2</v>
@@ -4616,7 +4613,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B85">
         <v>7.6000999999999998E-4</v>
@@ -4628,7 +4625,7 @@
         <v>0.50004636899999999</v>
       </c>
       <c r="E85">
-        <v>2.4838368E-2</v>
+        <v>2.7907983000000001E-2</v>
       </c>
       <c r="F85">
         <v>9.2153499E-2</v>
@@ -4642,7 +4639,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B86">
         <v>7.4356499999999996E-4</v>
@@ -4654,7 +4651,7 @@
         <v>0.50049595099999999</v>
       </c>
       <c r="E86">
-        <v>2.549999E-2</v>
+        <v>2.6673499999999999E-2</v>
       </c>
       <c r="F86">
         <v>9.1281444000000003E-2</v>
@@ -4668,7 +4665,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B87">
         <v>7.9224700000000005E-4</v>
@@ -4680,7 +4677,7 @@
         <v>0.500037642</v>
       </c>
       <c r="E87">
-        <v>2.6181453E-2</v>
+        <v>2.7468919000000001E-2</v>
       </c>
       <c r="F87">
         <v>9.1722809000000002E-2</v>
@@ -4694,7 +4691,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B88">
         <v>8.5975099999999996E-4</v>
@@ -4706,7 +4703,7 @@
         <v>0.50000099099999995</v>
       </c>
       <c r="E88">
-        <v>2.6915963000000001E-2</v>
+        <v>2.7848810000000002E-2</v>
       </c>
       <c r="F88">
         <v>9.1934420000000003E-2</v>
@@ -4720,7 +4717,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B89">
         <v>7.0235800000000004E-4</v>
@@ -4732,7 +4729,7 @@
         <v>0.40077602200000001</v>
       </c>
       <c r="E89">
-        <v>2.0475185999999999E-2</v>
+        <v>2.3096966E-2</v>
       </c>
       <c r="F89">
         <v>9.5246530999999995E-2</v>
@@ -4746,7 +4743,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B90">
         <v>6.7399699999999996E-4</v>
@@ -4758,7 +4755,7 @@
         <v>0.399699582</v>
       </c>
       <c r="E90">
-        <v>2.1077841999999999E-2</v>
+        <v>2.5790118000000001E-2</v>
       </c>
       <c r="F90">
         <v>9.4840091000000001E-2</v>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B91">
         <v>6.1247500000000002E-4</v>
@@ -4784,7 +4781,7 @@
         <v>0.39970823500000002</v>
       </c>
       <c r="E91">
-        <v>2.0777276000000001E-2</v>
+        <v>2.6694748000000001E-2</v>
       </c>
       <c r="F91">
         <v>9.4596124000000004E-2</v>
@@ -4798,7 +4795,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B92">
         <v>5.9411399999999997E-4</v>
@@ -4810,7 +4807,7 @@
         <v>0.39958102600000001</v>
       </c>
       <c r="E92">
-        <v>2.0836258999999999E-2</v>
+        <v>1.6276200000000001E-2</v>
       </c>
       <c r="F92">
         <v>9.4314624E-2</v>
@@ -4824,7 +4821,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B93">
         <v>6.1466400000000001E-4</v>
@@ -4836,7 +4833,7 @@
         <v>0.40017336999999997</v>
       </c>
       <c r="E93">
-        <v>2.0735538000000001E-2</v>
+        <v>2.2372559E-2</v>
       </c>
       <c r="F93">
         <v>9.4777095000000006E-2</v>
@@ -4850,7 +4847,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B94">
         <v>6.6162899999999995E-4</v>
@@ -4862,7 +4859,7 @@
         <v>0.40074769799999999</v>
       </c>
       <c r="E94">
-        <v>2.2464746000000001E-2</v>
+        <v>2.2298869999999998E-2</v>
       </c>
       <c r="F94">
         <v>9.4852504000000004E-2</v>
@@ -4876,7 +4873,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B95">
         <v>5.9813300000000004E-4</v>
@@ -4888,7 +4885,7 @@
         <v>0.30013885400000001</v>
       </c>
       <c r="E95">
-        <v>1.9020628000000001E-2</v>
+        <v>2.0460501999999998E-2</v>
       </c>
       <c r="F95">
         <v>0.105815622</v>
@@ -4902,7 +4899,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B96">
         <v>5.8159900000000003E-4</v>
@@ -4914,7 +4911,7 @@
         <v>0.30050412700000001</v>
       </c>
       <c r="E96">
-        <v>2.4834759000000001E-2</v>
+        <v>3.3435341E-2</v>
       </c>
       <c r="F96">
         <v>0.11494191300000001</v>
@@ -4928,7 +4925,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B97">
         <v>5.2616900000000005E-4</v>
@@ -4940,7 +4937,7 @@
         <v>0.30007125099999998</v>
       </c>
       <c r="E97">
-        <v>1.9110674000000001E-2</v>
+        <v>1.43962E-2</v>
       </c>
       <c r="F97">
         <v>0.12915310899999999</v>
@@ -4954,7 +4951,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B98">
         <v>5.04985E-4</v>
@@ -4966,7 +4963,7 @@
         <v>0.300041644</v>
       </c>
       <c r="E98">
-        <v>2.1812228999999999E-2</v>
+        <v>2.4023714000000002E-2</v>
       </c>
       <c r="F98">
         <v>0.135209721</v>
@@ -4980,7 +4977,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B99">
         <v>5.1139399999999998E-4</v>
@@ -4992,7 +4989,7 @@
         <v>0.30000299000000002</v>
       </c>
       <c r="E99">
-        <v>2.5789294000000001E-2</v>
+        <v>2.0355875999999998E-2</v>
       </c>
       <c r="F99">
         <v>0.14187197200000001</v>
@@ -5006,7 +5003,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B100">
         <v>5.3669500000000001E-4</v>
@@ -5018,7 +5015,7 @@
         <v>0.30005833100000001</v>
       </c>
       <c r="E100">
-        <v>2.6643176000000001E-2</v>
+        <v>2.4404681000000001E-2</v>
       </c>
       <c r="F100">
         <v>0.14897181500000001</v>
@@ -5032,7 +5029,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B101">
         <v>7.1749599999999998E-4</v>
@@ -5044,7 +5041,7 @@
         <v>0.50050467899999995</v>
       </c>
       <c r="E101">
-        <v>2.8744255E-2</v>
+        <v>2.8163105000000001E-2</v>
       </c>
       <c r="F101">
         <v>8.8546011999999993E-2</v>
@@ -5058,7 +5055,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B102">
         <v>7.0684700000000003E-4</v>
@@ -5070,7 +5067,7 @@
         <v>0.50011482500000004</v>
       </c>
       <c r="E102">
-        <v>2.7856384000000001E-2</v>
+        <v>3.0175171000000001E-2</v>
       </c>
       <c r="F102">
         <v>8.9643099000000004E-2</v>
@@ -5084,7 +5081,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B103">
         <v>6.9391699999999995E-4</v>
@@ -5096,7 +5093,7 @@
         <v>0.49996141900000002</v>
       </c>
       <c r="E103">
-        <v>2.7173981E-2</v>
+        <v>3.3903497999999997E-2</v>
       </c>
       <c r="F103">
         <v>8.9105503000000003E-2</v>
@@ -5110,7 +5107,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B104">
         <v>6.8117199999999996E-4</v>
@@ -5122,7 +5119,7 @@
         <v>0.49998881699999997</v>
       </c>
       <c r="E104">
-        <v>2.6883537999999998E-2</v>
+        <v>3.0178110000000001E-2</v>
       </c>
       <c r="F104">
         <v>8.8787929000000002E-2</v>
@@ -5136,7 +5133,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B105">
         <v>6.7872799999999997E-4</v>
@@ -5148,7 +5145,7 @@
         <v>0.49983905899999997</v>
       </c>
       <c r="E105">
-        <v>2.6575871000000001E-2</v>
+        <v>2.8687727E-2</v>
       </c>
       <c r="F105">
         <v>8.8617395000000002E-2</v>
@@ -5162,7 +5159,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B106">
         <v>7.1950099999999999E-4</v>
@@ -5174,7 +5171,7 @@
         <v>0.50012871199999998</v>
       </c>
       <c r="E106">
-        <v>2.6791129E-2</v>
+        <v>2.8405264E-2</v>
       </c>
       <c r="F106">
         <v>8.9807804000000005E-2</v>
@@ -5188,7 +5185,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B107">
         <v>6.1575900000000001E-4</v>
@@ -5200,7 +5197,7 @@
         <v>0.40001579300000001</v>
       </c>
       <c r="E107">
-        <v>2.3810701E-2</v>
+        <v>3.2579062999999998E-2</v>
       </c>
       <c r="F107">
         <v>9.3052383000000002E-2</v>
@@ -5214,7 +5211,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B108">
         <v>6.0389799999999996E-4</v>
@@ -5226,7 +5223,7 @@
         <v>0.40011335199999998</v>
       </c>
       <c r="E108">
-        <v>2.3536505999999999E-2</v>
+        <v>2.7406429E-2</v>
       </c>
       <c r="F108">
         <v>9.0973494000000002E-2</v>
@@ -5240,7 +5237,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B109">
         <v>5.7284199999999995E-4</v>
@@ -5252,7 +5249,7 @@
         <v>0.40002267499999999</v>
       </c>
       <c r="E109">
-        <v>2.5438157999999999E-2</v>
+        <v>3.3192933000000001E-2</v>
       </c>
       <c r="F109">
         <v>8.9342075000000007E-2</v>
@@ -5266,7 +5263,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B110">
         <v>5.5556900000000001E-4</v>
@@ -5278,7 +5275,7 @@
         <v>0.39995072199999998</v>
       </c>
       <c r="E110">
-        <v>2.5517495000000001E-2</v>
+        <v>3.0516689999999999E-2</v>
       </c>
       <c r="F110">
         <v>8.9309071000000004E-2</v>
@@ -5292,7 +5289,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B111">
         <v>5.6215900000000001E-4</v>
@@ -5304,7 +5301,7 @@
         <v>0.39991206200000001</v>
       </c>
       <c r="E111">
-        <v>2.6224523999999999E-2</v>
+        <v>3.3594800000000001E-2</v>
       </c>
       <c r="F111">
         <v>8.8778441999999999E-2</v>
@@ -5318,7 +5315,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B112">
         <v>5.4408699999999996E-4</v>
@@ -5330,7 +5327,7 @@
         <v>0.29846209099999998</v>
       </c>
       <c r="E112">
-        <v>3.9465617000000001E-2</v>
+        <v>3.6771788E-2</v>
       </c>
       <c r="F112">
         <v>9.1228983E-2</v>
@@ -5344,7 +5341,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B113">
         <v>4.5836E-4</v>
@@ -5356,7 +5353,7 @@
         <v>0.30222506500000001</v>
       </c>
       <c r="E113">
-        <v>4.5065751000000001E-2</v>
+        <v>4.3851583E-2</v>
       </c>
       <c r="F113">
         <v>9.2706983000000007E-2</v>
@@ -5370,7 +5367,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B114">
         <v>3.0230799999999999E-4</v>
@@ -5382,7 +5379,7 @@
         <v>0.296834975</v>
       </c>
       <c r="E114">
-        <v>3.5464901E-2</v>
+        <v>3.5984049999999997E-2</v>
       </c>
       <c r="F114">
         <v>9.9475516E-2</v>
@@ -5396,7 +5393,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B115">
         <v>2.0462099999999999E-4</v>
@@ -5408,7 +5405,7 @@
         <v>0.29701893400000001</v>
       </c>
       <c r="E115">
-        <v>3.6502927999999997E-2</v>
+        <v>3.6558697000000001E-2</v>
       </c>
       <c r="F115">
         <v>9.6633421999999997E-2</v>
@@ -5422,7 +5419,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B116">
         <v>5.2193699999999999E-4</v>
@@ -5434,7 +5431,7 @@
         <v>0.40036071000000001</v>
       </c>
       <c r="E116">
-        <v>3.5911619999999998E-2</v>
+        <v>3.2603696000000001E-2</v>
       </c>
       <c r="F116">
         <v>8.9501396999999996E-2</v>
@@ -5448,7 +5445,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B117">
         <v>4.4927699999999999E-4</v>
@@ -5460,7 +5457,7 @@
         <v>0.399764919</v>
       </c>
       <c r="E117">
-        <v>3.8463404E-2</v>
+        <v>3.2396071999999998E-2</v>
       </c>
       <c r="F117">
         <v>9.5001253999999993E-2</v>
@@ -5474,7 +5471,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118">
         <v>2.8546399999999998E-4</v>
@@ -5486,7 +5483,7 @@
         <v>0.399049243</v>
       </c>
       <c r="E118">
-        <v>3.5169270000000002E-2</v>
+        <v>3.0683358000000001E-2</v>
       </c>
       <c r="F118">
         <v>0.106014196</v>
@@ -5500,7 +5497,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B119">
         <v>2.4194099999999999E-4</v>
@@ -5512,7 +5509,7 @@
         <v>0.40002338700000001</v>
       </c>
       <c r="E119">
-        <v>6.6916982E-2</v>
+        <v>2.9894546000000001E-2</v>
       </c>
       <c r="F119">
         <v>0.106790285</v>
@@ -5526,7 +5523,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B120">
         <v>6.5725699999999996E-4</v>
@@ -5538,7 +5535,7 @@
         <v>0.50333939500000002</v>
       </c>
       <c r="E120">
-        <v>2.8484735000000001E-2</v>
+        <v>2.5148977999999999E-2</v>
       </c>
       <c r="F120">
         <v>9.2660582000000005E-2</v>
@@ -5552,7 +5549,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B121">
         <v>5.2808399999999995E-4</v>
@@ -5564,7 +5561,7 @@
         <v>0.50035887499999998</v>
       </c>
       <c r="E121">
-        <v>4.2228937000000001E-2</v>
+        <v>3.6052422000000001E-2</v>
       </c>
       <c r="F121">
         <v>9.9396029999999996E-2</v>
@@ -5578,7 +5575,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B122">
         <v>3.5915099999999999E-4</v>
@@ -5590,7 +5587,7 @@
         <v>0.49840438399999998</v>
       </c>
       <c r="E122">
-        <v>3.5165189999999999E-2</v>
+        <v>3.4000928E-2</v>
       </c>
       <c r="F122">
         <v>0.108600243</v>
@@ -5604,7 +5601,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B123">
         <v>3.1127999999999999E-4</v>
@@ -5616,7 +5613,7 @@
         <v>0.49988101000000001</v>
       </c>
       <c r="E123">
-        <v>3.8919571E-2</v>
+        <v>3.2927250999999998E-2</v>
       </c>
       <c r="F123">
         <v>0.10772396300000001</v>
@@ -5630,7 +5627,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B124">
         <v>4.7841700000000002E-4</v>
@@ -5642,7 +5639,7 @@
         <v>0.30053032600000001</v>
       </c>
       <c r="E124">
-        <v>4.2801569999999997E-2</v>
+        <v>3.6170202999999998E-2</v>
       </c>
       <c r="F124">
         <v>0.103238596</v>
@@ -5656,7 +5653,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B125">
         <v>4.9956000000000002E-4</v>
@@ -5668,7 +5665,7 @@
         <v>0.29977596000000001</v>
       </c>
       <c r="E125">
-        <v>4.0141706999999999E-2</v>
+        <v>3.4628844999999998E-2</v>
       </c>
       <c r="F125">
         <v>0.102442293</v>
@@ -5682,7 +5679,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B126">
         <v>3.2126799999999999E-4</v>
@@ -5694,7 +5691,7 @@
         <v>0.30118348099999998</v>
       </c>
       <c r="E126">
-        <v>3.4455592E-2</v>
+        <v>3.0989666999999999E-2</v>
       </c>
       <c r="F126">
         <v>0.10929739199999999</v>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B127">
         <v>2.7020599999999999E-4</v>
@@ -5720,7 +5717,7 @@
         <v>0.29982659</v>
       </c>
       <c r="E127">
-        <v>4.1210475000000003E-2</v>
+        <v>3.2594555999999997E-2</v>
       </c>
       <c r="F127">
         <v>0.107326958</v>
@@ -5734,7 +5731,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B128">
         <v>4.9661200000000001E-4</v>
@@ -5746,7 +5743,7 @@
         <v>0.40112509299999999</v>
       </c>
       <c r="E128">
-        <v>4.5082240000000003E-2</v>
+        <v>3.7916901000000003E-2</v>
       </c>
       <c r="F128">
         <v>0.100575394</v>
@@ -5760,7 +5757,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B129">
         <v>5.3819899999999995E-4</v>
@@ -5772,7 +5769,7 @@
         <v>0.400130769</v>
       </c>
       <c r="E129">
-        <v>4.503236E-2</v>
+        <v>3.8375550000000001E-2</v>
       </c>
       <c r="F129">
         <v>0.10001264</v>
@@ -5786,7 +5783,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130">
         <v>3.5480499999999998E-4</v>
@@ -5798,7 +5795,7 @@
         <v>0.39987046199999998</v>
       </c>
       <c r="E130">
-        <v>4.3609781E-2</v>
+        <v>3.4675389000000001E-2</v>
       </c>
       <c r="F130">
         <v>0.110734652</v>
@@ -5812,7 +5809,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131">
         <v>3.0498E-4</v>
@@ -5824,7 +5821,7 @@
         <v>0.39983951400000001</v>
       </c>
       <c r="E131">
-        <v>3.8087335E-2</v>
+        <v>3.4950776000000003E-2</v>
       </c>
       <c r="F131">
         <v>0.10964180599999999</v>
@@ -5838,7 +5835,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B132">
         <v>5.7161400000000002E-4</v>
@@ -5850,7 +5847,7 @@
         <v>0.49980213000000001</v>
       </c>
       <c r="E132">
-        <v>4.6878808000000001E-2</v>
+        <v>3.7310514000000003E-2</v>
       </c>
       <c r="F132">
         <v>0.100384342</v>
@@ -5864,7 +5861,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B133">
         <v>6.1787599999999995E-4</v>
@@ -5876,7 +5873,7 @@
         <v>0.500028205</v>
       </c>
       <c r="E133">
-        <v>4.9885762E-2</v>
+        <v>3.8094810999999999E-2</v>
       </c>
       <c r="F133">
         <v>9.9515904000000002E-2</v>
@@ -5890,7 +5887,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B134">
         <v>4.3410900000000001E-4</v>
@@ -5902,7 +5899,7 @@
         <v>0.49784190099999998</v>
       </c>
       <c r="E134">
-        <v>7.3446624000000002E-2</v>
+        <v>3.7069141E-2</v>
       </c>
       <c r="F134">
         <v>0.110014009</v>
@@ -5916,7 +5913,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B135">
         <v>3.79055E-4</v>
@@ -5928,7 +5925,7 @@
         <v>0.49926978</v>
       </c>
       <c r="E135">
-        <v>6.1689590000000002E-2</v>
+        <v>3.2560628000000001E-2</v>
       </c>
       <c r="F135">
         <v>0.10874370999999999</v>
@@ -5942,7 +5939,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B136">
         <v>5.0153199999999995E-4</v>
@@ -5954,7 +5951,7 @@
         <v>0.29999452700000001</v>
       </c>
       <c r="E136">
-        <v>3.9067486999999998E-2</v>
+        <v>3.3678996000000003E-2</v>
       </c>
       <c r="F136">
         <v>0.109497229</v>
@@ -5968,7 +5965,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B137">
         <v>5.0392299999999998E-4</v>
@@ -5980,7 +5977,7 @@
         <v>0.29948034400000001</v>
       </c>
       <c r="E137">
-        <v>4.7531764999999997E-2</v>
+        <v>3.5209544000000002E-2</v>
       </c>
       <c r="F137">
         <v>0.109779302</v>
@@ -5994,7 +5991,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B138">
         <v>3.4781999999999999E-4</v>
@@ -6006,7 +6003,7 @@
         <v>0.29999618500000003</v>
       </c>
       <c r="E138">
-        <v>4.7035642000000003E-2</v>
+        <v>3.7449899000000002E-2</v>
       </c>
       <c r="F138">
         <v>0.10975439100000001</v>
@@ -6020,7 +6017,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B139">
         <v>2.7612200000000001E-4</v>
@@ -6032,7 +6029,7 @@
         <v>0.300056612</v>
       </c>
       <c r="E139">
-        <v>4.5309544E-2</v>
+        <v>3.7161039999999999E-2</v>
       </c>
       <c r="F139">
         <v>0.111006706</v>
@@ -6046,7 +6043,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B140">
         <v>5.4036500000000001E-4</v>
@@ -6058,7 +6055,7 @@
         <v>0.40050686699999999</v>
       </c>
       <c r="E140">
-        <v>4.6744597999999998E-2</v>
+        <v>3.8979002999999998E-2</v>
       </c>
       <c r="F140">
         <v>9.8130669000000004E-2</v>
@@ -6072,7 +6069,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B141">
         <v>5.2480699999999996E-4</v>
@@ -6084,7 +6081,7 @@
         <v>0.401062998</v>
       </c>
       <c r="E141">
-        <v>3.7531783999999999E-2</v>
+        <v>3.1236511000000002E-2</v>
       </c>
       <c r="F141">
         <v>0.104900016</v>
@@ -6098,7 +6095,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B142">
         <v>3.9074900000000002E-4</v>
@@ -6110,7 +6107,7 @@
         <v>0.39881570100000002</v>
       </c>
       <c r="E142">
-        <v>4.2380693999999997E-2</v>
+        <v>3.3225333000000003E-2</v>
       </c>
       <c r="F142">
         <v>0.10894643900000001</v>
@@ -6124,7 +6121,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B143">
         <v>3.3084899999999998E-4</v>
@@ -6136,7 +6133,7 @@
         <v>0.39911565100000002</v>
       </c>
       <c r="E143">
-        <v>4.8708187999999999E-2</v>
+        <v>3.6519250000000003E-2</v>
       </c>
       <c r="F143">
         <v>0.108711746</v>
@@ -6150,7 +6147,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B144">
         <v>5.6678999999999996E-4</v>
@@ -6162,7 +6159,7 @@
         <v>0.50163681100000002</v>
       </c>
       <c r="E144">
-        <v>4.4913554000000001E-2</v>
+        <v>3.7039750000000003E-2</v>
       </c>
       <c r="F144">
         <v>9.8336361999999997E-2</v>
@@ -6176,7 +6173,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B145">
         <v>6.0097700000000004E-4</v>
@@ -6188,7 +6185,7 @@
         <v>0.49942540800000002</v>
       </c>
       <c r="E145">
-        <v>4.4640606999999999E-2</v>
+        <v>3.6877614000000003E-2</v>
       </c>
       <c r="F145">
         <v>9.8248176000000007E-2</v>
@@ -6202,7 +6199,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B146">
         <v>4.8327E-4</v>
@@ -6214,7 +6211,7 @@
         <v>0.50056330999999998</v>
       </c>
       <c r="E146">
-        <v>5.5029842000000002E-2</v>
+        <v>3.3496234999999999E-2</v>
       </c>
       <c r="F146">
         <v>0.102968558</v>
@@ -6228,7 +6225,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B147">
         <v>4.9274500000000005E-4</v>
@@ -6240,7 +6237,7 @@
         <v>0.29988877800000002</v>
       </c>
       <c r="E147">
-        <v>3.6448479999999998E-2</v>
+        <v>3.3134829999999997E-2</v>
       </c>
       <c r="F147">
         <v>0.10019613600000001</v>
@@ -6254,7 +6251,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B148">
         <v>3.2658299999999997E-4</v>
@@ -6266,7 +6263,7 @@
         <v>0.29819178499999999</v>
       </c>
       <c r="E148">
-        <v>3.5661086000000002E-2</v>
+        <v>3.3243096E-2</v>
       </c>
       <c r="F148">
         <v>0.10441104800000001</v>
@@ -6280,7 +6277,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B149">
         <v>2.25011E-4</v>
@@ -6292,7 +6289,7 @@
         <v>0.29830796199999998</v>
       </c>
       <c r="E149">
-        <v>3.2729743999999998E-2</v>
+        <v>2.8524424999999999E-2</v>
       </c>
       <c r="F149">
         <v>0.107690773</v>
@@ -6306,7 +6303,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B150">
         <v>5.0822400000000005E-4</v>
@@ -6318,7 +6315,7 @@
         <v>0.39998064300000002</v>
       </c>
       <c r="E150">
-        <v>3.5481061000000001E-2</v>
+        <v>2.8374363E-2</v>
       </c>
       <c r="F150">
         <v>9.7909154999999998E-2</v>
@@ -6332,7 +6329,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B151">
         <v>3.85542E-4</v>
@@ -6344,7 +6341,7 @@
         <v>0.40142784199999998</v>
       </c>
       <c r="E151">
-        <v>3.7443071000000001E-2</v>
+        <v>3.2418615999999997E-2</v>
       </c>
       <c r="F151">
         <v>0.104410629</v>
@@ -6358,7 +6355,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B152">
         <v>2.7817599999999999E-4</v>
@@ -6370,7 +6367,7 @@
         <v>0.40073868600000001</v>
       </c>
       <c r="E152">
-        <v>4.8454603999999998E-2</v>
+        <v>2.9233142E-2</v>
       </c>
       <c r="F152">
         <v>0.108353029</v>
@@ -6384,7 +6381,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B153">
         <v>5.7829300000000001E-4</v>
@@ -6396,7 +6393,7 @@
         <v>0.49932425499999999</v>
       </c>
       <c r="E153">
-        <v>3.3814474999999997E-2</v>
+        <v>2.2336103E-2</v>
       </c>
       <c r="F153">
         <v>9.9111609000000003E-2</v>
@@ -6410,7 +6407,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B154">
         <v>4.49791E-4</v>
@@ -6422,7 +6419,7 @@
         <v>0.49965446800000002</v>
       </c>
       <c r="E154">
-        <v>4.3603258999999998E-2</v>
+        <v>3.5048993000000001E-2</v>
       </c>
       <c r="F154">
         <v>0.10304944100000001</v>
@@ -6436,7 +6433,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B155">
         <v>3.38769E-4</v>
@@ -6448,7 +6445,7 @@
         <v>0.49989457599999998</v>
       </c>
       <c r="E155">
-        <v>3.8023349999999997E-2</v>
+        <v>3.2506526000000001E-2</v>
       </c>
       <c r="F155">
         <v>0.108397884</v>
@@ -6462,7 +6459,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B156">
         <v>5.0523799999999998E-4</v>
@@ -6474,7 +6471,7 @@
         <v>0.30028363699999999</v>
       </c>
       <c r="E156">
-        <v>4.1271736000000003E-2</v>
+        <v>3.2856110000000001E-2</v>
       </c>
       <c r="F156">
         <v>0.102398581</v>
@@ -6488,7 +6485,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B157">
         <v>3.7785800000000001E-4</v>
@@ -6500,7 +6497,7 @@
         <v>0.30006925000000001</v>
       </c>
       <c r="E157">
-        <v>3.6809690999999999E-2</v>
+        <v>2.8938051999999999E-2</v>
       </c>
       <c r="F157">
         <v>0.108183192</v>
@@ -6514,7 +6511,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B158">
         <v>2.8554999999999997E-4</v>
@@ -6526,7 +6523,7 @@
         <v>0.300038366</v>
       </c>
       <c r="E158">
-        <v>3.8511337E-2</v>
+        <v>2.9716191999999999E-2</v>
       </c>
       <c r="F158">
         <v>0.107811647</v>
@@ -6540,7 +6537,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B159">
         <v>4.70111E-4</v>
@@ -6552,7 +6549,7 @@
         <v>0.401582726</v>
       </c>
       <c r="E159">
-        <v>4.3640801999999999E-2</v>
+        <v>3.5263436000000002E-2</v>
       </c>
       <c r="F159">
         <v>0.101165298</v>
@@ -6566,7 +6563,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B160">
         <v>4.27133E-4</v>
@@ -6578,7 +6575,7 @@
         <v>0.39933699</v>
       </c>
       <c r="E160">
-        <v>4.1300086E-2</v>
+        <v>3.2918416999999998E-2</v>
       </c>
       <c r="F160">
         <v>0.10437996400000001</v>
@@ -6592,7 +6589,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B161">
         <v>3.3823700000000002E-4</v>
@@ -6604,7 +6601,7 @@
         <v>0.40005315400000002</v>
       </c>
       <c r="E161">
-        <v>4.5480125000000003E-2</v>
+        <v>3.0640058000000001E-2</v>
       </c>
       <c r="F161">
         <v>0.108152225</v>
@@ -6618,7 +6615,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B162">
         <v>5.7063399999999998E-4</v>
@@ -6630,7 +6627,7 @@
         <v>0.50041046</v>
       </c>
       <c r="E162">
-        <v>4.6042647999999999E-2</v>
+        <v>3.2445148E-2</v>
       </c>
       <c r="F162">
         <v>0.100247435</v>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B163">
         <v>5.2623700000000004E-4</v>
@@ -6656,7 +6653,7 @@
         <v>0.49990065900000002</v>
       </c>
       <c r="E163">
-        <v>5.1275907000000003E-2</v>
+        <v>4.1581205000000003E-2</v>
       </c>
       <c r="F163">
         <v>9.9901226999999995E-2</v>
@@ -6670,7 +6667,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B164">
         <v>3.8766700000000001E-4</v>
@@ -6682,7 +6679,7 @@
         <v>0.50011976599999997</v>
       </c>
       <c r="E164">
-        <v>5.4014270000000003E-2</v>
+        <v>2.8642780999999999E-2</v>
       </c>
       <c r="F164">
         <v>0.108257747</v>
@@ -6696,7 +6693,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B165">
         <v>4.8464800000000001E-4</v>
@@ -6708,7 +6705,7 @@
         <v>0.30006123899999998</v>
       </c>
       <c r="E165">
-        <v>3.8515338000000003E-2</v>
+        <v>2.9416213E-2</v>
       </c>
       <c r="F165">
         <v>0.107851928</v>
@@ -6722,7 +6719,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B166">
         <v>4.0982300000000002E-4</v>
@@ -6734,7 +6731,7 @@
         <v>0.30000044100000001</v>
       </c>
       <c r="E166">
-        <v>3.9715410999999999E-2</v>
+        <v>3.1521225E-2</v>
       </c>
       <c r="F166">
         <v>0.113022656</v>
@@ -6748,7 +6745,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B167">
         <v>3.1294599999999998E-4</v>
@@ -6760,7 +6757,7 @@
         <v>0.30003166100000001</v>
       </c>
       <c r="E167">
-        <v>4.9237347000000001E-2</v>
+        <v>3.5077997999999999E-2</v>
       </c>
       <c r="F167">
         <v>0.11181050300000001</v>
@@ -6774,7 +6771,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B168">
         <v>5.2144500000000005E-4</v>
@@ -6786,7 +6783,7 @@
         <v>0.40037684400000001</v>
       </c>
       <c r="E168">
-        <v>4.5546267000000001E-2</v>
+        <v>3.9031063999999997E-2</v>
       </c>
       <c r="F168">
         <v>9.4369333E-2</v>
@@ -6800,7 +6797,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B169">
         <v>4.6947900000000002E-4</v>
@@ -6812,7 +6809,7 @@
         <v>0.39994793499999998</v>
       </c>
       <c r="E169">
-        <v>3.7810668999999998E-2</v>
+        <v>2.8204534E-2</v>
       </c>
       <c r="F169">
         <v>9.1765380999999993E-2</v>
@@ -6826,7 +6823,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B170">
         <v>3.4246299999999999E-4</v>
@@ -6838,7 +6835,7 @@
         <v>0.39314682299999998</v>
       </c>
       <c r="E170">
-        <v>3.3905121000000003E-2</v>
+        <v>3.3906947E-2</v>
       </c>
       <c r="F170">
         <v>9.3838846000000004E-2</v>
@@ -6852,7 +6849,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B171">
         <v>5.7827599999999996E-4</v>
@@ -6864,7 +6861,7 @@
         <v>0.49995556099999999</v>
       </c>
       <c r="E171">
-        <v>4.8558603999999998E-2</v>
+        <v>3.7198548999999997E-2</v>
       </c>
       <c r="F171">
         <v>9.5985962999999994E-2</v>
@@ -6878,7 +6875,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B172">
         <v>5.4361800000000005E-4</v>
@@ -6890,7 +6887,7 @@
         <v>0.50145735700000005</v>
       </c>
       <c r="E172">
-        <v>4.8427867999999999E-2</v>
+        <v>3.2468634000000003E-2</v>
       </c>
       <c r="F172">
         <v>0.101831532</v>
@@ -6904,7 +6901,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B173">
         <v>3.1115599999999999E-4</v>
@@ -6916,7 +6913,7 @@
         <v>0.63610518599999999</v>
       </c>
       <c r="E173">
-        <v>4.8044137000000001E-2</v>
+        <v>3.2970342E-2</v>
       </c>
       <c r="F173">
         <v>0.10235364600000001</v>
@@ -6930,7 +6927,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B174">
         <v>4.84589E-4</v>
@@ -6942,7 +6939,7 @@
         <v>0.29996972900000002</v>
       </c>
       <c r="E174">
-        <v>2.7657220999999999E-2</v>
+        <v>2.5996668000000001E-2</v>
       </c>
       <c r="F174">
         <v>0.10192069600000001</v>
@@ -6956,7 +6953,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B175">
         <v>4.84723E-4</v>
@@ -6968,7 +6965,7 @@
         <v>0.30086995999999999</v>
       </c>
       <c r="E175">
-        <v>2.9996608000000001E-2</v>
+        <v>2.8763354000000001E-2</v>
       </c>
       <c r="F175">
         <v>0.100728892</v>
@@ -6982,7 +6979,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B176">
         <v>4.2448600000000001E-4</v>
@@ -6994,7 +6991,7 @@
         <v>0.30027710699999999</v>
       </c>
       <c r="E176">
-        <v>3.3680896000000002E-2</v>
+        <v>3.3740159999999998E-2</v>
       </c>
       <c r="F176">
         <v>0.101963254</v>
@@ -7008,7 +7005,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B177">
         <v>3.21245E-4</v>
@@ -7020,7 +7017,7 @@
         <v>0.30165437000000001</v>
       </c>
       <c r="E177">
-        <v>2.8404616000000001E-2</v>
+        <v>2.7233378999999999E-2</v>
       </c>
       <c r="F177">
         <v>0.106520084</v>
@@ -7034,7 +7031,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B178">
         <v>2.53766E-4</v>
@@ -7046,7 +7043,7 @@
         <v>0.30044469600000001</v>
       </c>
       <c r="E178">
-        <v>2.9515776000000001E-2</v>
+        <v>2.0616160000000001E-2</v>
       </c>
       <c r="F178">
         <v>0.110764391</v>
@@ -7060,7 +7057,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B179">
         <v>2.18042E-4</v>
@@ -7072,7 +7069,7 @@
         <v>0.29925571200000001</v>
       </c>
       <c r="E179">
-        <v>4.0818380000000001E-2</v>
+        <v>1.8358867000000001E-2</v>
       </c>
       <c r="F179">
         <v>0.112600636</v>
@@ -7086,7 +7083,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B180">
         <v>2.04692E-4</v>
@@ -7098,7 +7095,7 @@
         <v>0.30026093500000001</v>
       </c>
       <c r="E180">
-        <v>2.8816622E-2</v>
+        <v>2.1651783000000001E-2</v>
       </c>
       <c r="F180">
         <v>0.108112661</v>
@@ -7112,7 +7109,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B181">
         <v>5.2550700000000004E-4</v>
@@ -7124,7 +7121,7 @@
         <v>0.40456734900000002</v>
       </c>
       <c r="E181">
-        <v>3.485328E-2</v>
+        <v>3.3982204000000002E-2</v>
       </c>
       <c r="F181">
         <v>0.100120453</v>
@@ -7138,7 +7135,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B182">
         <v>5.3621300000000001E-4</v>
@@ -7150,7 +7147,7 @@
         <v>0.40080857199999997</v>
       </c>
       <c r="E182">
-        <v>3.6146741000000003E-2</v>
+        <v>3.5946688999999997E-2</v>
       </c>
       <c r="F182">
         <v>9.9449108999999994E-2</v>
@@ -7164,7 +7161,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B183">
         <v>4.7342700000000001E-4</v>
@@ -7176,7 +7173,7 @@
         <v>0.39943406199999998</v>
       </c>
       <c r="E183">
-        <v>3.4894360999999999E-2</v>
+        <v>3.4410559E-2</v>
       </c>
       <c r="F183">
         <v>0.103465405</v>
@@ -7190,7 +7187,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B184">
         <v>3.60226E-4</v>
@@ -7202,7 +7199,7 @@
         <v>0.39901998599999999</v>
       </c>
       <c r="E184">
-        <v>3.1833512000000001E-2</v>
+        <v>2.698455E-2</v>
       </c>
       <c r="F184">
         <v>0.110368597</v>
@@ -7216,7 +7213,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B185">
         <v>2.6574900000000002E-4</v>
@@ -7228,7 +7225,7 @@
         <v>0.40128135700000001</v>
       </c>
       <c r="E185">
-        <v>4.7793125999999998E-2</v>
+        <v>2.6107383000000001E-2</v>
       </c>
       <c r="F185">
         <v>0.10981632400000001</v>
@@ -7242,7 +7239,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B186">
         <v>2.40091E-4</v>
@@ -7254,7 +7251,7 @@
         <v>0.398708968</v>
       </c>
       <c r="E186">
-        <v>7.3278926999999994E-2</v>
+        <v>2.5653498E-2</v>
       </c>
       <c r="F186">
         <v>0.109913707</v>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B187">
         <v>2.2167000000000001E-4</v>
@@ -7280,7 +7277,7 @@
         <v>0.40003253100000002</v>
       </c>
       <c r="E187">
-        <v>7.0955006000000001E-2</v>
+        <v>1.8274945000000001E-2</v>
       </c>
       <c r="F187">
         <v>0.11041532699999999</v>
@@ -7294,7 +7291,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B188">
         <v>6.5489400000000005E-4</v>
@@ -7306,7 +7303,7 @@
         <v>0.50102734100000001</v>
       </c>
       <c r="E188">
-        <v>4.0853266999999999E-2</v>
+        <v>3.9141698000000003E-2</v>
       </c>
       <c r="F188">
         <v>9.9028083000000003E-2</v>
@@ -7320,7 +7317,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B189">
         <v>6.7796600000000001E-4</v>
@@ -7332,7 +7329,7 @@
         <v>0.49949943499999999</v>
       </c>
       <c r="E189">
-        <v>4.2382797999999999E-2</v>
+        <v>4.1188469999999998E-2</v>
       </c>
       <c r="F189">
         <v>9.7580385000000006E-2</v>
@@ -7346,7 +7343,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B190">
         <v>5.4967899999999997E-4</v>
@@ -7358,7 +7355,7 @@
         <v>0.50015754999999995</v>
       </c>
       <c r="E190">
-        <v>4.0361706999999997E-2</v>
+        <v>4.1100949999999997E-2</v>
       </c>
       <c r="F190">
         <v>0.101830843</v>
@@ -7372,7 +7369,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B191">
         <v>3.9895000000000002E-4</v>
@@ -7384,7 +7381,7 @@
         <v>0.49934918099999998</v>
       </c>
       <c r="E191">
-        <v>4.7611008000000003E-2</v>
+        <v>2.8115138000000001E-2</v>
       </c>
       <c r="F191">
         <v>0.111231076</v>
@@ -7398,7 +7395,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B192">
         <v>3.54428E-4</v>
@@ -7410,7 +7407,7 @@
         <v>0.50286452199999998</v>
       </c>
       <c r="E192">
-        <v>7.4892011999999994E-2</v>
+        <v>2.5991879999999998E-2</v>
       </c>
       <c r="F192">
         <v>0.108552304</v>
@@ -7424,7 +7421,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B193">
         <v>3.3188100000000002E-4</v>
@@ -7436,7 +7433,7 @@
         <v>0.49958002400000001</v>
       </c>
       <c r="E193">
-        <v>6.5147737999999997E-2</v>
+        <v>2.5567070000000001E-2</v>
       </c>
       <c r="F193">
         <v>0.111880279</v>
@@ -7450,7 +7447,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B194">
         <v>3.1751099999999998E-4</v>
@@ -7462,7 +7459,7 @@
         <v>0.50318848900000002</v>
       </c>
       <c r="E194">
-        <v>6.8701842999999999E-2</v>
+        <v>2.5804876000000001E-2</v>
       </c>
       <c r="F194">
         <v>0.110167457</v>
@@ -7476,7 +7473,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B195">
         <v>5.18681E-4</v>
@@ -7488,7 +7485,7 @@
         <v>0.29919042400000001</v>
       </c>
       <c r="E195">
-        <v>3.9886977999999997E-2</v>
+        <v>4.0519695000000001E-2</v>
       </c>
       <c r="F195">
         <v>0.102206272</v>
@@ -7502,7 +7499,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B196">
         <v>4.9001800000000005E-4</v>
@@ -7514,7 +7511,7 @@
         <v>0.30003544999999998</v>
       </c>
       <c r="E196">
-        <v>3.5557048000000001E-2</v>
+        <v>3.5539057999999998E-2</v>
       </c>
       <c r="F196">
         <v>0.108222652</v>
@@ -7528,7 +7525,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B197">
         <v>5.0937400000000005E-4</v>
@@ -7540,7 +7537,7 @@
         <v>0.29971783400000002</v>
       </c>
       <c r="E197">
-        <v>3.4331379000000002E-2</v>
+        <v>3.1520261000000001E-2</v>
       </c>
       <c r="F197">
         <v>0.109312838</v>
@@ -7554,7 +7551,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B198">
         <v>3.65507E-4</v>
@@ -7566,7 +7563,7 @@
         <v>0.30000356700000003</v>
       </c>
       <c r="E198">
-        <v>5.1118615999999999E-2</v>
+        <v>2.52023E-2</v>
       </c>
       <c r="F198">
         <v>0.114449734</v>
@@ -7580,7 +7577,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B199">
         <v>3.0124600000000002E-4</v>
@@ -7592,7 +7589,7 @@
         <v>0.29861169900000001</v>
       </c>
       <c r="E199">
-        <v>6.6413747999999995E-2</v>
+        <v>2.5660776E-2</v>
       </c>
       <c r="F199">
         <v>0.115184302</v>
@@ -7606,7 +7603,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B200">
         <v>2.8024199999999999E-4</v>
@@ -7618,7 +7615,7 @@
         <v>0.29985795599999998</v>
       </c>
       <c r="E200">
-        <v>6.6196255999999995E-2</v>
+        <v>2.3959202999999998E-2</v>
       </c>
       <c r="F200">
         <v>0.114170378</v>
@@ -7632,7 +7629,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B201">
         <v>2.7145000000000001E-4</v>
@@ -7644,7 +7641,7 @@
         <v>0.29980958600000002</v>
       </c>
       <c r="E201">
-        <v>6.1389894E-2</v>
+        <v>2.4672979000000001E-2</v>
       </c>
       <c r="F201">
         <v>0.114551606</v>
@@ -7658,7 +7655,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B202">
         <v>4.9716300000000001E-4</v>
@@ -7670,7 +7667,7 @@
         <v>0.39820402900000001</v>
       </c>
       <c r="E202">
-        <v>3.9495048999999997E-2</v>
+        <v>4.0553687999999997E-2</v>
       </c>
       <c r="F202">
         <v>0.107373751</v>
@@ -7684,7 +7681,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B203">
         <v>4.92466E-4</v>
@@ -7696,7 +7693,7 @@
         <v>0.39896216099999998</v>
       </c>
       <c r="E203">
-        <v>3.8421223999999997E-2</v>
+        <v>3.7943923999999997E-2</v>
       </c>
       <c r="F203">
         <v>0.106738518</v>
@@ -7710,7 +7707,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B204">
         <v>5.3962499999999996E-4</v>
@@ -7722,7 +7719,7 @@
         <v>0.39933082600000003</v>
       </c>
       <c r="E204">
-        <v>4.0525404000000001E-2</v>
+        <v>3.9118199999999999E-2</v>
       </c>
       <c r="F204">
         <v>0.108351713</v>
@@ -7736,7 +7733,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B205">
         <v>4.2028999999999998E-4</v>
@@ -7748,7 +7745,7 @@
         <v>0.40105601099999999</v>
       </c>
       <c r="E205">
-        <v>6.8845437999999995E-2</v>
+        <v>2.8223287999999999E-2</v>
       </c>
       <c r="F205">
         <v>0.116344845</v>
@@ -7762,7 +7759,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B206">
         <v>3.3060400000000002E-4</v>
@@ -7774,7 +7771,7 @@
         <v>0.39966170000000001</v>
       </c>
       <c r="E206">
-        <v>4.3627777999999999E-2</v>
+        <v>2.8835245999999998E-2</v>
       </c>
       <c r="F206">
         <v>0.11832458899999999</v>
@@ -7788,7 +7785,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B207">
         <v>3.0584500000000001E-4</v>
@@ -7800,7 +7797,7 @@
         <v>0.401437606</v>
       </c>
       <c r="E207">
-        <v>3.6550775000000001E-2</v>
+        <v>2.7479773999999998E-2</v>
       </c>
       <c r="F207">
         <v>0.119888392</v>
@@ -7814,7 +7811,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B208">
         <v>2.9125199999999998E-4</v>
@@ -7826,7 +7823,7 @@
         <v>0.40070955899999999</v>
       </c>
       <c r="E208">
-        <v>5.3149543E-2</v>
+        <v>3.0562319000000001E-2</v>
       </c>
       <c r="F208">
         <v>0.114329707</v>
@@ -7840,7 +7837,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B209">
         <v>5.6804700000000002E-4</v>
@@ -7852,7 +7849,7 @@
         <v>0.50076906200000004</v>
       </c>
       <c r="E209">
-        <v>4.2668380999999998E-2</v>
+        <v>4.1167963000000002E-2</v>
       </c>
       <c r="F209">
         <v>0.103836703</v>
@@ -7866,7 +7863,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B210">
         <v>5.8126300000000005E-4</v>
@@ -7878,7 +7875,7 @@
         <v>0.49977500800000002</v>
       </c>
       <c r="E210">
-        <v>4.4473360000000003E-2</v>
+        <v>4.1036514000000003E-2</v>
       </c>
       <c r="F210">
         <v>0.10628235699999999</v>
@@ -7892,7 +7889,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B211">
         <v>6.2164100000000003E-4</v>
@@ -7904,7 +7901,7 @@
         <v>0.499679392</v>
       </c>
       <c r="E211">
-        <v>4.0051691E-2</v>
+        <v>4.1156499999999999E-2</v>
       </c>
       <c r="F211">
         <v>0.110220675</v>
@@ -7918,7 +7915,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B212">
         <v>4.8212199999999998E-4</v>
@@ -7930,7 +7927,7 @@
         <v>0.499367542</v>
       </c>
       <c r="E212">
-        <v>6.9093981999999998E-2</v>
+        <v>3.0501744000000001E-2</v>
       </c>
       <c r="F212">
         <v>0.116096568</v>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B213">
         <v>3.6832299999999999E-4</v>
@@ -7956,7 +7953,7 @@
         <v>0.50092015999999995</v>
       </c>
       <c r="E213">
-        <v>3.8758915999999997E-2</v>
+        <v>2.9811035E-2</v>
       </c>
       <c r="F213">
         <v>0.122499317</v>
@@ -7970,7 +7967,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B214">
         <v>3.2732300000000002E-4</v>
@@ -7982,7 +7979,7 @@
         <v>0.49992052799999998</v>
       </c>
       <c r="E214">
-        <v>4.0073879999999999E-2</v>
+        <v>2.0171081E-2</v>
       </c>
       <c r="F214">
         <v>0.12782097000000001</v>
@@ -7996,7 +7993,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B215">
         <v>3.2196200000000002E-4</v>
@@ -8008,7 +8005,7 @@
         <v>0.49934297</v>
       </c>
       <c r="E215">
-        <v>6.0286174999999997E-2</v>
+        <v>2.8582026E-2</v>
       </c>
       <c r="F215">
         <v>0.11676415800000001</v>
@@ -8022,7 +8019,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B216">
         <v>4.8343099999999999E-4</v>
@@ -8034,7 +8031,7 @@
         <v>0.30003924100000001</v>
       </c>
       <c r="E216">
-        <v>3.2509215000000001E-2</v>
+        <v>2.9279166999999998E-2</v>
       </c>
       <c r="F216">
         <v>0.114784118</v>
@@ -8048,7 +8045,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B217">
         <v>4.7872600000000001E-4</v>
@@ -8060,7 +8057,7 @@
         <v>0.29903062699999999</v>
       </c>
       <c r="E217">
-        <v>3.2588632999999999E-2</v>
+        <v>2.5857577999999999E-2</v>
       </c>
       <c r="F217">
         <v>0.10958135099999999</v>
@@ -8074,7 +8071,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B218">
         <v>4.4455299999999998E-4</v>
@@ -8086,7 +8083,7 @@
         <v>0.29980042600000001</v>
       </c>
       <c r="E218">
-        <v>3.1885854999999998E-2</v>
+        <v>2.689706E-2</v>
       </c>
       <c r="F218">
         <v>0.10856081200000001</v>
@@ -8100,7 +8097,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B219">
         <v>3.8442400000000002E-4</v>
@@ -8112,7 +8109,7 @@
         <v>0.300352656</v>
       </c>
       <c r="E219">
-        <v>3.7383800000000002E-2</v>
+        <v>2.7090680999999998E-2</v>
       </c>
       <c r="F219">
         <v>0.108928434</v>
@@ -8126,7 +8123,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B220">
         <v>3.2228600000000002E-4</v>
@@ -8138,7 +8135,7 @@
         <v>0.29982069500000003</v>
       </c>
       <c r="E220">
-        <v>4.3492595000000002E-2</v>
+        <v>2.6526444999999999E-2</v>
       </c>
       <c r="F220">
         <v>0.110902872</v>
@@ -8152,7 +8149,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B221">
         <v>2.9366100000000002E-4</v>
@@ -8164,7 +8161,7 @@
         <v>0.30012657700000001</v>
       </c>
       <c r="E221">
-        <v>6.1729950999999998E-2</v>
+        <v>3.2150801999999999E-2</v>
       </c>
       <c r="F221">
         <v>0.115226499</v>
@@ -8178,7 +8175,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B222">
         <v>2.7240599999999999E-4</v>
@@ -8190,7 +8187,7 @@
         <v>0.29883443599999998</v>
       </c>
       <c r="E222">
-        <v>6.6170259999999995E-2</v>
+        <v>3.1520719000000003E-2</v>
       </c>
       <c r="F222">
         <v>0.11349644</v>
@@ -8204,7 +8201,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B223">
         <v>5.1822599999999999E-4</v>
@@ -8216,7 +8213,7 @@
         <v>0.40103576400000002</v>
       </c>
       <c r="E223">
-        <v>3.7581605999999997E-2</v>
+        <v>2.8851980999999999E-2</v>
       </c>
       <c r="F223">
         <v>0.109166028</v>
@@ -8230,7 +8227,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B224">
         <v>5.0449399999999997E-4</v>
@@ -8242,7 +8239,7 @@
         <v>0.40004508500000002</v>
       </c>
       <c r="E224">
-        <v>3.8170769E-2</v>
+        <v>3.0098415E-2</v>
       </c>
       <c r="F224">
         <v>0.109666481</v>
@@ -8256,7 +8253,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B225">
         <v>5.07009E-4</v>
@@ -8268,7 +8265,7 @@
         <v>0.39886264100000002</v>
       </c>
       <c r="E225">
-        <v>4.0584954999999999E-2</v>
+        <v>3.4996043999999997E-2</v>
       </c>
       <c r="F225">
         <v>0.109285695</v>
@@ -8282,7 +8279,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B226">
         <v>4.29863E-4</v>
@@ -8294,7 +8291,7 @@
         <v>0.39965901199999998</v>
       </c>
       <c r="E226">
-        <v>7.1105811000000005E-2</v>
+        <v>3.5208625E-2</v>
       </c>
       <c r="F226">
         <v>0.110949139</v>
@@ -8308,7 +8305,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B227">
         <v>3.4672300000000001E-4</v>
@@ -8320,7 +8317,7 @@
         <v>0.39999618199999998</v>
       </c>
       <c r="E227">
-        <v>6.9506928999999995E-2</v>
+        <v>4.0058535999999999E-2</v>
       </c>
       <c r="F227">
         <v>0.110695898</v>
@@ -8334,7 +8331,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B228">
         <v>3.13467E-4</v>
@@ -8346,7 +8343,7 @@
         <v>0.40056073800000003</v>
       </c>
       <c r="E228">
-        <v>7.1139833E-2</v>
+        <v>3.0372111E-2</v>
       </c>
       <c r="F228">
         <v>0.11312243299999999</v>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B229">
         <v>3.0008900000000002E-4</v>
@@ -8372,7 +8369,7 @@
         <v>0.39697400300000002</v>
       </c>
       <c r="E229">
-        <v>6.8165431999999998E-2</v>
+        <v>3.0062344000000001E-2</v>
       </c>
       <c r="F229">
         <v>0.11259936800000001</v>
@@ -8386,7 +8383,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B230">
         <v>5.6569300000000003E-4</v>
@@ -8398,7 +8395,7 @@
         <v>0.50014953600000001</v>
       </c>
       <c r="E230">
-        <v>6.9078813000000003E-2</v>
+        <v>3.2101386000000003E-2</v>
       </c>
       <c r="F230">
         <v>0.11520121999999999</v>
@@ -8412,7 +8409,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B231">
         <v>5.6636299999999996E-4</v>
@@ -8424,7 +8421,7 @@
         <v>0.50009379399999998</v>
       </c>
       <c r="E231">
-        <v>5.5513298000000003E-2</v>
+        <v>3.3790003999999998E-2</v>
       </c>
       <c r="F231">
         <v>0.114298685</v>
@@ -8438,7 +8435,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B232">
         <v>5.5780800000000002E-4</v>
@@ -8450,7 +8447,7 @@
         <v>0.49851990699999998</v>
       </c>
       <c r="E232">
-        <v>6.8876906000000002E-2</v>
+        <v>3.0070327000000001E-2</v>
       </c>
       <c r="F232">
         <v>0.116313977</v>
@@ -8464,7 +8461,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B233">
         <v>4.9915300000000001E-4</v>
@@ -8476,7 +8473,7 @@
         <v>0.49927363899999999</v>
       </c>
       <c r="E233">
-        <v>6.1411471000000002E-2</v>
+        <v>3.2267628E-2</v>
       </c>
       <c r="F233">
         <v>0.11773539500000001</v>
@@ -8490,7 +8487,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B234">
         <v>4.11395E-4</v>
@@ -8502,7 +8499,7 @@
         <v>0.49920661399999999</v>
       </c>
       <c r="E234">
-        <v>4.8344787E-2</v>
+        <v>2.7664886999999999E-2</v>
       </c>
       <c r="F234">
         <v>0.12562072899999999</v>
@@ -8516,7 +8513,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B235">
         <v>3.53161E-4</v>
@@ -8528,7 +8525,7 @@
         <v>0.49958985500000003</v>
       </c>
       <c r="E235">
-        <v>3.7024263000000002E-2</v>
+        <v>3.2011471E-2</v>
       </c>
       <c r="F235">
         <v>0.11188050300000001</v>
@@ -8542,7 +8539,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B236">
         <v>4.7270299999999999E-4</v>
@@ -8554,7 +8551,7 @@
         <v>0.30055517599999998</v>
       </c>
       <c r="E236">
-        <v>3.0824668E-2</v>
+        <v>2.9953827999999998E-2</v>
       </c>
       <c r="F236">
         <v>9.8189598000000003E-2</v>
@@ -8568,7 +8565,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B237">
         <v>4.6852800000000001E-4</v>
@@ -8580,7 +8577,7 @@
         <v>0.30032410799999998</v>
       </c>
       <c r="E237">
-        <v>3.3418607000000003E-2</v>
+        <v>3.2612093000000002E-2</v>
       </c>
       <c r="F237">
         <v>9.5314093000000003E-2</v>
@@ -8594,7 +8591,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B238">
         <v>4.1679199999999998E-4</v>
@@ -8606,7 +8603,7 @@
         <v>0.30124453200000001</v>
       </c>
       <c r="E238">
-        <v>3.7811510999999999E-2</v>
+        <v>3.8066342000000003E-2</v>
       </c>
       <c r="F238">
         <v>9.8369604999999999E-2</v>
@@ -8620,7 +8617,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B239">
         <v>3.2306400000000002E-4</v>
@@ -8632,7 +8629,7 @@
         <v>0.29904739499999999</v>
       </c>
       <c r="E239">
-        <v>3.5929846000000001E-2</v>
+        <v>3.5776985999999997E-2</v>
       </c>
       <c r="F239">
         <v>9.9846620999999997E-2</v>
@@ -8646,7 +8643,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B240">
         <v>2.6293600000000002E-4</v>
@@ -8658,7 +8655,7 @@
         <v>0.30047309999999999</v>
       </c>
       <c r="E240">
-        <v>3.3267286E-2</v>
+        <v>2.8083650000000002E-2</v>
       </c>
       <c r="F240">
         <v>0.10603617999999999</v>
@@ -8672,7 +8669,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B241">
         <v>2.2804999999999999E-4</v>
@@ -8684,7 +8681,7 @@
         <v>0.30166880499999998</v>
       </c>
       <c r="E241">
-        <v>3.1315015000000002E-2</v>
+        <v>2.919161E-2</v>
       </c>
       <c r="F241">
         <v>0.10724196799999999</v>
@@ -8698,7 +8695,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B242">
         <v>2.0938099999999999E-4</v>
@@ -8710,7 +8707,7 @@
         <v>0.29948566300000001</v>
       </c>
       <c r="E242">
-        <v>3.6314119999999998E-2</v>
+        <v>2.7488122E-2</v>
       </c>
       <c r="F242">
         <v>0.104573546</v>
@@ -8724,7 +8721,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B243">
         <v>5.0179900000000004E-4</v>
@@ -8736,7 +8733,7 @@
         <v>0.39968498499999999</v>
       </c>
       <c r="E243">
-        <v>2.9392582E-2</v>
+        <v>2.7075848E-2</v>
       </c>
       <c r="F243">
         <v>0.100459284</v>
@@ -8750,7 +8747,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B244">
         <v>5.1192700000000002E-4</v>
@@ -8762,7 +8759,7 @@
         <v>0.39811110900000002</v>
       </c>
       <c r="E244">
-        <v>3.2175303000000002E-2</v>
+        <v>2.7941183000000001E-2</v>
       </c>
       <c r="F244">
         <v>9.9352846999999994E-2</v>
@@ -8776,7 +8773,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B245">
         <v>4.3557999999999997E-4</v>
@@ -8788,7 +8785,7 @@
         <v>0.40116832899999999</v>
       </c>
       <c r="E245">
-        <v>3.9693225999999998E-2</v>
+        <v>3.6700075999999998E-2</v>
       </c>
       <c r="F245">
         <v>0.10021440700000001</v>
@@ -8802,7 +8799,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B246">
         <v>3.5768399999999999E-4</v>
@@ -8814,7 +8811,7 @@
         <v>0.39981008400000001</v>
       </c>
       <c r="E246">
-        <v>3.5477432000000003E-2</v>
+        <v>3.2424057999999999E-2</v>
       </c>
       <c r="F246">
         <v>0.105138485</v>
@@ -8828,7 +8825,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B247">
         <v>2.76524E-4</v>
@@ -8840,7 +8837,7 @@
         <v>0.39963096399999998</v>
       </c>
       <c r="E247">
-        <v>4.1707279E-2</v>
+        <v>2.8262046999999998E-2</v>
       </c>
       <c r="F247">
         <v>0.10851050399999999</v>
@@ -8854,7 +8851,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B248">
         <v>2.5828500000000002E-4</v>
@@ -8866,7 +8863,7 @@
         <v>0.39990617699999997</v>
       </c>
       <c r="E248">
-        <v>6.2740635000000003E-2</v>
+        <v>2.8981139E-2</v>
       </c>
       <c r="F248">
         <v>0.107568398</v>
@@ -8880,7 +8877,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B249">
         <v>2.3551900000000001E-4</v>
@@ -8892,7 +8889,7 @@
         <v>0.39852104300000002</v>
       </c>
       <c r="E249">
-        <v>5.7989448999999998E-2</v>
+        <v>2.6817901000000002E-2</v>
       </c>
       <c r="F249">
         <v>0.108287201</v>
@@ -8906,7 +8903,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B250">
         <v>6.48955E-4</v>
@@ -8918,7 +8915,7 @@
         <v>0.49962082099999999</v>
       </c>
       <c r="E250">
-        <v>3.4657304E-2</v>
+        <v>2.4963539999999999E-2</v>
       </c>
       <c r="F250">
         <v>9.9429778999999996E-2</v>
@@ -8932,7 +8929,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B251">
         <v>6.1183099999999996E-4</v>
@@ -8944,7 +8941,7 @@
         <v>0.50033280999999996</v>
       </c>
       <c r="E251">
-        <v>3.7521118999999999E-2</v>
+        <v>2.7673001999999999E-2</v>
       </c>
       <c r="F251">
         <v>9.8495864000000002E-2</v>
@@ -8958,7 +8955,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B252">
         <v>5.1377200000000001E-4</v>
@@ -8970,7 +8967,7 @@
         <v>0.50024451299999995</v>
       </c>
       <c r="E252">
-        <v>4.4029801E-2</v>
+        <v>3.9128736999999997E-2</v>
       </c>
       <c r="F252">
         <v>0.100396349</v>
@@ -8984,7 +8981,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B253">
         <v>4.3876499999999998E-4</v>
@@ -8996,7 +8993,7 @@
         <v>0.49925901499999997</v>
       </c>
       <c r="E253">
-        <v>3.9294586999999999E-2</v>
+        <v>3.4625995999999999E-2</v>
       </c>
       <c r="F253">
         <v>0.10699968</v>
@@ -9010,7 +9007,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B254">
         <v>3.4390000000000001E-4</v>
@@ -9022,7 +9019,7 @@
         <v>0.50068191399999995</v>
       </c>
       <c r="E254">
-        <v>6.5830854999999994E-2</v>
+        <v>3.0414301000000001E-2</v>
       </c>
       <c r="F254">
         <v>0.109581978</v>
@@ -9036,7 +9033,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B255">
         <v>3.10771E-4</v>
@@ -9048,7 +9045,7 @@
         <v>0.50035387600000003</v>
       </c>
       <c r="E255">
-        <v>7.3258196999999997E-2</v>
+        <v>2.9485480000000001E-2</v>
       </c>
       <c r="F255">
         <v>0.10888812</v>
@@ -9062,7 +9059,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B256">
         <v>3.0146300000000002E-4</v>
@@ -9074,7 +9071,7 @@
         <v>0.49992013899999999</v>
       </c>
       <c r="E256">
-        <v>5.1725806999999999E-2</v>
+        <v>2.8539121000000001E-2</v>
       </c>
       <c r="F256">
         <v>0.10817375999999999</v>
@@ -9088,7 +9085,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B257">
         <v>4.7849500000000001E-4</v>
@@ -9100,7 +9097,7 @@
         <v>0.30004532699999997</v>
       </c>
       <c r="E257">
-        <v>4.0780660000000003E-2</v>
+        <v>3.5949209000000003E-2</v>
       </c>
       <c r="F257">
         <v>0.103141573</v>
@@ -9114,7 +9111,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B258">
         <v>5.0275999999999999E-4</v>
@@ -9126,7 +9123,7 @@
         <v>0.29920427599999999</v>
       </c>
       <c r="E258">
-        <v>4.1816536000000001E-2</v>
+        <v>3.4553436E-2</v>
       </c>
       <c r="F258">
         <v>0.101860464</v>
@@ -9140,7 +9137,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B259">
         <v>5.1740599999999999E-4</v>
@@ -9152,7 +9149,7 @@
         <v>0.30149447299999999</v>
       </c>
       <c r="E259">
-        <v>4.1015214000000001E-2</v>
+        <v>3.4323686999999999E-2</v>
       </c>
       <c r="F259">
         <v>0.10246135300000001</v>
@@ -9166,7 +9163,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B260">
         <v>3.7951899999999998E-4</v>
@@ -9178,7 +9175,7 @@
         <v>0.29935602700000002</v>
       </c>
       <c r="E260">
-        <v>3.2089376000000003E-2</v>
+        <v>2.8244406999999999E-2</v>
       </c>
       <c r="F260">
         <v>0.107956841</v>
@@ -9192,7 +9189,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B261">
         <v>3.2461399999999998E-4</v>
@@ -9204,7 +9201,7 @@
         <v>0.298850589</v>
       </c>
       <c r="E261">
-        <v>7.0884645999999996E-2</v>
+        <v>2.7735271999999998E-2</v>
       </c>
       <c r="F261">
         <v>0.109011937</v>
@@ -9218,7 +9215,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B262">
         <v>2.92262E-4</v>
@@ -9230,7 +9227,7 @@
         <v>0.30029543199999997</v>
       </c>
       <c r="E262">
-        <v>7.4512727000000001E-2</v>
+        <v>2.7834968000000002E-2</v>
       </c>
       <c r="F262">
         <v>0.108335639</v>
@@ -9244,7 +9241,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B263">
         <v>2.7891199999999998E-4</v>
@@ -9256,7 +9253,7 @@
         <v>0.29951224900000001</v>
       </c>
       <c r="E263">
-        <v>6.4799326000000004E-2</v>
+        <v>2.8513480000000001E-2</v>
       </c>
       <c r="F263">
         <v>0.107322791</v>
@@ -9270,7 +9267,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B264">
         <v>4.4690600000000001E-4</v>
@@ -9282,7 +9279,7 @@
         <v>0.40118413600000002</v>
       </c>
       <c r="E264">
-        <v>4.5435773999999998E-2</v>
+        <v>3.8519957000000001E-2</v>
       </c>
       <c r="F264">
         <v>0.10055367599999999</v>
@@ -9296,7 +9293,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B265">
         <v>4.50968E-4</v>
@@ -9308,7 +9305,7 @@
         <v>0.40014166899999998</v>
       </c>
       <c r="E265">
-        <v>4.2461959000000001E-2</v>
+        <v>3.6762580000000003E-2</v>
       </c>
       <c r="F265">
         <v>9.9674258000000002E-2</v>
@@ -9322,7 +9319,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B266">
         <v>4.99166E-4</v>
@@ -9334,7 +9331,7 @@
         <v>0.40072669900000002</v>
       </c>
       <c r="E266">
-        <v>4.6791843999999999E-2</v>
+        <v>4.1438547999999999E-2</v>
       </c>
       <c r="F266">
         <v>0.100050923</v>
@@ -9348,7 +9345,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B267">
         <v>4.3689199999999998E-4</v>
@@ -9360,7 +9357,7 @@
         <v>0.39974975899999998</v>
       </c>
       <c r="E267">
-        <v>3.7030752E-2</v>
+        <v>3.1148538E-2</v>
       </c>
       <c r="F267">
         <v>0.108159581</v>
@@ -9374,7 +9371,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B268">
         <v>3.6157600000000001E-4</v>
@@ -9386,7 +9383,7 @@
         <v>0.400765488</v>
       </c>
       <c r="E268">
-        <v>6.5080570000000004E-2</v>
+        <v>2.9858714000000001E-2</v>
       </c>
       <c r="F268">
         <v>0.109293213</v>
@@ -9400,7 +9397,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B269">
         <v>3.40119E-4</v>
@@ -9412,7 +9409,7 @@
         <v>0.40009669599999997</v>
       </c>
       <c r="E269">
-        <v>7.3524844000000006E-2</v>
+        <v>2.9213735000000001E-2</v>
       </c>
       <c r="F269">
         <v>0.10913827299999999</v>
@@ -9426,7 +9423,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B270">
         <v>3.23025E-4</v>
@@ -9438,7 +9435,7 @@
         <v>0.40044863800000002</v>
       </c>
       <c r="E270">
-        <v>7.6759078999999994E-2</v>
+        <v>2.8591861E-2</v>
       </c>
       <c r="F270">
         <v>0.10835315500000001</v>
@@ -9452,7 +9449,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B271">
         <v>5.6255699999999999E-4</v>
@@ -9464,7 +9461,7 @@
         <v>0.49986556300000001</v>
       </c>
       <c r="E271">
-        <v>4.3558463999999998E-2</v>
+        <v>3.3598491000000001E-2</v>
       </c>
       <c r="F271">
         <v>0.10062673599999999</v>
@@ -9478,7 +9475,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B272">
         <v>5.7886999999999999E-4</v>
@@ -9490,7 +9487,7 @@
         <v>0.49958438500000002</v>
       </c>
       <c r="E272">
-        <v>4.4103181999999998E-2</v>
+        <v>3.3946135000000002E-2</v>
       </c>
       <c r="F272">
         <v>9.9812217999999994E-2</v>
@@ -9504,7 +9501,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B273">
         <v>6.3783199999999996E-4</v>
@@ -9516,7 +9513,7 @@
         <v>0.49801411899999998</v>
       </c>
       <c r="E273">
-        <v>4.2463493999999997E-2</v>
+        <v>3.3256761000000003E-2</v>
       </c>
       <c r="F273">
         <v>0.100906723</v>
@@ -9530,7 +9527,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B274">
         <v>5.2629499999999997E-4</v>
@@ -9542,7 +9539,7 @@
         <v>0.50003780099999995</v>
       </c>
       <c r="E274">
-        <v>4.5139868E-2</v>
+        <v>3.8036022000000003E-2</v>
       </c>
       <c r="F274">
         <v>0.101938865</v>
@@ -9556,7 +9553,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B275">
         <v>4.5853300000000001E-4</v>
@@ -9568,7 +9565,7 @@
         <v>0.499705173</v>
       </c>
       <c r="E275">
-        <v>4.4022573000000002E-2</v>
+        <v>3.3203124000000001E-2</v>
       </c>
       <c r="F275">
         <v>0.106222393</v>
@@ -9582,7 +9579,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B276">
         <v>4.09391E-4</v>
@@ -9594,7 +9591,7 @@
         <v>0.49964764900000003</v>
       </c>
       <c r="E276">
-        <v>6.8103606999999997E-2</v>
+        <v>2.8537580999999999E-2</v>
       </c>
       <c r="F276">
         <v>0.10792351</v>
@@ -9608,7 +9605,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B277">
         <v>4.1426199999999999E-4</v>
@@ -9620,7 +9617,7 @@
         <v>0.50079021499999998</v>
       </c>
       <c r="E277">
-        <v>5.6538620999999997E-2</v>
+        <v>3.0278824999999999E-2</v>
       </c>
       <c r="F277">
         <v>0.108647546</v>
@@ -9634,7 +9631,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B278">
         <v>4.8616099999999998E-4</v>
@@ -9646,7 +9643,7 @@
         <v>0.29988949399999998</v>
       </c>
       <c r="E278">
-        <v>4.0868091000000002E-2</v>
+        <v>3.4821600000000001E-2</v>
       </c>
       <c r="F278">
         <v>0.102740609</v>
@@ -9660,7 +9657,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B279">
         <v>4.9223300000000002E-4</v>
@@ -9672,7 +9669,7 @@
         <v>0.29991707200000001</v>
       </c>
       <c r="E279">
-        <v>3.9588467000000002E-2</v>
+        <v>3.5770488000000003E-2</v>
       </c>
       <c r="F279">
         <v>9.9979082999999996E-2</v>
@@ -9686,7 +9683,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B280">
         <v>4.8966000000000005E-4</v>
@@ -9698,7 +9695,7 @@
         <v>0.299807559</v>
       </c>
       <c r="E280">
-        <v>4.2113662000000003E-2</v>
+        <v>3.5374483999999998E-2</v>
       </c>
       <c r="F280">
         <v>9.8520637999999994E-2</v>
@@ -9712,7 +9709,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B281">
         <v>4.1326699999999999E-4</v>
@@ -9724,7 +9721,7 @@
         <v>0.30008244499999998</v>
       </c>
       <c r="E281">
-        <v>3.8818410999999997E-2</v>
+        <v>3.1020714000000001E-2</v>
       </c>
       <c r="F281">
         <v>0.104997322</v>
@@ -9738,7 +9735,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B282">
         <v>3.5472599999999998E-4</v>
@@ -9750,7 +9747,7 @@
         <v>0.299649999</v>
       </c>
       <c r="E282">
-        <v>3.805335E-2</v>
+        <v>3.0169298000000001E-2</v>
       </c>
       <c r="F282">
         <v>0.106645016</v>
@@ -9764,7 +9761,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B283">
         <v>3.0862499999999998E-4</v>
@@ -9776,7 +9773,7 @@
         <v>0.300016848</v>
       </c>
       <c r="E283">
-        <v>4.267257E-2</v>
+        <v>2.9701722E-2</v>
       </c>
       <c r="F283">
         <v>0.107568497</v>
@@ -9790,7 +9787,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B284">
         <v>2.9086800000000001E-4</v>
@@ -9802,7 +9799,7 @@
         <v>0.30050387099999998</v>
       </c>
       <c r="E284">
-        <v>4.7419393999999997E-2</v>
+        <v>3.1289824000000001E-2</v>
       </c>
       <c r="F284">
         <v>0.10544677199999999</v>
@@ -9816,7 +9813,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B285">
         <v>5.3141199999999999E-4</v>
@@ -9828,7 +9825,7 @@
         <v>0.40096458800000001</v>
       </c>
       <c r="E285">
-        <v>3.9940086E-2</v>
+        <v>3.6926992999999998E-2</v>
       </c>
       <c r="F285">
         <v>0.100374031</v>
@@ -9842,7 +9839,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B286">
         <v>4.9130500000000004E-4</v>
@@ -9854,7 +9851,7 @@
         <v>0.39783279599999999</v>
       </c>
       <c r="E286">
-        <v>3.9921999999999999E-2</v>
+        <v>3.4722467E-2</v>
       </c>
       <c r="F286">
         <v>0.100867067</v>
@@ -9868,7 +9865,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B287">
         <v>4.9682100000000005E-4</v>
@@ -9880,7 +9877,7 @@
         <v>0.39957826800000001</v>
       </c>
       <c r="E287">
-        <v>3.5337199999999999E-2</v>
+        <v>3.3049200000000001E-2</v>
       </c>
       <c r="F287">
         <v>0.10193480000000001</v>
@@ -9894,7 +9891,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B288">
         <v>4.6433100000000001E-4</v>
@@ -9906,7 +9903,7 @@
         <v>0.39989443400000002</v>
       </c>
       <c r="E288">
-        <v>4.1705930000000002E-2</v>
+        <v>3.1602706000000001E-2</v>
       </c>
       <c r="F288">
         <v>0.10475915299999999</v>
@@ -9920,7 +9917,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B289">
         <v>4.0902799999999997E-4</v>
@@ -9932,7 +9929,7 @@
         <v>0.40126719</v>
       </c>
       <c r="E289">
-        <v>6.0387098E-2</v>
+        <v>3.1978808999999997E-2</v>
       </c>
       <c r="F289">
         <v>0.10727930199999999</v>
@@ -9946,7 +9943,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B290">
         <v>3.7444099999999999E-4</v>
@@ -9958,7 +9955,7 @@
         <v>0.40043706899999998</v>
       </c>
       <c r="E290">
-        <v>7.2278722000000004E-2</v>
+        <v>3.0790000000000001E-2</v>
       </c>
       <c r="F290">
         <v>0.10862016200000001</v>
@@ -9972,7 +9969,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B291">
         <v>3.3825899999999999E-4</v>
@@ -9984,7 +9981,7 @@
         <v>0.39960972299999997</v>
       </c>
       <c r="E291">
-        <v>5.0731548000000001E-2</v>
+        <v>3.2077708000000003E-2</v>
       </c>
       <c r="F291">
         <v>0.109580419</v>
@@ -9998,7 +9995,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B292">
         <v>5.5933100000000004E-4</v>
@@ -10010,7 +10007,7 @@
         <v>0.499773087</v>
       </c>
       <c r="E292">
-        <v>4.3240530999999999E-2</v>
+        <v>3.1987520999999998E-2</v>
       </c>
       <c r="F292">
         <v>9.6250286000000004E-2</v>
@@ -10024,7 +10021,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B293">
         <v>5.6149699999999999E-4</v>
@@ -10036,7 +10033,7 @@
         <v>0.49969234000000001</v>
       </c>
       <c r="E293">
-        <v>4.6532391999999999E-2</v>
+        <v>3.4721224000000002E-2</v>
       </c>
       <c r="F293">
         <v>9.3758707999999996E-2</v>
@@ -10050,7 +10047,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B294">
         <v>5.6852900000000002E-4</v>
@@ -10062,7 +10059,7 @@
         <v>0.49999912200000002</v>
       </c>
       <c r="E294">
-        <v>4.8635330999999997E-2</v>
+        <v>3.8079976000000001E-2</v>
       </c>
       <c r="F294">
         <v>9.3466701999999999E-2</v>
@@ -10076,7 +10073,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B295">
         <v>5.5993099999999995E-4</v>
@@ -10088,7 +10085,7 @@
         <v>0.50000105500000003</v>
       </c>
       <c r="E295">
-        <v>4.9490144999999999E-2</v>
+        <v>3.3559245000000001E-2</v>
       </c>
       <c r="F295">
         <v>9.5530058000000001E-2</v>
@@ -10102,7 +10099,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B296">
         <v>4.9463399999999998E-4</v>
@@ -10114,7 +10111,7 @@
         <v>0.50235871200000004</v>
       </c>
       <c r="E296">
-        <v>3.7902236999999998E-2</v>
+        <v>2.8625714E-2</v>
       </c>
       <c r="F296">
         <v>0.104715946</v>
@@ -10128,7 +10125,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B297">
         <v>4.6393200000000002E-4</v>
@@ -10140,7 +10137,7 @@
         <v>0.49960959599999999</v>
       </c>
       <c r="E297">
-        <v>4.5027570000000003E-2</v>
+        <v>2.7584549E-2</v>
       </c>
       <c r="F297">
         <v>0.105402013</v>
@@ -10154,7 +10151,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B298">
         <v>3.34135E-4</v>
@@ -10166,7 +10163,7 @@
         <v>0.58694023799999995</v>
       </c>
       <c r="E298">
-        <v>4.2935114000000003E-2</v>
+        <v>2.5076272E-2</v>
       </c>
       <c r="F298">
         <v>0.102427253</v>
@@ -10180,7 +10177,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B299">
         <v>4.2709099999999999E-4</v>
@@ -10192,7 +10189,7 @@
         <v>0.300595785</v>
       </c>
       <c r="E299">
-        <v>2.0250721999999999E-2</v>
+        <v>1.8875831999999999E-2</v>
       </c>
       <c r="F299">
         <v>0.102772961</v>
@@ -10206,7 +10203,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B300">
         <v>4.3149099999999999E-4</v>
@@ -10218,7 +10215,7 @@
         <v>0.30079881800000002</v>
       </c>
       <c r="E300">
-        <v>2.1508796E-2</v>
+        <v>2.0397160000000001E-2</v>
       </c>
       <c r="F300">
         <v>0.10339688700000001</v>
@@ -10232,7 +10229,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B301">
         <v>3.9097999999999997E-4</v>
@@ -10244,7 +10241,7 @@
         <v>0.30092750000000001</v>
       </c>
       <c r="E301">
-        <v>3.3229887E-2</v>
+        <v>3.2527309999999997E-2</v>
       </c>
       <c r="F301">
         <v>0.100884113</v>
@@ -10258,7 +10255,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B302">
         <v>3.3918300000000001E-4</v>
@@ -10270,7 +10267,7 @@
         <v>0.29819463800000001</v>
       </c>
       <c r="E302">
-        <v>2.8830732000000001E-2</v>
+        <v>2.6236393E-2</v>
       </c>
       <c r="F302">
         <v>0.103947435</v>
@@ -10284,7 +10281,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B303">
         <v>2.9627499999999998E-4</v>
@@ -10296,7 +10293,7 @@
         <v>0.29996649600000003</v>
       </c>
       <c r="E303">
-        <v>2.8150482000000001E-2</v>
+        <v>2.2631852000000001E-2</v>
       </c>
       <c r="F303">
         <v>0.10510950099999999</v>
@@ -10310,7 +10307,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B304">
         <v>2.7603600000000001E-4</v>
@@ -10322,7 +10319,7 @@
         <v>0.29922444599999998</v>
       </c>
       <c r="E304">
-        <v>2.8260444999999999E-2</v>
+        <v>2.1853049999999999E-2</v>
       </c>
       <c r="F304">
         <v>0.105832572</v>
@@ -10336,7 +10333,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B305">
         <v>2.64763E-4</v>
@@ -10348,7 +10345,7 @@
         <v>0.29931229500000001</v>
       </c>
       <c r="E305">
-        <v>3.1558317000000002E-2</v>
+        <v>2.2081080999999999E-2</v>
       </c>
       <c r="F305">
         <v>0.10425438300000001</v>
@@ -10362,7 +10359,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B306">
         <v>4.6320699999999999E-4</v>
@@ -10374,7 +10371,7 @@
         <v>0.39906417700000002</v>
       </c>
       <c r="E306">
-        <v>2.7279082999999999E-2</v>
+        <v>2.6606799E-2</v>
       </c>
       <c r="F306">
         <v>0.100653384</v>
@@ -10388,7 +10385,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B307">
         <v>4.5498799999999997E-4</v>
@@ -10400,7 +10397,7 @@
         <v>0.39925735299999998</v>
       </c>
       <c r="E307">
-        <v>3.0386533E-2</v>
+        <v>2.8405099999999999E-2</v>
       </c>
       <c r="F307">
         <v>9.8851866999999996E-2</v>
@@ -10414,7 +10411,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B308">
         <v>4.3629200000000002E-4</v>
@@ -10426,7 +10423,7 @@
         <v>0.398908343</v>
       </c>
       <c r="E308">
-        <v>3.6496613999999997E-2</v>
+        <v>3.6396097000000002E-2</v>
       </c>
       <c r="F308">
         <v>0.100735436</v>
@@ -10440,7 +10437,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B309">
         <v>3.9866700000000001E-4</v>
@@ -10452,7 +10449,7 @@
         <v>0.39891339799999997</v>
       </c>
       <c r="E309">
-        <v>3.0948234000000002E-2</v>
+        <v>2.8173764E-2</v>
       </c>
       <c r="F309">
         <v>0.10731945</v>
@@ -10466,7 +10463,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B310">
         <v>3.3655799999999999E-4</v>
@@ -10478,7 +10475,7 @@
         <v>0.40106589199999998</v>
       </c>
       <c r="E310">
-        <v>3.6833079999999997E-2</v>
+        <v>2.7300264000000001E-2</v>
       </c>
       <c r="F310">
         <v>0.104447937</v>
@@ -10492,7 +10489,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B311">
         <v>3.0972699999999998E-4</v>
@@ -10504,7 +10501,7 @@
         <v>0.39997719900000001</v>
       </c>
       <c r="E311">
-        <v>3.7491233999999998E-2</v>
+        <v>2.4306024999999998E-2</v>
       </c>
       <c r="F311">
         <v>0.100064399</v>
@@ -10518,7 +10515,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B312">
         <v>2.9860200000000003E-4</v>
@@ -10530,7 +10527,7 @@
         <v>0.399170462</v>
       </c>
       <c r="E312">
-        <v>3.4313367999999997E-2</v>
+        <v>2.4034926000000002E-2</v>
       </c>
       <c r="F312">
         <v>9.9761053000000002E-2</v>
@@ -10544,7 +10541,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B313">
         <v>5.8556899999999998E-4</v>
@@ -10556,7 +10553,7 @@
         <v>0.50132858499999999</v>
       </c>
       <c r="E313">
-        <v>3.9261512999999998E-2</v>
+        <v>3.5760098999999997E-2</v>
       </c>
       <c r="F313">
         <v>9.2089454000000001E-2</v>
@@ -10570,7 +10567,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B314">
         <v>5.4085199999999998E-4</v>
@@ -10582,7 +10579,7 @@
         <v>0.50137097799999997</v>
       </c>
       <c r="E314">
-        <v>4.1191199999999997E-2</v>
+        <v>4.0050941999999999E-2</v>
       </c>
       <c r="F314">
         <v>9.2783633000000004E-2</v>
@@ -10596,7 +10593,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B315">
         <v>5.2526299999999999E-4</v>
@@ -10608,7 +10605,7 @@
         <v>0.49945460400000002</v>
       </c>
       <c r="E315">
-        <v>4.7282786E-2</v>
+        <v>4.6477519000000002E-2</v>
       </c>
       <c r="F315">
         <v>9.3627264000000002E-2</v>
@@ -10622,7 +10619,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B316">
         <v>4.62764E-4</v>
@@ -10634,7 +10631,7 @@
         <v>0.50061619400000001</v>
       </c>
       <c r="E316">
-        <v>5.2233031999999999E-2</v>
+        <v>4.3855742000000003E-2</v>
       </c>
       <c r="F316">
         <v>9.3554020000000002E-2</v>
@@ -10648,7 +10645,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B317">
         <v>3.65235E-4</v>
@@ -10660,7 +10657,7 @@
         <v>0.50027888099999995</v>
       </c>
       <c r="E317">
-        <v>4.1933915000000002E-2</v>
+        <v>2.7426127000000002E-2</v>
       </c>
       <c r="F317">
         <v>0.101548746</v>
@@ -10674,7 +10671,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B318">
         <v>3.27277E-4</v>
@@ -10686,7 +10683,7 @@
         <v>0.49991671900000001</v>
       </c>
       <c r="E318">
-        <v>6.4726811999999995E-2</v>
+        <v>2.5266204E-2</v>
       </c>
       <c r="F318">
         <v>0.110354388</v>
@@ -10700,7 +10697,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B319">
         <v>3.14875E-4</v>
@@ -10712,7 +10709,7 @@
         <v>0.50003056499999998</v>
       </c>
       <c r="E319">
-        <v>6.8702416000000002E-2</v>
+        <v>2.4889184000000002E-2</v>
       </c>
       <c r="F319">
         <v>0.109727409</v>
@@ -10726,7 +10723,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B320">
         <v>5.3314300000000003E-4</v>
@@ -10738,7 +10735,7 @@
         <v>0.298486943</v>
       </c>
       <c r="E320">
-        <v>3.7798134999999997E-2</v>
+        <v>3.6146156999999998E-2</v>
       </c>
       <c r="F320">
         <v>0.102955349</v>
@@ -10752,7 +10749,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B321">
         <v>5.1531000000000005E-4</v>
@@ -10764,7 +10761,7 @@
         <v>0.29985018800000002</v>
       </c>
       <c r="E321">
-        <v>4.0141284999999999E-2</v>
+        <v>3.7439083999999997E-2</v>
       </c>
       <c r="F321">
         <v>0.10231591499999999</v>
@@ -10778,7 +10775,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B322">
         <v>4.7795299999999998E-4</v>
@@ -10790,7 +10787,7 @@
         <v>0.30006054700000001</v>
       </c>
       <c r="E322">
-        <v>3.3727591000000001E-2</v>
+        <v>3.1618561000000003E-2</v>
       </c>
       <c r="F322">
         <v>0.105785476</v>
@@ -10804,7 +10801,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B323">
         <v>3.6146000000000003E-4</v>
@@ -10816,7 +10813,7 @@
         <v>0.29996759200000001</v>
       </c>
       <c r="E323">
-        <v>3.9639283999999997E-2</v>
+        <v>2.4192293E-2</v>
       </c>
       <c r="F323">
         <v>0.10970555</v>
@@ -10830,7 +10827,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B324">
         <v>2.9615000000000002E-4</v>
@@ -10842,7 +10839,7 @@
         <v>0.29927169599999998</v>
       </c>
       <c r="E324">
-        <v>6.0865677E-2</v>
+        <v>2.6010675E-2</v>
       </c>
       <c r="F324">
         <v>0.109082656</v>
@@ -10856,7 +10853,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B325">
         <v>2.6539199999999998E-4</v>
@@ -10868,7 +10865,7 @@
         <v>0.30087852900000001</v>
       </c>
       <c r="E325">
-        <v>7.5760642000000003E-2</v>
+        <v>2.4306310000000001E-2</v>
       </c>
       <c r="F325">
         <v>0.10911349100000001</v>
@@ -10882,7 +10879,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B326">
         <v>2.54348E-4</v>
@@ -10894,7 +10891,7 @@
         <v>0.27718706700000001</v>
       </c>
       <c r="E326">
-        <v>3.6368708E-2</v>
+        <v>2.3473473000000002E-2</v>
       </c>
       <c r="F326">
         <v>0.103970942</v>
@@ -10908,7 +10905,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B327">
         <v>5.5100500000000003E-4</v>
@@ -10920,7 +10917,7 @@
         <v>0.401205753</v>
       </c>
       <c r="E327">
-        <v>4.0367198999999999E-2</v>
+        <v>3.7712063999999997E-2</v>
       </c>
       <c r="F327">
         <v>0.10470025099999999</v>
@@ -10934,7 +10931,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B328">
         <v>5.6732099999999997E-4</v>
@@ -10946,7 +10943,7 @@
         <v>0.40160295099999999</v>
       </c>
       <c r="E328">
-        <v>4.0969556999999997E-2</v>
+        <v>4.1222267E-2</v>
       </c>
       <c r="F328">
         <v>0.105206543</v>
@@ -10960,7 +10957,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B329">
         <v>5.3201699999999997E-4</v>
@@ -10972,7 +10969,7 @@
         <v>0.40022643899999999</v>
       </c>
       <c r="E329">
-        <v>3.5358458000000002E-2</v>
+        <v>3.4129283000000003E-2</v>
       </c>
       <c r="F329">
         <v>0.110609967</v>
@@ -10986,7 +10983,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B330">
         <v>4.2268500000000001E-4</v>
@@ -10998,7 +10995,7 @@
         <v>0.39981734200000002</v>
       </c>
       <c r="E330">
-        <v>7.1620111E-2</v>
+        <v>2.5461850000000001E-2</v>
       </c>
       <c r="F330">
         <v>0.113427005</v>
@@ -11012,7 +11009,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B331">
         <v>3.2515300000000001E-4</v>
@@ -11024,7 +11021,7 @@
         <v>0.39902740599999997</v>
       </c>
       <c r="E331">
-        <v>7.3646951000000002E-2</v>
+        <v>2.9937952E-2</v>
       </c>
       <c r="F331">
         <v>0.11154404900000001</v>
@@ -11038,7 +11035,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B332">
         <v>3.0033399999999997E-4</v>
@@ -11050,7 +11047,7 @@
         <v>0.399791332</v>
       </c>
       <c r="E332">
-        <v>7.0960326000000004E-2</v>
+        <v>2.5111034000000001E-2</v>
       </c>
       <c r="F332">
         <v>0.11136420700000001</v>
@@ -11064,7 +11061,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B333">
         <v>2.8682499999999999E-4</v>
@@ -11076,7 +11073,7 @@
         <v>0.39983521399999999</v>
       </c>
       <c r="E333">
-        <v>6.7126547999999994E-2</v>
+        <v>2.4440446000000001E-2</v>
       </c>
       <c r="F333">
         <v>0.110826652</v>
@@ -11090,7 +11087,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B334">
         <v>6.5962200000000001E-4</v>
@@ -11102,7 +11099,7 @@
         <v>0.49965211700000001</v>
       </c>
       <c r="E334">
-        <v>4.2670694000000002E-2</v>
+        <v>3.8939330000000001E-2</v>
       </c>
       <c r="F334">
         <v>0.10375522299999999</v>
@@ -11116,7 +11113,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B335">
         <v>6.4296000000000004E-4</v>
@@ -11128,7 +11125,7 @@
         <v>0.49918752599999999</v>
       </c>
       <c r="E335">
-        <v>4.1950378000000003E-2</v>
+        <v>3.7288868000000003E-2</v>
       </c>
       <c r="F335">
         <v>0.106407322</v>
@@ -11142,7 +11139,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B336">
         <v>6.3665800000000002E-4</v>
@@ -11154,7 +11151,7 @@
         <v>0.53332581999999995</v>
       </c>
       <c r="E336">
-        <v>4.0856731E-2</v>
+        <v>3.6855077E-2</v>
       </c>
       <c r="F336">
         <v>0.104040328</v>
@@ -11168,7 +11165,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B337">
         <v>6.3738399999999995E-4</v>
@@ -11180,7 +11177,7 @@
         <v>0.49974123100000001</v>
       </c>
       <c r="E337">
-        <v>4.2100723E-2</v>
+        <v>3.9244738000000001E-2</v>
       </c>
       <c r="F337">
         <v>0.10597546100000001</v>
@@ -11194,7 +11191,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B338">
         <v>6.19449E-4</v>
@@ -11206,7 +11203,7 @@
         <v>0.50026277399999997</v>
       </c>
       <c r="E338">
-        <v>4.1591356000000003E-2</v>
+        <v>3.4016498999999999E-2</v>
       </c>
       <c r="F338">
         <v>0.109977661</v>
@@ -11220,7 +11217,7 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B339">
         <v>4.9860200000000001E-4</v>
@@ -11232,7 +11229,7 @@
         <v>0.50027971900000001</v>
       </c>
       <c r="E339">
-        <v>7.0967073000000006E-2</v>
+        <v>2.3932939E-2</v>
       </c>
       <c r="F339">
         <v>0.11422294400000001</v>
@@ -11246,7 +11243,7 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B340">
         <v>3.6904199999999998E-4</v>
@@ -11258,7 +11255,7 @@
         <v>0.50030577499999995</v>
       </c>
       <c r="E340">
-        <v>6.6469704000000004E-2</v>
+        <v>2.6483E-2</v>
       </c>
       <c r="F340">
         <v>0.116510979</v>
@@ -11272,7 +11269,7 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B341">
         <v>3.21902E-4</v>
@@ -11284,7 +11281,7 @@
         <v>0.50013415000000006</v>
       </c>
       <c r="E341">
-        <v>5.7089112999999997E-2</v>
+        <v>2.9292808E-2</v>
       </c>
       <c r="F341">
         <v>0.11521322000000001</v>
@@ -11298,7 +11295,7 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B342">
         <v>3.0918599999999998E-4</v>
@@ -11310,7 +11307,7 @@
         <v>0.49975158200000003</v>
       </c>
       <c r="E342">
-        <v>5.5146272000000003E-2</v>
+        <v>2.4939234000000001E-2</v>
       </c>
       <c r="F342">
         <v>0.114309811</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B343">
         <v>4.85129E-4</v>
@@ -11336,7 +11333,7 @@
         <v>0.30007985999999998</v>
       </c>
       <c r="E343">
-        <v>3.1432143000000003E-2</v>
+        <v>2.9019796E-2</v>
       </c>
       <c r="F343">
         <v>0.11381099</v>
@@ -11350,7 +11347,7 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B344">
         <v>4.7428800000000001E-4</v>
@@ -11362,7 +11359,7 @@
         <v>0.30001281800000001</v>
       </c>
       <c r="E344">
-        <v>3.3010744000000002E-2</v>
+        <v>3.1406066000000003E-2</v>
       </c>
       <c r="F344">
         <v>0.11308117199999999</v>
@@ -11376,7 +11373,7 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B345">
         <v>4.58329E-4</v>
@@ -11388,7 +11385,7 @@
         <v>0.29983200300000001</v>
       </c>
       <c r="E345">
-        <v>3.3648738999999997E-2</v>
+        <v>2.7470317000000001E-2</v>
       </c>
       <c r="F345">
         <v>0.113457661</v>
@@ -11402,7 +11399,7 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B346">
         <v>3.9580799999999999E-4</v>
@@ -11414,7 +11411,7 @@
         <v>0.29999587</v>
       </c>
       <c r="E346">
-        <v>4.6113999000000003E-2</v>
+        <v>2.5909682999999999E-2</v>
       </c>
       <c r="F346">
         <v>0.11548971800000001</v>
@@ -11428,7 +11425,7 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B347">
         <v>3.3780799999999999E-4</v>
@@ -11440,7 +11437,7 @@
         <v>0.29984454500000002</v>
       </c>
       <c r="E347">
-        <v>7.0016203999999999E-2</v>
+        <v>2.6734391E-2</v>
       </c>
       <c r="F347">
         <v>0.114565863</v>
@@ -11454,7 +11451,7 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B348">
         <v>2.9499700000000002E-4</v>
@@ -11466,7 +11463,7 @@
         <v>0.29999497400000003</v>
       </c>
       <c r="E348">
-        <v>5.1478729000000001E-2</v>
+        <v>2.6031990000000001E-2</v>
       </c>
       <c r="F348">
         <v>0.113484838</v>
@@ -11480,7 +11477,7 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B349">
         <v>2.7738399999999999E-4</v>
@@ -11492,7 +11489,7 @@
         <v>0.299965806</v>
       </c>
       <c r="E349">
-        <v>6.8609329999999996E-2</v>
+        <v>2.5472035000000001E-2</v>
       </c>
       <c r="F349">
         <v>0.110792153</v>
@@ -11506,7 +11503,7 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B350">
         <v>5.13668E-4</v>
@@ -11518,7 +11515,7 @@
         <v>0.40181292899999999</v>
       </c>
       <c r="E350">
-        <v>3.3861730999999999E-2</v>
+        <v>2.8976854E-2</v>
       </c>
       <c r="F350">
         <v>0.108200269</v>
@@ -11532,7 +11529,7 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B351">
         <v>5.3114999999999998E-4</v>
@@ -11544,7 +11541,7 @@
         <v>0.40075802599999999</v>
       </c>
       <c r="E351">
-        <v>3.5328396999999997E-2</v>
+        <v>3.0165536E-2</v>
       </c>
       <c r="F351">
         <v>0.10805416900000001</v>
@@ -11558,7 +11555,7 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B352">
         <v>5.0897099999999999E-4</v>
@@ -11570,7 +11567,7 @@
         <v>0.39980108800000003</v>
       </c>
       <c r="E352">
-        <v>4.0676258999999999E-2</v>
+        <v>2.8191463E-2</v>
       </c>
       <c r="F352">
         <v>0.109044108</v>
@@ -11584,7 +11581,7 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B353">
         <v>4.3509100000000003E-4</v>
@@ -11596,7 +11593,7 @@
         <v>0.3997909</v>
       </c>
       <c r="E353">
-        <v>6.4119865999999998E-2</v>
+        <v>2.6927901000000001E-2</v>
       </c>
       <c r="F353">
         <v>0.111962584</v>
@@ -11610,7 +11607,7 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B354">
         <v>3.6169799999999998E-4</v>
@@ -11622,7 +11619,7 @@
         <v>0.39989279700000002</v>
       </c>
       <c r="E354">
-        <v>4.0492685E-2</v>
+        <v>2.9547614999999999E-2</v>
       </c>
       <c r="F354">
         <v>0.115546248</v>
@@ -11636,7 +11633,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B355">
         <v>3.3175099999999998E-4</v>
@@ -11648,7 +11645,7 @@
         <v>0.399759647</v>
       </c>
       <c r="E355">
-        <v>3.7007920999999999E-2</v>
+        <v>2.8581051E-2</v>
       </c>
       <c r="F355">
         <v>0.116101996</v>
@@ -11662,7 +11659,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B356">
         <v>3.0890699999999998E-4</v>
@@ -11674,7 +11671,7 @@
         <v>0.39975485500000002</v>
       </c>
       <c r="E356">
-        <v>3.5096822999999999E-2</v>
+        <v>2.2202800000000002E-2</v>
       </c>
       <c r="F356">
         <v>0.11645707700000001</v>
@@ -11688,7 +11685,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B357">
         <v>5.4922200000000003E-4</v>
@@ -11700,7 +11697,7 @@
         <v>0.49980048199999999</v>
       </c>
       <c r="E357">
-        <v>3.8351444999999998E-2</v>
+        <v>3.0615773999999998E-2</v>
       </c>
       <c r="F357">
         <v>0.105765605</v>
@@ -11714,7 +11711,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B358">
         <v>5.5316299999999996E-4</v>
@@ -11726,7 +11723,7 @@
         <v>0.50032897399999998</v>
       </c>
       <c r="E358">
-        <v>3.8767682999999997E-2</v>
+        <v>3.1153771E-2</v>
       </c>
       <c r="F358">
         <v>0.105608667</v>
@@ -11740,7 +11737,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B359">
         <v>5.5357200000000001E-4</v>
@@ -11752,7 +11749,7 @@
         <v>0.49995863899999998</v>
       </c>
       <c r="E359">
-        <v>4.1497602000000001E-2</v>
+        <v>2.9911225999999999E-2</v>
       </c>
       <c r="F359">
         <v>0.107865848</v>
@@ -11766,7 +11763,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B360">
         <v>5.1459900000000002E-4</v>
@@ -11778,7 +11775,7 @@
         <v>0.49924889700000002</v>
       </c>
       <c r="E360">
-        <v>7.3695811E-2</v>
+        <v>2.7726224000000001E-2</v>
       </c>
       <c r="F360">
         <v>0.11089763900000001</v>
@@ -11792,7 +11789,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B361">
         <v>4.2470700000000003E-4</v>
@@ -11804,7 +11801,7 @@
         <v>0.49989370999999999</v>
       </c>
       <c r="E361">
-        <v>4.5768153999999998E-2</v>
+        <v>2.8382245E-2</v>
       </c>
       <c r="F361">
         <v>0.116405312</v>
@@ -11818,7 +11815,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B362">
         <v>3.68847E-4</v>
@@ -11830,7 +11827,7 @@
         <v>0.49769276600000001</v>
       </c>
       <c r="E362">
-        <v>3.9563547999999997E-2</v>
+        <v>2.2175271999999999E-2</v>
       </c>
       <c r="F362">
         <v>0.115419568</v>
@@ -11844,7 +11841,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B363">
         <v>3.3055999999999998E-4</v>
@@ -11856,7 +11853,7 @@
         <v>0.59374902299999999</v>
       </c>
       <c r="E363">
-        <v>3.6715955000000002E-2</v>
+        <v>3.1967387999999999E-2</v>
       </c>
       <c r="F363">
         <v>0.12346001199999999</v>
@@ -11892,10 +11889,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
@@ -11906,7 +11903,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>2.0462099999999999E-4</v>
@@ -11932,7 +11929,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>6.5725699999999996E-4</v>
@@ -11958,7 +11955,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>3.1127999999999999E-4</v>
@@ -11984,7 +11981,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>4.4927699999999999E-4</v>
@@ -12010,7 +12007,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>5.4967899999999997E-4</v>
@@ -12036,7 +12033,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>3.38769E-4</v>
@@ -12062,7 +12059,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>2.4194099999999999E-4</v>
@@ -12088,7 +12085,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>4.9274500000000005E-4</v>
@@ -12114,7 +12111,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>6.1183099999999996E-4</v>
@@ -12140,7 +12137,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>3.9097999999999997E-4</v>
@@ -12166,7 +12163,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>2.2167000000000001E-4</v>
@@ -12192,7 +12189,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>6.7796600000000001E-4</v>
@@ -12218,7 +12215,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>2.54348E-4</v>
@@ -12244,7 +12241,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>8.0239500000000002E-4</v>
@@ -12270,7 +12267,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>5.0275999999999999E-4</v>
@@ -12296,7 +12293,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>5.9944000000000002E-4</v>
@@ -12322,7 +12319,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>7.1244500000000003E-4</v>
@@ -12348,7 +12345,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>3.7785800000000001E-4</v>
@@ -12374,7 +12371,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>5.6844399999999998E-4</v>
@@ -12400,7 +12397,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>6.5962200000000001E-4</v>
@@ -12426,7 +12423,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>7.5361500000000001E-4</v>
@@ -12452,7 +12449,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>3.65507E-4</v>
@@ -12478,7 +12475,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24">
         <v>3.21902E-4</v>
@@ -12504,7 +12501,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <v>4.4690600000000001E-4</v>
@@ -12530,7 +12527,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26">
         <v>2.6539199999999998E-4</v>
@@ -12556,7 +12553,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27">
         <v>2.7240599999999999E-4</v>
@@ -12582,7 +12579,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>5.6636299999999996E-4</v>
@@ -12608,7 +12605,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29">
         <v>4.4455299999999998E-4</v>
@@ -12634,7 +12631,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>3.4781999999999999E-4</v>
@@ -12660,7 +12657,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31">
         <v>3.0862499999999998E-4</v>
@@ -12686,7 +12683,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32">
         <v>3.9580799999999999E-4</v>
@@ -12712,7 +12709,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33">
         <v>4.85129E-4</v>
@@ -12738,7 +12735,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>4.7428800000000001E-4</v>
@@ -12764,7 +12761,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>3.4672300000000001E-4</v>
@@ -12790,7 +12787,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>5.7827599999999996E-4</v>
@@ -12816,7 +12813,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B37">
         <v>4.6433100000000001E-4</v>
@@ -12842,7 +12839,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>4.11395E-4</v>
@@ -12868,7 +12865,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>3.13467E-4</v>
@@ -12894,7 +12891,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>7.2654800000000004E-4</v>
@@ -12920,7 +12917,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B41">
         <v>8.1662800000000002E-4</v>
@@ -12946,7 +12943,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42">
         <v>8.5975099999999996E-4</v>
@@ -12972,7 +12969,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43">
         <v>7.0617800000000001E-4</v>
@@ -12998,7 +12995,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44">
         <v>6.3737199999999998E-4</v>
@@ -13024,7 +13021,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45">
         <v>5.2616900000000005E-4</v>
@@ -13050,7 +13047,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46">
         <v>7.4180700000000003E-4</v>
@@ -13076,7 +13073,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47">
         <v>9.1292700000000001E-4</v>
@@ -13102,7 +13099,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48">
         <v>9.4360899999999998E-4</v>
@@ -13128,7 +13125,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49">
         <v>6.1466400000000001E-4</v>
@@ -13154,7 +13151,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50">
         <v>6.6162899999999995E-4</v>
@@ -13180,7 +13177,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51">
         <v>7.2370699999999997E-4</v>
@@ -13206,7 +13203,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52">
         <v>8.0128199999999995E-4</v>
@@ -13232,7 +13229,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53">
         <v>6.8117199999999996E-4</v>
@@ -13258,7 +13255,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54">
         <v>6.1575900000000001E-4</v>
@@ -13284,7 +13281,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55">
         <v>5.7284199999999995E-4</v>
@@ -13310,7 +13307,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56">
         <v>7.3430900000000005E-4</v>

--- a/V2.0/settings/data_main.xlsx
+++ b/V2.0/settings/data_main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iagr9\Projekte\MA\MA-Model_2\V2.0\settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465784A3-1C29-40C1-B000-A00B5EA2EA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0CB100-0B7A-404B-B228-026D437E2A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="23">
   <si>
     <t>exp</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>ye</t>
-  </si>
-  <si>
-    <t>ratio</t>
   </si>
   <si>
     <t>niba1</t>
@@ -102,6 +99,15 @@
   </si>
   <si>
     <t>h_dis_0</t>
+  </si>
+  <si>
+    <t>H_DPZ</t>
+  </si>
+  <si>
+    <t>L_DPZ</t>
+  </si>
+  <si>
+    <t>dpz_flooded</t>
   </si>
 </sst>
 </file>
@@ -466,36 +472,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -509,16 +521,22 @@
         <v>0.2</v>
       </c>
       <c r="E2" s="1">
-        <v>9.6295716614565059E-4</v>
+        <v>9.6295699999999996E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.1823660146057291</v>
+        <v>-1</v>
       </c>
       <c r="G2" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.43149999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -532,16 +550,22 @@
         <v>0.2</v>
       </c>
       <c r="E3" s="1">
-        <v>5.4068508635758987E-4</v>
+        <v>5.4068499999999995E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>0.21301483549235181</v>
+        <v>-1</v>
       </c>
       <c r="G3" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>0.34539999999999998</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -555,16 +579,22 @@
         <v>0.2</v>
       </c>
       <c r="E4" s="1">
-        <v>5.7356177557115905E-4</v>
+        <v>5.7356200000000001E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>0.25425761110318579</v>
+        <v>-1</v>
       </c>
       <c r="G4" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.35E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.33950000000000002</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -578,16 +608,22 @@
         <v>0.2</v>
       </c>
       <c r="E5" s="1">
-        <v>1.6091137159752529E-3</v>
+        <v>1.609114E-3</v>
       </c>
       <c r="F5" s="1">
-        <v>0.36931815679769697</v>
+        <v>-1</v>
       </c>
       <c r="G5" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.35420000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -601,16 +637,22 @@
         <v>0.2</v>
       </c>
       <c r="E6" s="1">
-        <v>2.022104184845368E-3</v>
+        <v>2.0221039999999998E-3</v>
       </c>
       <c r="F6" s="1">
-        <v>0.50113155679252741</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.36980000000000002</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -624,21 +666,27 @@
         <v>0.2</v>
       </c>
       <c r="E7" s="1">
-        <v>1.8583168791360669E-3</v>
+        <v>1.858317E-3</v>
       </c>
       <c r="F7" s="1">
-        <v>0.76352010233390366</v>
+        <v>-1</v>
       </c>
       <c r="G7" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.34239999999999998</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1">
-        <v>6.8899999999999994E-4</v>
+        <v>6.8900000000000005E-4</v>
       </c>
       <c r="C8" s="1">
         <v>160</v>
@@ -647,16 +695,22 @@
         <v>0.2</v>
       </c>
       <c r="E8" s="1">
-        <v>1.5414611966421831E-3</v>
+        <v>1.541461E-3</v>
       </c>
       <c r="F8" s="1">
-        <v>1.2806653375687329</v>
+        <v>-1</v>
       </c>
       <c r="G8" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.29349999999999998</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -670,21 +724,26 @@
         <v>0.2</v>
       </c>
       <c r="E9" s="1">
-        <v>1.203053031576804E-3</v>
+        <v>1.2030529999999999E-3</v>
       </c>
       <c r="F9" s="1">
-        <v>4.4268567706128978</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="H9">
+        <v>0.23089999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="1">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C10" s="1">
@@ -697,18 +756,23 @@
         <v>-1</v>
       </c>
       <c r="F10" s="1">
-        <v>-1</v>
+        <v>0.99572192500000001</v>
       </c>
       <c r="G10" s="1">
-        <v>0.99572192513368896</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="1">
-        <f>0.0002</f>
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="C11" s="1">
@@ -721,18 +785,23 @@
         <v>-1</v>
       </c>
       <c r="F11" s="1">
-        <v>-1</v>
+        <v>0.99572192500000001</v>
       </c>
       <c r="G11" s="1">
-        <v>0.99572192513368896</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H11">
+        <v>-1</v>
+      </c>
+      <c r="I11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="1">
-        <f>0.00025</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="C12" s="1">
@@ -745,18 +814,23 @@
         <v>-1</v>
       </c>
       <c r="F12" s="1">
-        <v>-1</v>
+        <v>0.99572192500000001</v>
       </c>
       <c r="G12" s="1">
-        <v>0.99572192513368896</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H12">
+        <v>-1</v>
+      </c>
+      <c r="I12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="1">
-        <f>0.0003</f>
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="C13" s="1">
@@ -769,18 +843,23 @@
         <v>-1</v>
       </c>
       <c r="F13" s="1">
-        <v>-1</v>
+        <v>0.996256684</v>
       </c>
       <c r="G13" s="1">
-        <v>0.99625668449197802</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H13">
+        <v>-1</v>
+      </c>
+      <c r="I13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="1">
-        <f>0.00035</f>
         <v>3.5E-4</v>
       </c>
       <c r="C14" s="1">
@@ -793,13 +872,19 @@
         <v>-1</v>
       </c>
       <c r="F14" s="1">
-        <v>-1</v>
+        <v>0.996256684</v>
       </c>
       <c r="G14" s="1">
-        <v>0.99625668449197802</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H14">
+        <v>-1</v>
+      </c>
+      <c r="I14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -813,16 +898,22 @@
         <v>0.2</v>
       </c>
       <c r="E15">
-        <v>2.2772938978669619E-4</v>
+        <v>2.27729E-4</v>
       </c>
       <c r="F15">
-        <v>0.1370529158760026</v>
+        <v>-1</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.5799999999999998E-3</v>
+      </c>
+      <c r="H15">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -836,13 +927,19 @@
         <v>0.2</v>
       </c>
       <c r="E16">
-        <v>1.3477410867637691E-3</v>
+        <v>1.347741E-3</v>
       </c>
       <c r="F16">
-        <v>0.17284629282554129</v>
+        <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>2.18E-2</v>
+      </c>
+      <c r="H16">
+        <v>0.498</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -859,13 +956,19 @@
         <v>0.2</v>
       </c>
       <c r="E17">
-        <v>1.48167952704679E-3</v>
+        <v>1.48168E-3</v>
       </c>
       <c r="F17">
-        <v>0.2279575182571614</v>
+        <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="H17">
+        <v>0.45</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -882,13 +985,19 @@
         <v>0.2</v>
       </c>
       <c r="E18">
-        <v>1.5823525896206921E-3</v>
+        <v>1.5823530000000001E-3</v>
       </c>
       <c r="F18">
-        <v>0.31658092682248279</v>
+        <v>-1</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>0.03</v>
+      </c>
+      <c r="H18">
+        <v>0.43</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -905,13 +1014,19 @@
         <v>0.2</v>
       </c>
       <c r="E19">
-        <v>1.2640770242587729E-3</v>
+        <v>1.264077E-3</v>
       </c>
       <c r="F19">
-        <v>0.46464702343852138</v>
+        <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="H19">
+        <v>0.33</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -928,13 +1043,19 @@
         <v>0.2</v>
       </c>
       <c r="E20">
-        <v>1.750109021017441E-3</v>
+        <v>1.7501089999999999E-3</v>
       </c>
       <c r="F20">
-        <v>0.73605944943634971</v>
+        <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="H20">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -951,13 +1072,19 @@
         <v>0.2</v>
       </c>
       <c r="E21">
-        <v>1.238571092807607E-3</v>
+        <v>1.2385709999999999E-3</v>
       </c>
       <c r="F21">
-        <v>1.3401074860750279</v>
+        <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="H21">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -974,13 +1101,19 @@
         <v>0.2</v>
       </c>
       <c r="E22">
-        <v>9.1166767204117576E-4</v>
+        <v>9.1166800000000003E-4</v>
       </c>
       <c r="F22">
-        <v>2.5877090019246669</v>
+        <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="H22">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -997,13 +1130,19 @@
         <v>0.2</v>
       </c>
       <c r="E23">
-        <v>4.5693419373077951E-4</v>
+        <v>4.5693399999999999E-4</v>
       </c>
       <c r="F23">
-        <v>4.8558997971939712</v>
+        <v>-1</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="H23">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1011,7 +1150,6 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C24">
@@ -1024,10 +1162,16 @@
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>0.95080213899999999</v>
       </c>
       <c r="G24">
-        <v>0.95080213903743305</v>
+        <v>-1</v>
+      </c>
+      <c r="H24">
+        <v>-1</v>
+      </c>
+      <c r="I24">
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1035,7 +1179,6 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <f>0.0002</f>
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="C25">
@@ -1048,10 +1191,16 @@
         <v>-1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>0.98930481299999995</v>
       </c>
       <c r="G25">
-        <v>0.989304812834224</v>
+        <v>-1</v>
+      </c>
+      <c r="H25">
+        <v>-1</v>
+      </c>
+      <c r="I25">
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,7 +1208,6 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <f>0.00025</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="C26">
@@ -1072,10 +1220,16 @@
         <v>-1</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>0.99358288800000005</v>
       </c>
       <c r="G26">
-        <v>0.99358288770053405</v>
+        <v>-1</v>
+      </c>
+      <c r="H26">
+        <v>-1</v>
+      </c>
+      <c r="I26">
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1083,7 +1237,6 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <f>0.0003</f>
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="C27">
@@ -1096,10 +1249,16 @@
         <v>-1</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>0.99518716600000001</v>
       </c>
       <c r="G27">
-        <v>0.99518716577540101</v>
+        <v>-1</v>
+      </c>
+      <c r="H27">
+        <v>-1</v>
+      </c>
+      <c r="I27">
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1107,7 +1266,6 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <f>0.00035</f>
         <v>3.5E-4</v>
       </c>
       <c r="C28">
@@ -1120,10 +1278,16 @@
         <v>-1</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>0.99732620299999997</v>
       </c>
       <c r="G28">
-        <v>0.99732620320855603</v>
+        <v>-1</v>
+      </c>
+      <c r="H28">
+        <v>-1</v>
+      </c>
+      <c r="I28">
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -1131,7 +1295,6 @@
         <v>3</v>
       </c>
       <c r="B29">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C29">
@@ -1144,10 +1307,16 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>0.96243386200000003</v>
       </c>
       <c r="G29">
-        <v>0.96243386243386198</v>
+        <v>-1</v>
+      </c>
+      <c r="H29">
+        <v>-1</v>
+      </c>
+      <c r="I29">
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -1164,13 +1333,19 @@
         <v>0.2</v>
       </c>
       <c r="E30" s="1">
-        <v>5.6943586866757242E-4</v>
+        <v>5.6943599999999999E-4</v>
       </c>
       <c r="F30" s="1">
-        <v>0.1320822729650824</v>
+        <v>-1</v>
       </c>
       <c r="G30" s="1">
-        <v>-1</v>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="H30">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -1187,13 +1362,19 @@
         <v>0.2</v>
       </c>
       <c r="E31" s="1">
-        <v>1.7641118244044319E-3</v>
+        <v>1.764112E-3</v>
       </c>
       <c r="F31" s="1">
-        <v>0.1597123428111161</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="1">
-        <v>-1</v>
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="H31">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -1210,17 +1391,23 @@
         <v>0.2</v>
       </c>
       <c r="E32" s="1">
-        <v>2.7815827299968472E-3</v>
+        <v>2.7815829999999998E-3</v>
       </c>
       <c r="F32" s="1">
-        <v>0.211589538977805</v>
+        <v>-1</v>
       </c>
       <c r="G32" s="1">
-        <v>-1</v>
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="H32">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
       </c>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,16 +1421,22 @@
         <v>0.2</v>
       </c>
       <c r="E33" s="1">
-        <v>3.1243836337864731E-3</v>
+        <v>3.124384E-3</v>
       </c>
       <c r="F33" s="1">
-        <v>0.29354094122178198</v>
+        <v>-1</v>
       </c>
       <c r="G33" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="H33">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>3</v>
       </c>
@@ -1257,16 +1450,22 @@
         <v>0.2</v>
       </c>
       <c r="E34" s="1">
-        <v>3.5047858321507158E-3</v>
+        <v>3.5047860000000002E-3</v>
       </c>
       <c r="F34" s="1">
-        <v>0.45503198214379609</v>
+        <v>-1</v>
       </c>
       <c r="G34" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.45E-2</v>
+      </c>
+      <c r="H34">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>3</v>
       </c>
@@ -1280,21 +1479,27 @@
         <v>0.2</v>
       </c>
       <c r="E35" s="1">
-        <v>3.0154706835275259E-3</v>
+        <v>3.015471E-3</v>
       </c>
       <c r="F35" s="1">
-        <v>0.66921493130958387</v>
+        <v>-1</v>
       </c>
       <c r="G35" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="H35">
+        <v>0.45929999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="1">
-        <v>8.0399999999999992E-4</v>
+        <v>8.0400000000000003E-4</v>
       </c>
       <c r="C36" s="1">
         <v>240</v>
@@ -1303,16 +1508,22 @@
         <v>0.2</v>
       </c>
       <c r="E36" s="1">
-        <v>2.3056367382307788E-3</v>
+        <v>2.3056370000000001E-3</v>
       </c>
       <c r="F36" s="1">
-        <v>1.162567156778866</v>
+        <v>-1</v>
       </c>
       <c r="G36" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="H36">
+        <v>0.36370000000000002</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>3</v>
       </c>
@@ -1326,16 +1537,22 @@
         <v>0.2</v>
       </c>
       <c r="E37" s="1">
-        <v>1.8617433763087039E-3</v>
+        <v>1.8617429999999999E-3</v>
       </c>
       <c r="F37" s="1">
-        <v>2.1446243317633749</v>
+        <v>-1</v>
       </c>
       <c r="G37" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="H37">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>3</v>
       </c>
@@ -1349,21 +1566,26 @@
         <v>0.2</v>
       </c>
       <c r="E38" s="1">
-        <v>9.7170389896743172E-4</v>
+        <v>9.7170399999999999E-4</v>
       </c>
       <c r="F38" s="1">
-        <v>3.606055934726871</v>
+        <v>-1</v>
       </c>
       <c r="G38" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="H38">
+        <v>0.26240000000000002</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B39" s="1">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C39" s="1">
@@ -1376,18 +1598,23 @@
         <v>-1</v>
       </c>
       <c r="F39" s="1">
-        <v>-1</v>
+        <v>0.74973261999999996</v>
       </c>
       <c r="G39" s="1">
-        <v>0.74973262032085497</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H39">
+        <v>-1</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B40" s="1">
-        <f>0.0002</f>
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="C40" s="1">
@@ -1400,18 +1627,23 @@
         <v>-1</v>
       </c>
       <c r="F40" s="1">
-        <v>-1</v>
+        <v>0.97433155100000002</v>
       </c>
       <c r="G40" s="1">
-        <v>0.97433155080213896</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H40">
+        <v>-1</v>
+      </c>
+      <c r="I40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="1">
-        <f>0.00025</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="C41" s="1">
@@ -1424,18 +1656,23 @@
         <v>-1</v>
       </c>
       <c r="F41" s="1">
-        <v>-1</v>
+        <v>0.98609625700000003</v>
       </c>
       <c r="G41" s="1">
-        <v>0.98609625668449197</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H41">
+        <v>-1</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B42" s="1">
-        <f>0.0003</f>
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="C42" s="1">
@@ -1448,18 +1685,23 @@
         <v>-1</v>
       </c>
       <c r="F42" s="1">
-        <v>-1</v>
+        <v>0.99144385000000002</v>
       </c>
       <c r="G42" s="1">
-        <v>0.99144385026737902</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H42">
+        <v>-1</v>
+      </c>
+      <c r="I42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B43" s="1">
-        <f>0.00035</f>
         <v>3.5E-4</v>
       </c>
       <c r="C43" s="1">
@@ -1472,18 +1714,23 @@
         <v>-1</v>
       </c>
       <c r="F43" s="1">
-        <v>-1</v>
+        <v>0.99518716600000001</v>
       </c>
       <c r="G43" s="1">
-        <v>0.99518716577540101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H43">
+        <v>-1</v>
+      </c>
+      <c r="I43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B44" s="1">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C44" s="1">
@@ -1496,18 +1743,23 @@
         <v>-1</v>
       </c>
       <c r="F44" s="1">
-        <v>-1</v>
+        <v>0.93015873000000004</v>
       </c>
       <c r="G44" s="1">
-        <v>0.93015873015872996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H44">
+        <v>-1</v>
+      </c>
+      <c r="I44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B45" s="1">
-        <f>0.0002</f>
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="C45" s="1">
@@ -1520,18 +1772,23 @@
         <v>-1</v>
       </c>
       <c r="F45" s="1">
-        <v>-1</v>
+        <v>0.94973545000000004</v>
       </c>
       <c r="G45" s="1">
-        <v>0.94973544973544899</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H45">
+        <v>-1</v>
+      </c>
+      <c r="I45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B46" s="1">
-        <f>0.00025</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="C46" s="1">
@@ -1544,18 +1801,23 @@
         <v>-1</v>
       </c>
       <c r="F46" s="1">
-        <v>-1</v>
+        <v>0.97566137600000002</v>
       </c>
       <c r="G46" s="1">
-        <v>0.97566137566137501</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H46">
+        <v>-1</v>
+      </c>
+      <c r="I46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B47" s="1">
-        <f>0.0003</f>
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="C47" s="1">
@@ -1568,18 +1830,23 @@
         <v>-1</v>
       </c>
       <c r="F47" s="1">
-        <v>-1</v>
+        <v>0.98783068799999996</v>
       </c>
       <c r="G47" s="1">
-        <v>0.98783068783068695</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H47">
+        <v>-1</v>
+      </c>
+      <c r="I47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="1">
-        <f>0.00035</f>
         <v>3.5E-4</v>
       </c>
       <c r="C48" s="1">
@@ -1592,18 +1859,23 @@
         <v>-1</v>
       </c>
       <c r="F48" s="1">
-        <v>-1</v>
+        <v>0.99523809500000004</v>
       </c>
       <c r="G48" s="1">
-        <v>0.99523809523809503</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H48">
+        <v>-1</v>
+      </c>
+      <c r="I48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B49" s="1">
-        <f>0.00018</f>
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="C49" s="1">
@@ -1616,13 +1888,19 @@
         <v>-1</v>
       </c>
       <c r="F49" s="1">
-        <v>-1</v>
+        <v>0.92751322800000002</v>
       </c>
       <c r="G49" s="1">
-        <v>0.92751322751322696</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1</v>
+      </c>
+      <c r="H49">
+        <v>-1</v>
+      </c>
+      <c r="I49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -1636,16 +1914,22 @@
         <v>0.2</v>
       </c>
       <c r="E50">
-        <v>6.6906144476863239E-4</v>
+        <v>6.6906099999999998E-4</v>
       </c>
       <c r="F50">
-        <v>9.9454994068497199E-2</v>
+        <v>-1</v>
       </c>
       <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="H50">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -1659,16 +1943,22 @@
         <v>0.2</v>
       </c>
       <c r="E51">
-        <v>2.481912581033939E-3</v>
+        <v>2.4819130000000001E-3</v>
       </c>
       <c r="F51">
-        <v>0.13324589043500251</v>
+        <v>-1</v>
       </c>
       <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="H51">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -1682,16 +1972,22 @@
         <v>0.2</v>
       </c>
       <c r="E52">
-        <v>3.5047858321507158E-3</v>
+        <v>3.5047860000000002E-3</v>
       </c>
       <c r="F52">
-        <v>0.17507291557699109</v>
+        <v>-1</v>
       </c>
       <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.45E-2</v>
+      </c>
+      <c r="H52">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -1705,16 +2001,22 @@
         <v>0.2</v>
       </c>
       <c r="E53">
-        <v>3.5300274842651859E-3</v>
+        <v>3.5300269999999998E-3</v>
       </c>
       <c r="F53">
-        <v>0.24912153359547129</v>
+        <v>-1</v>
       </c>
       <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H53">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -1728,16 +2030,22 @@
         <v>0.2</v>
       </c>
       <c r="E54">
-        <v>3.7511155850126609E-3</v>
+        <v>3.7511160000000001E-3</v>
       </c>
       <c r="F54">
-        <v>0.38077808031907501</v>
+        <v>-1</v>
       </c>
       <c r="G54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.96E-2</v>
+      </c>
+      <c r="H54">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -1751,16 +2059,22 @@
         <v>0.2</v>
       </c>
       <c r="E55">
-        <v>3.7918205784826329E-3</v>
+        <v>3.7918209999999999E-3</v>
       </c>
       <c r="F55">
-        <v>0.58685321837904003</v>
+        <v>-1</v>
       </c>
       <c r="G55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="H55">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -1774,16 +2088,22 @@
         <v>0.2</v>
       </c>
       <c r="E56">
-        <v>2.9280961559260119E-3</v>
+        <v>2.9280959999999998E-3</v>
       </c>
       <c r="F56">
-        <v>0.98659551435052129</v>
+        <v>-1</v>
       </c>
       <c r="G56">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="H56">
+        <v>0.42</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -1797,16 +2117,22 @@
         <v>0.2</v>
       </c>
       <c r="E57">
-        <v>2.4002025628507462E-3</v>
+        <v>2.4002030000000001E-3</v>
       </c>
       <c r="F57">
-        <v>1.8618922637938651</v>
+        <v>-1</v>
       </c>
       <c r="G57">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6.1600000000000002E-2</v>
+      </c>
+      <c r="H57">
+        <v>0.35</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -1820,28 +2146,33 @@
         <v>0.2</v>
       </c>
       <c r="E58">
-        <v>1.53434215541255E-3</v>
+        <v>1.534342E-3</v>
       </c>
       <c r="F58">
-        <v>2.5177979188444941</v>
+        <v>-1</v>
       </c>
       <c r="G58">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="H58">
+        <v>0.32</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>3</v>
       </c>
       <c r="B59">
-        <f>0.00018</f>
-        <v>1.8000000000000001E-4</v>
+        <v>2.2510799999999999E-4</v>
       </c>
       <c r="C59">
         <v>280</v>
       </c>
       <c r="D59">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E59">
         <v>-1</v>
@@ -1850,22 +2181,27 @@
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.64973262032085499</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>3</v>
       </c>
       <c r="B60">
-        <f>0.0002</f>
-        <v>2.0000000000000001E-4</v>
+        <v>2.5108200000000002E-4</v>
       </c>
       <c r="C60">
         <v>280</v>
       </c>
       <c r="D60">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E60">
         <v>-1</v>
@@ -1874,22 +2210,27 @@
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.91657754010695103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>3</v>
       </c>
       <c r="B61">
-        <f>0.00025</f>
-        <v>2.5000000000000001E-4</v>
+        <v>2.8571400000000001E-4</v>
       </c>
       <c r="C61">
         <v>280</v>
       </c>
       <c r="D61">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E61">
         <v>-1</v>
@@ -1898,22 +2239,27 @@
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.97754010695187099</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>3</v>
       </c>
       <c r="B62">
-        <f>0.0003</f>
-        <v>2.9999999999999997E-4</v>
+        <v>3.3419899999999998E-4</v>
       </c>
       <c r="C62">
         <v>280</v>
       </c>
       <c r="D62">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E62">
         <v>-1</v>
@@ -1922,22 +2268,27 @@
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.98716577540106898</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>3</v>
       </c>
       <c r="B63">
-        <f>0.00035</f>
-        <v>3.5E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="C63">
         <v>280</v>
       </c>
       <c r="D63">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E63">
         <v>-1</v>
@@ -1946,16 +2297,21 @@
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.99251336898395703</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>3</v>
       </c>
       <c r="B64">
-        <f>0.00018</f>
-        <v>1.8000000000000001E-4</v>
+        <v>5.0216499999999995E-4</v>
       </c>
       <c r="C64">
         <v>280</v>
@@ -1970,16 +2326,21 @@
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.89470899470899401</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>3</v>
       </c>
       <c r="B65">
-        <f>0.0002</f>
-        <v>2.0000000000000001E-4</v>
+        <v>6.44156E-4</v>
       </c>
       <c r="C65">
         <v>280</v>
@@ -1994,16 +2355,21 @@
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.91216931216931196</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>3</v>
       </c>
       <c r="B66">
-        <f>0.00025</f>
-        <v>2.5000000000000001E-4</v>
+        <v>9.904759999999999E-4</v>
       </c>
       <c r="C66">
         <v>280</v>
@@ -2018,16 +2384,21 @@
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.96137566137566099</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>3</v>
       </c>
       <c r="B67">
-        <f>0.0003</f>
-        <v>2.9999999999999997E-4</v>
+        <v>1.4112549999999999E-3</v>
       </c>
       <c r="C67">
         <v>280</v>
@@ -2042,22 +2413,27 @@
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.98148148148148096</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>3</v>
       </c>
       <c r="B68">
-        <f>0.00035</f>
-        <v>3.5E-4</v>
+        <v>2.4242400000000001E-4</v>
       </c>
       <c r="C68">
         <v>280</v>
       </c>
       <c r="D68">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E68">
         <v>-1</v>
@@ -2066,16 +2442,21 @@
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.98994708994708902</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.4723619999999997E-3</v>
+      </c>
+      <c r="H68">
+        <v>0.236398467</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>3</v>
       </c>
       <c r="B69">
-        <f>0.00018</f>
-        <v>1.8000000000000001E-4</v>
+        <v>2.7186099999999998E-4</v>
       </c>
       <c r="C69">
         <v>280</v>
@@ -2090,328 +2471,1201 @@
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.89894179894179804</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.0201009999999999E-3</v>
+      </c>
+      <c r="H69">
+        <v>0.236398467</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="1">
+        <v>3.0995699999999997E-4</v>
+      </c>
+      <c r="C70" s="1">
+        <v>280</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4.773869E-3</v>
+      </c>
+      <c r="H70">
+        <v>0.222605364</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3.6017299999999998E-4</v>
+      </c>
+      <c r="C71" s="1">
+        <v>280</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G71" s="1">
+        <v>5.3768840000000002E-3</v>
+      </c>
+      <c r="H71">
+        <v>0.188888889</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4.3636400000000001E-4</v>
+      </c>
+      <c r="C72" s="1">
+        <v>280</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G72" s="1">
+        <v>8.2412059999999992E-3</v>
+      </c>
+      <c r="H72">
+        <v>0.215708812</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="1">
+        <v>5.4891800000000002E-4</v>
+      </c>
+      <c r="C73" s="1">
+        <v>280</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1.0502513E-2</v>
+      </c>
+      <c r="H73">
+        <v>0.215708812</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="1">
+        <v>7.1515200000000004E-4</v>
+      </c>
+      <c r="C74" s="1">
+        <v>280</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1.201005E-2</v>
+      </c>
+      <c r="H74">
+        <v>0.195019157</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1.0147190000000001E-3</v>
+      </c>
+      <c r="C75" s="1">
+        <v>280</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1.201005E-2</v>
+      </c>
+      <c r="H75">
+        <v>0.18735632199999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="1">
+        <v>1.4943720000000001E-3</v>
+      </c>
+      <c r="C76" s="1">
+        <v>280</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G76" s="1">
+        <v>1.1708543E-2</v>
+      </c>
+      <c r="H76">
+        <v>0.18429118799999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2.5800900000000002E-4</v>
+      </c>
+      <c r="C77" s="1">
+        <v>280</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E77" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F77" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1.1557789000000001E-2</v>
+      </c>
+      <c r="H77">
+        <v>0.44636015299999998</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2.90909E-4</v>
+      </c>
+      <c r="C78" s="1">
+        <v>280</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E78" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F78" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1.2462312E-2</v>
+      </c>
+      <c r="H78">
+        <v>0.51685823799999997</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3.3419899999999998E-4</v>
+      </c>
+      <c r="C79" s="1">
+        <v>280</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E79" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F79" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1.8643216000000001E-2</v>
+      </c>
+      <c r="H79">
+        <v>0.46015325699999998</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3.9307399999999998E-4</v>
+      </c>
+      <c r="C80" s="1">
+        <v>280</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E80" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2.9346733999999999E-2</v>
+      </c>
+      <c r="H80">
+        <v>0.493103448</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4.7445899999999999E-4</v>
+      </c>
+      <c r="C81" s="1">
+        <v>280</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E81" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G81" s="1">
+        <v>2.6783919999999999E-2</v>
+      </c>
+      <c r="H81">
+        <v>0.46015325699999998</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="1">
+        <v>5.9913399999999997E-4</v>
+      </c>
+      <c r="C82" s="1">
+        <v>280</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E82" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F82" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2.6783919999999999E-2</v>
+      </c>
+      <c r="H82">
+        <v>0.37739463600000001</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="1">
+        <v>7.7229399999999998E-4</v>
+      </c>
+      <c r="C83" s="1">
+        <v>280</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E83" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2.6633166E-2</v>
+      </c>
+      <c r="H83">
+        <v>0.29310344799999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>1.0320349999999999E-3</v>
+      </c>
+      <c r="C84">
+        <v>280</v>
+      </c>
+      <c r="D84">
+        <v>0.15</v>
+      </c>
+      <c r="E84">
+        <v>-1</v>
+      </c>
+      <c r="F84">
+        <v>-1</v>
+      </c>
+      <c r="G84">
+        <v>2.3316582999999998E-2</v>
+      </c>
+      <c r="H84">
+        <v>0.236398467</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85">
+        <v>1.314286E-3</v>
+      </c>
+      <c r="C85">
+        <v>280</v>
+      </c>
+      <c r="D85">
+        <v>0.15</v>
+      </c>
+      <c r="E85">
+        <v>-1</v>
+      </c>
+      <c r="F85">
+        <v>-1</v>
+      </c>
+      <c r="G85">
+        <v>1.8492462000000001E-2</v>
+      </c>
+      <c r="H85">
+        <v>0.21340996200000001</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C86">
+        <v>280</v>
+      </c>
+      <c r="D86">
+        <v>0.2</v>
+      </c>
+      <c r="E86">
+        <v>-1</v>
+      </c>
+      <c r="F86">
+        <v>0.64973261999999998</v>
+      </c>
+      <c r="G86">
+        <v>-1</v>
+      </c>
+      <c r="H86">
+        <v>-1</v>
+      </c>
+      <c r="I86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C87">
+        <v>280</v>
+      </c>
+      <c r="D87">
+        <v>0.2</v>
+      </c>
+      <c r="E87">
+        <v>-1</v>
+      </c>
+      <c r="F87">
+        <v>0.91657754000000002</v>
+      </c>
+      <c r="G87">
+        <v>-1</v>
+      </c>
+      <c r="H87">
+        <v>-1</v>
+      </c>
+      <c r="I87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C88">
+        <v>280</v>
+      </c>
+      <c r="D88">
+        <v>0.2</v>
+      </c>
+      <c r="E88">
+        <v>-1</v>
+      </c>
+      <c r="F88">
+        <v>0.97754010700000005</v>
+      </c>
+      <c r="G88">
+        <v>-1</v>
+      </c>
+      <c r="H88">
+        <v>-1</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C89">
+        <v>280</v>
+      </c>
+      <c r="D89">
+        <v>0.2</v>
+      </c>
+      <c r="E89">
+        <v>-1</v>
+      </c>
+      <c r="F89">
+        <v>0.98716577500000002</v>
+      </c>
+      <c r="G89">
+        <v>-1</v>
+      </c>
+      <c r="H89">
+        <v>-1</v>
+      </c>
+      <c r="I89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C90">
+        <v>280</v>
+      </c>
+      <c r="D90">
+        <v>0.2</v>
+      </c>
+      <c r="E90">
+        <v>-1</v>
+      </c>
+      <c r="F90">
+        <v>0.99251336899999998</v>
+      </c>
+      <c r="G90">
+        <v>-1</v>
+      </c>
+      <c r="H90">
+        <v>-1</v>
+      </c>
+      <c r="I90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C91">
+        <v>280</v>
+      </c>
+      <c r="D91">
+        <v>0.05</v>
+      </c>
+      <c r="E91">
+        <v>-1</v>
+      </c>
+      <c r="F91">
+        <v>0.89470899500000001</v>
+      </c>
+      <c r="G91">
+        <v>-1</v>
+      </c>
+      <c r="H91">
+        <v>-1</v>
+      </c>
+      <c r="I91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C92">
+        <v>280</v>
+      </c>
+      <c r="D92">
+        <v>0.05</v>
+      </c>
+      <c r="E92">
+        <v>-1</v>
+      </c>
+      <c r="F92">
+        <v>0.91216931199999995</v>
+      </c>
+      <c r="G92">
+        <v>-1</v>
+      </c>
+      <c r="H92">
+        <v>-1</v>
+      </c>
+      <c r="I92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="C93">
+        <v>280</v>
+      </c>
+      <c r="D93">
+        <v>0.05</v>
+      </c>
+      <c r="E93">
+        <v>-1</v>
+      </c>
+      <c r="F93">
+        <v>0.96137566100000005</v>
+      </c>
+      <c r="G93">
+        <v>-1</v>
+      </c>
+      <c r="H93">
+        <v>-1</v>
+      </c>
+      <c r="I93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C94">
+        <v>280</v>
+      </c>
+      <c r="D94">
+        <v>0.05</v>
+      </c>
+      <c r="E94">
+        <v>-1</v>
+      </c>
+      <c r="F94">
+        <v>0.98148148099999999</v>
+      </c>
+      <c r="G94">
+        <v>-1</v>
+      </c>
+      <c r="H94">
+        <v>-1</v>
+      </c>
+      <c r="I94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <v>3.5E-4</v>
+      </c>
+      <c r="C95">
+        <v>280</v>
+      </c>
+      <c r="D95">
+        <v>0.05</v>
+      </c>
+      <c r="E95">
+        <v>-1</v>
+      </c>
+      <c r="F95">
+        <v>0.98994709000000003</v>
+      </c>
+      <c r="G95">
+        <v>-1</v>
+      </c>
+      <c r="H95">
+        <v>-1</v>
+      </c>
+      <c r="I95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C96">
+        <v>280</v>
+      </c>
+      <c r="D96">
+        <v>0.1</v>
+      </c>
+      <c r="E96">
+        <v>-1</v>
+      </c>
+      <c r="F96">
+        <v>0.89894179900000004</v>
+      </c>
+      <c r="G96">
+        <v>-1</v>
+      </c>
+      <c r="H96">
+        <v>-1</v>
+      </c>
+      <c r="I96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="C97">
+        <v>2050</v>
+      </c>
+      <c r="D97">
+        <v>0.3</v>
+      </c>
+      <c r="E97">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F97">
+        <v>-1</v>
+      </c>
+      <c r="G97">
+        <v>-1</v>
+      </c>
+      <c r="H97">
+        <v>-1</v>
+      </c>
+      <c r="I97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98">
+        <v>9.0499999999999999E-4</v>
+      </c>
+      <c r="C98">
+        <v>2350</v>
+      </c>
+      <c r="D98">
+        <v>0.5</v>
+      </c>
+      <c r="E98">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F98">
+        <v>-1</v>
+      </c>
+      <c r="G98">
+        <v>-1</v>
+      </c>
+      <c r="H98">
+        <v>-1</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>5</v>
       </c>
-      <c r="B70" s="1">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="C70" s="1">
-        <v>2050</v>
-      </c>
-      <c r="D70" s="1">
+      <c r="B99">
+        <v>6.3250000000000003E-4</v>
+      </c>
+      <c r="C99">
+        <v>1600</v>
+      </c>
+      <c r="D99">
         <v>0.3</v>
       </c>
-      <c r="E70" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="E99">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F99">
+        <v>-1</v>
+      </c>
+      <c r="G99">
+        <v>-1</v>
+      </c>
+      <c r="H99">
+        <v>-1</v>
+      </c>
+      <c r="I99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="1">
-        <v>9.0499999999999999E-4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>2350</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="B100">
+        <v>6.0749999999999997E-4</v>
+      </c>
+      <c r="C100">
+        <v>1500</v>
+      </c>
+      <c r="D100">
+        <v>0.3</v>
+      </c>
+      <c r="E100">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F100">
+        <v>-1</v>
+      </c>
+      <c r="G100">
+        <v>-1</v>
+      </c>
+      <c r="H100">
+        <v>-1</v>
+      </c>
+      <c r="I100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101">
+        <v>7.3800000000000005E-4</v>
+      </c>
+      <c r="C101">
+        <v>1450</v>
+      </c>
+      <c r="D101">
         <v>0.5</v>
       </c>
-      <c r="E71" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="E101">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F101">
+        <v>-1</v>
+      </c>
+      <c r="G101">
+        <v>-1</v>
+      </c>
+      <c r="H101">
+        <v>-1</v>
+      </c>
+      <c r="I101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102">
+        <v>8.6499999999999999E-4</v>
+      </c>
+      <c r="C102">
+        <v>1850</v>
+      </c>
+      <c r="D102">
+        <v>0.5</v>
+      </c>
+      <c r="E102">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F102">
+        <v>-1</v>
+      </c>
+      <c r="G102">
+        <v>-1</v>
+      </c>
+      <c r="H102">
+        <v>-1</v>
+      </c>
+      <c r="I102">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="1">
-        <v>6.3250000000000003E-4</v>
-      </c>
-      <c r="C72" s="1">
+      <c r="B103">
+        <v>6.2750000000000002E-4</v>
+      </c>
+      <c r="C103">
         <v>1600</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D103">
         <v>0.3</v>
       </c>
-      <c r="E72" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="E103">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F103">
+        <v>-1</v>
+      </c>
+      <c r="G103">
+        <v>-1</v>
+      </c>
+      <c r="H103">
+        <v>-1</v>
+      </c>
+      <c r="I103">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>6</v>
       </c>
-      <c r="B73" s="1">
-        <v>6.0749999999999997E-4</v>
-      </c>
-      <c r="C73" s="1">
+      <c r="B104">
+        <v>5.8500000000000002E-4</v>
+      </c>
+      <c r="C104">
+        <v>1450</v>
+      </c>
+      <c r="D104">
+        <v>0.3</v>
+      </c>
+      <c r="E104">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F104">
+        <v>-1</v>
+      </c>
+      <c r="G104">
+        <v>-1</v>
+      </c>
+      <c r="H104">
+        <v>-1</v>
+      </c>
+      <c r="I104">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105">
+        <v>7.0750000000000001E-4</v>
+      </c>
+      <c r="C105">
+        <v>1400</v>
+      </c>
+      <c r="D105">
+        <v>0.5</v>
+      </c>
+      <c r="E105">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F105">
+        <v>-1</v>
+      </c>
+      <c r="G105">
+        <v>-1</v>
+      </c>
+      <c r="H105">
+        <v>-1</v>
+      </c>
+      <c r="I105">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106">
+        <v>6.3500000000000004E-4</v>
+      </c>
+      <c r="C106">
+        <v>1150</v>
+      </c>
+      <c r="D106">
+        <v>0.5</v>
+      </c>
+      <c r="E106">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F106">
+        <v>-1</v>
+      </c>
+      <c r="G106">
+        <v>-1</v>
+      </c>
+      <c r="H106">
+        <v>-1</v>
+      </c>
+      <c r="I106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107">
+        <v>6.6750000000000002E-4</v>
+      </c>
+      <c r="C107">
+        <v>1600</v>
+      </c>
+      <c r="D107">
+        <v>0.3</v>
+      </c>
+      <c r="E107">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F107">
+        <v>-1</v>
+      </c>
+      <c r="G107">
+        <v>-1</v>
+      </c>
+      <c r="H107">
+        <v>-1</v>
+      </c>
+      <c r="I107">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>7</v>
+      </c>
+      <c r="B108">
+        <v>6.3029999999999998E-4</v>
+      </c>
+      <c r="C108">
         <v>1500</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D108">
         <v>0.3</v>
       </c>
-      <c r="E73" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="1">
-        <v>7.3800000000000005E-4</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1450</v>
-      </c>
-      <c r="D74" s="1">
+      <c r="E108">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F108">
+        <v>-1</v>
+      </c>
+      <c r="G108">
+        <v>-1</v>
+      </c>
+      <c r="H108">
+        <v>-1</v>
+      </c>
+      <c r="I108">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109">
+        <v>7.2250000000000005E-4</v>
+      </c>
+      <c r="C109">
+        <v>1350</v>
+      </c>
+      <c r="D109">
         <v>0.5</v>
       </c>
-      <c r="E74" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="1">
-        <v>8.6499999999999999E-4</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1850</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="E109">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F109">
+        <v>-1</v>
+      </c>
+      <c r="G109">
+        <v>-1</v>
+      </c>
+      <c r="H109">
+        <v>-1</v>
+      </c>
+      <c r="I109">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110">
+        <v>6.7250000000000003E-4</v>
+      </c>
+      <c r="C110">
+        <v>1200</v>
+      </c>
+      <c r="D110">
         <v>0.5</v>
       </c>
-      <c r="E75" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="1">
-        <v>6.2750000000000002E-4</v>
-      </c>
-      <c r="C76" s="1">
-        <v>1600</v>
-      </c>
-      <c r="D76" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E76" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" s="1">
-        <v>5.8500000000000002E-4</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1450</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E77" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="1">
-        <v>7.0750000000000001E-4</v>
-      </c>
-      <c r="C78" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D78" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E78" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F78" s="1">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="1">
-        <v>6.3500000000000004E-4</v>
-      </c>
-      <c r="C79" s="1">
-        <v>1150</v>
-      </c>
-      <c r="D79" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E79" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B80" s="1">
-        <v>6.6750000000000002E-4</v>
-      </c>
-      <c r="C80" s="1">
-        <v>1600</v>
-      </c>
-      <c r="D80" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E80" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-      <c r="G80" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B81" s="1">
-        <v>6.3029999999999998E-4</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1500</v>
-      </c>
-      <c r="D81" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E81" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" s="1">
-        <v>7.2250000000000005E-4</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1350</v>
-      </c>
-      <c r="D82" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E82" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B83" s="1">
-        <v>6.7250000000000003E-4</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1200</v>
-      </c>
-      <c r="D83" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E83" s="1">
-        <v>5.9087441444048081E-3</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
+      <c r="E110">
+        <v>5.9087439999999996E-3</v>
+      </c>
+      <c r="F110">
+        <v>-1</v>
+      </c>
+      <c r="G110">
+        <v>-1</v>
+      </c>
+      <c r="H110">
+        <v>-1</v>
+      </c>
+      <c r="I110">
         <v>-1</v>
       </c>
     </row>
@@ -2432,30 +3686,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>8.0239500000000002E-4</v>
@@ -2481,7 +3735,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>6.91448E-4</v>
@@ -2507,7 +3761,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>5.95906E-4</v>
@@ -2533,7 +3787,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>6.2088699999999998E-4</v>
@@ -2559,7 +3813,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>5.9944000000000002E-4</v>
@@ -2585,7 +3839,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>6.1677100000000001E-4</v>
@@ -2611,7 +3865,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>5.9561800000000002E-4</v>
@@ -2637,7 +3891,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>5.7893599999999995E-4</v>
@@ -2663,7 +3917,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>4.9265500000000005E-4</v>
@@ -2689,7 +3943,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>9.1292700000000001E-4</v>
@@ -2715,7 +3969,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>9.8825999999999992E-4</v>
@@ -2741,7 +3995,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>9.4360899999999998E-4</v>
@@ -2767,7 +4021,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>7.7894200000000002E-4</v>
@@ -2793,7 +4047,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>7.8108599999999995E-4</v>
@@ -2819,7 +4073,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>7.4180700000000003E-4</v>
@@ -2845,7 +4099,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>6.3737199999999998E-4</v>
@@ -2871,7 +4125,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>6.3181200000000004E-4</v>
@@ -2897,7 +4151,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>5.6106099999999996E-4</v>
@@ -2923,7 +4177,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>8.0128199999999995E-4</v>
@@ -2949,7 +4203,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>8.1002600000000004E-4</v>
@@ -2975,7 +4229,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>7.8814599999999999E-4</v>
@@ -3001,7 +4255,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23">
         <v>7.1302300000000002E-4</v>
@@ -3027,7 +4281,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>6.9510100000000005E-4</v>
@@ -3053,7 +4307,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>7.0127399999999999E-4</v>
@@ -3079,7 +4333,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26">
         <v>7.3645500000000001E-4</v>
@@ -3105,7 +4359,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27">
         <v>7.2969899999999999E-4</v>
@@ -3131,7 +4385,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28">
         <v>6.9667700000000004E-4</v>
@@ -3157,7 +4411,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>6.4236199999999995E-4</v>
@@ -3183,7 +4437,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30">
         <v>6.8012400000000005E-4</v>
@@ -3209,7 +4463,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>5.9216200000000003E-4</v>
@@ -3235,7 +4489,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32">
         <v>5.9390400000000002E-4</v>
@@ -3261,7 +4515,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>5.8364699999999996E-4</v>
@@ -3287,7 +4541,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>5.1002800000000004E-4</v>
@@ -3313,7 +4567,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>8.0508499999999998E-4</v>
@@ -3339,7 +4593,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>7.6724599999999997E-4</v>
@@ -3365,7 +4619,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>7.0617800000000001E-4</v>
@@ -3391,7 +4645,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>6.90491E-4</v>
@@ -3417,7 +4671,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B39">
         <v>6.6872600000000002E-4</v>
@@ -3443,7 +4697,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>6.0886200000000005E-4</v>
@@ -3469,7 +4723,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41">
         <v>5.8638600000000005E-4</v>
@@ -3495,7 +4749,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42">
         <v>5.8743599999999999E-4</v>
@@ -3521,7 +4775,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43">
         <v>5.2147200000000004E-4</v>
@@ -3547,7 +4801,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44">
         <v>7.3430900000000005E-4</v>
@@ -3573,7 +4827,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45">
         <v>6.9824100000000005E-4</v>
@@ -3599,7 +4853,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46">
         <v>6.8666599999999995E-4</v>
@@ -3625,7 +4879,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47">
         <v>6.0317599999999997E-4</v>
@@ -3651,7 +4905,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48">
         <v>6.0375999999999995E-4</v>
@@ -3677,7 +4931,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49">
         <v>7.2423300000000002E-4</v>
@@ -3703,7 +4957,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50">
         <v>8.1175500000000005E-4</v>
@@ -3729,7 +4983,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51">
         <v>7.9663900000000003E-4</v>
@@ -3755,7 +5009,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52">
         <v>7.5900900000000005E-4</v>
@@ -3781,7 +5035,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53">
         <v>7.5096099999999997E-4</v>
@@ -3807,7 +5061,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54">
         <v>7.63323E-4</v>
@@ -3833,7 +5087,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55">
         <v>7.2370699999999997E-4</v>
@@ -3859,7 +5113,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56">
         <v>7.0107399999999999E-4</v>
@@ -3885,7 +5139,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B57">
         <v>7.1206199999999996E-4</v>
@@ -3911,7 +5165,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58">
         <v>6.9931300000000002E-4</v>
@@ -3937,7 +5191,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>7.7304999999999995E-4</v>
@@ -3963,7 +5217,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>7.7200999999999995E-4</v>
@@ -3989,7 +5243,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B61">
         <v>7.2866900000000004E-4</v>
@@ -4015,7 +5269,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B62">
         <v>7.7559000000000005E-4</v>
@@ -4041,7 +5295,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B63">
         <v>7.6392500000000004E-4</v>
@@ -4067,7 +5321,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64">
         <v>7.2654800000000004E-4</v>
@@ -4093,7 +5347,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B65">
         <v>7.2222900000000001E-4</v>
@@ -4119,7 +5373,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B66">
         <v>7.1244500000000003E-4</v>
@@ -4145,7 +5399,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B67">
         <v>7.1245100000000001E-4</v>
@@ -4171,7 +5425,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B68">
         <v>7.3421300000000005E-4</v>
@@ -4197,7 +5451,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69">
         <v>7.4564200000000003E-4</v>
@@ -4223,7 +5477,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70">
         <v>7.5361500000000001E-4</v>
@@ -4249,7 +5503,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B71">
         <v>6.6505100000000005E-4</v>
@@ -4275,7 +5529,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B72">
         <v>6.3372099999999996E-4</v>
@@ -4301,7 +5555,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73">
         <v>6.1875899999999998E-4</v>
@@ -4327,7 +5581,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74">
         <v>6.2012899999999997E-4</v>
@@ -4353,7 +5607,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B75">
         <v>6.5113400000000004E-4</v>
@@ -4379,7 +5633,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76">
         <v>6.6688800000000003E-4</v>
@@ -4405,7 +5659,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B77">
         <v>5.7892299999999996E-4</v>
@@ -4431,7 +5685,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78">
         <v>5.6844399999999998E-4</v>
@@ -4457,7 +5711,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B79">
         <v>5.5183900000000004E-4</v>
@@ -4483,7 +5737,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80">
         <v>5.2785099999999997E-4</v>
@@ -4509,7 +5763,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81">
         <v>5.4509199999999995E-4</v>
@@ -4535,7 +5789,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82">
         <v>5.5842000000000001E-4</v>
@@ -4561,7 +5815,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83">
         <v>8.1662800000000002E-4</v>
@@ -4587,7 +5841,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B84">
         <v>8.2480499999999996E-4</v>
@@ -4613,7 +5867,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B85">
         <v>7.6000999999999998E-4</v>
@@ -4639,7 +5893,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B86">
         <v>7.4356499999999996E-4</v>
@@ -4665,7 +5919,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87">
         <v>7.9224700000000005E-4</v>
@@ -4691,7 +5945,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88">
         <v>8.5975099999999996E-4</v>
@@ -4717,7 +5971,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89">
         <v>7.0235800000000004E-4</v>
@@ -4743,7 +5997,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B90">
         <v>6.7399699999999996E-4</v>
@@ -4769,7 +6023,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91">
         <v>6.1247500000000002E-4</v>
@@ -4795,7 +6049,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92">
         <v>5.9411399999999997E-4</v>
@@ -4821,7 +6075,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93">
         <v>6.1466400000000001E-4</v>
@@ -4847,7 +6101,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94">
         <v>6.6162899999999995E-4</v>
@@ -4873,7 +6127,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B95">
         <v>5.9813300000000004E-4</v>
@@ -4899,7 +6153,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96">
         <v>5.8159900000000003E-4</v>
@@ -4925,7 +6179,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B97">
         <v>5.2616900000000005E-4</v>
@@ -4951,7 +6205,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98">
         <v>5.04985E-4</v>
@@ -4977,7 +6231,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B99">
         <v>5.1139399999999998E-4</v>
@@ -5003,7 +6257,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B100">
         <v>5.3669500000000001E-4</v>
@@ -5029,7 +6283,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101">
         <v>7.1749599999999998E-4</v>
@@ -5055,7 +6309,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B102">
         <v>7.0684700000000003E-4</v>
@@ -5081,7 +6335,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B103">
         <v>6.9391699999999995E-4</v>
@@ -5107,7 +6361,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B104">
         <v>6.8117199999999996E-4</v>
@@ -5133,7 +6387,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105">
         <v>6.7872799999999997E-4</v>
@@ -5159,7 +6413,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B106">
         <v>7.1950099999999999E-4</v>
@@ -5185,7 +6439,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B107">
         <v>6.1575900000000001E-4</v>
@@ -5211,7 +6465,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108">
         <v>6.0389799999999996E-4</v>
@@ -5237,7 +6491,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109">
         <v>5.7284199999999995E-4</v>
@@ -5263,7 +6517,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110">
         <v>5.5556900000000001E-4</v>
@@ -5289,7 +6543,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111">
         <v>5.6215900000000001E-4</v>
@@ -5315,7 +6569,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B112">
         <v>5.4408699999999996E-4</v>
@@ -5341,7 +6595,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B113">
         <v>4.5836E-4</v>
@@ -5367,7 +6621,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114">
         <v>3.0230799999999999E-4</v>
@@ -5393,7 +6647,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B115">
         <v>2.0462099999999999E-4</v>
@@ -5419,7 +6673,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B116">
         <v>5.2193699999999999E-4</v>
@@ -5445,7 +6699,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B117">
         <v>4.4927699999999999E-4</v>
@@ -5471,7 +6725,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B118">
         <v>2.8546399999999998E-4</v>
@@ -5497,7 +6751,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B119">
         <v>2.4194099999999999E-4</v>
@@ -5523,7 +6777,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B120">
         <v>6.5725699999999996E-4</v>
@@ -5549,7 +6803,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B121">
         <v>5.2808399999999995E-4</v>
@@ -5575,7 +6829,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B122">
         <v>3.5915099999999999E-4</v>
@@ -5601,7 +6855,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B123">
         <v>3.1127999999999999E-4</v>
@@ -5627,7 +6881,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B124">
         <v>4.7841700000000002E-4</v>
@@ -5653,7 +6907,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B125">
         <v>4.9956000000000002E-4</v>
@@ -5679,7 +6933,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B126">
         <v>3.2126799999999999E-4</v>
@@ -5705,7 +6959,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B127">
         <v>2.7020599999999999E-4</v>
@@ -5731,7 +6985,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B128">
         <v>4.9661200000000001E-4</v>
@@ -5757,7 +7011,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B129">
         <v>5.3819899999999995E-4</v>
@@ -5783,7 +7037,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B130">
         <v>3.5480499999999998E-4</v>
@@ -5809,7 +7063,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B131">
         <v>3.0498E-4</v>
@@ -5835,7 +7089,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B132">
         <v>5.7161400000000002E-4</v>
@@ -5861,7 +7115,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B133">
         <v>6.1787599999999995E-4</v>
@@ -5887,7 +7141,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B134">
         <v>4.3410900000000001E-4</v>
@@ -5913,7 +7167,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B135">
         <v>3.79055E-4</v>
@@ -5939,7 +7193,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B136">
         <v>5.0153199999999995E-4</v>
@@ -5965,7 +7219,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B137">
         <v>5.0392299999999998E-4</v>
@@ -5991,7 +7245,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B138">
         <v>3.4781999999999999E-4</v>
@@ -6017,7 +7271,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B139">
         <v>2.7612200000000001E-4</v>
@@ -6043,7 +7297,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B140">
         <v>5.4036500000000001E-4</v>
@@ -6069,7 +7323,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B141">
         <v>5.2480699999999996E-4</v>
@@ -6095,7 +7349,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B142">
         <v>3.9074900000000002E-4</v>
@@ -6121,7 +7375,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B143">
         <v>3.3084899999999998E-4</v>
@@ -6147,7 +7401,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B144">
         <v>5.6678999999999996E-4</v>
@@ -6173,7 +7427,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B145">
         <v>6.0097700000000004E-4</v>
@@ -6199,7 +7453,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B146">
         <v>4.8327E-4</v>
@@ -6225,7 +7479,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B147">
         <v>4.9274500000000005E-4</v>
@@ -6251,7 +7505,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B148">
         <v>3.2658299999999997E-4</v>
@@ -6277,7 +7531,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B149">
         <v>2.25011E-4</v>
@@ -6303,7 +7557,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B150">
         <v>5.0822400000000005E-4</v>
@@ -6329,7 +7583,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B151">
         <v>3.85542E-4</v>
@@ -6355,7 +7609,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B152">
         <v>2.7817599999999999E-4</v>
@@ -6381,7 +7635,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B153">
         <v>5.7829300000000001E-4</v>
@@ -6407,7 +7661,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B154">
         <v>4.49791E-4</v>
@@ -6433,7 +7687,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155">
         <v>3.38769E-4</v>
@@ -6459,7 +7713,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B156">
         <v>5.0523799999999998E-4</v>
@@ -6485,7 +7739,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B157">
         <v>3.7785800000000001E-4</v>
@@ -6511,7 +7765,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B158">
         <v>2.8554999999999997E-4</v>
@@ -6537,7 +7791,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B159">
         <v>4.70111E-4</v>
@@ -6563,7 +7817,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B160">
         <v>4.27133E-4</v>
@@ -6589,7 +7843,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B161">
         <v>3.3823700000000002E-4</v>
@@ -6615,7 +7869,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B162">
         <v>5.7063399999999998E-4</v>
@@ -6641,7 +7895,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B163">
         <v>5.2623700000000004E-4</v>
@@ -6667,7 +7921,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B164">
         <v>3.8766700000000001E-4</v>
@@ -6693,7 +7947,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B165">
         <v>4.8464800000000001E-4</v>
@@ -6719,7 +7973,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B166">
         <v>4.0982300000000002E-4</v>
@@ -6745,7 +7999,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B167">
         <v>3.1294599999999998E-4</v>
@@ -6771,7 +8025,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B168">
         <v>5.2144500000000005E-4</v>
@@ -6797,7 +8051,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B169">
         <v>4.6947900000000002E-4</v>
@@ -6823,7 +8077,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B170">
         <v>3.4246299999999999E-4</v>
@@ -6849,7 +8103,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B171">
         <v>5.7827599999999996E-4</v>
@@ -6875,7 +8129,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B172">
         <v>5.4361800000000005E-4</v>
@@ -6901,7 +8155,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B173">
         <v>3.1115599999999999E-4</v>
@@ -6927,7 +8181,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B174">
         <v>4.84589E-4</v>
@@ -6953,7 +8207,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B175">
         <v>4.84723E-4</v>
@@ -6979,7 +8233,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B176">
         <v>4.2448600000000001E-4</v>
@@ -7005,7 +8259,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B177">
         <v>3.21245E-4</v>
@@ -7031,7 +8285,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B178">
         <v>2.53766E-4</v>
@@ -7057,7 +8311,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B179">
         <v>2.18042E-4</v>
@@ -7083,7 +8337,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B180">
         <v>2.04692E-4</v>
@@ -7109,7 +8363,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B181">
         <v>5.2550700000000004E-4</v>
@@ -7135,7 +8389,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B182">
         <v>5.3621300000000001E-4</v>
@@ -7161,7 +8415,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B183">
         <v>4.7342700000000001E-4</v>
@@ -7187,7 +8441,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B184">
         <v>3.60226E-4</v>
@@ -7213,7 +8467,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B185">
         <v>2.6574900000000002E-4</v>
@@ -7239,7 +8493,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B186">
         <v>2.40091E-4</v>
@@ -7265,7 +8519,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187">
         <v>2.2167000000000001E-4</v>
@@ -7291,7 +8545,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B188">
         <v>6.5489400000000005E-4</v>
@@ -7317,7 +8571,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B189">
         <v>6.7796600000000001E-4</v>
@@ -7343,7 +8597,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B190">
         <v>5.4967899999999997E-4</v>
@@ -7369,7 +8623,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B191">
         <v>3.9895000000000002E-4</v>
@@ -7395,7 +8649,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B192">
         <v>3.54428E-4</v>
@@ -7421,7 +8675,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B193">
         <v>3.3188100000000002E-4</v>
@@ -7447,7 +8701,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B194">
         <v>3.1751099999999998E-4</v>
@@ -7473,7 +8727,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B195">
         <v>5.18681E-4</v>
@@ -7499,7 +8753,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B196">
         <v>4.9001800000000005E-4</v>
@@ -7525,7 +8779,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B197">
         <v>5.0937400000000005E-4</v>
@@ -7551,7 +8805,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B198">
         <v>3.65507E-4</v>
@@ -7577,7 +8831,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B199">
         <v>3.0124600000000002E-4</v>
@@ -7603,7 +8857,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B200">
         <v>2.8024199999999999E-4</v>
@@ -7629,7 +8883,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B201">
         <v>2.7145000000000001E-4</v>
@@ -7655,7 +8909,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B202">
         <v>4.9716300000000001E-4</v>
@@ -7681,7 +8935,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B203">
         <v>4.92466E-4</v>
@@ -7707,7 +8961,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B204">
         <v>5.3962499999999996E-4</v>
@@ -7733,7 +8987,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B205">
         <v>4.2028999999999998E-4</v>
@@ -7759,7 +9013,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B206">
         <v>3.3060400000000002E-4</v>
@@ -7785,7 +9039,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B207">
         <v>3.0584500000000001E-4</v>
@@ -7811,7 +9065,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B208">
         <v>2.9125199999999998E-4</v>
@@ -7837,7 +9091,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B209">
         <v>5.6804700000000002E-4</v>
@@ -7863,7 +9117,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B210">
         <v>5.8126300000000005E-4</v>
@@ -7889,7 +9143,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B211">
         <v>6.2164100000000003E-4</v>
@@ -7915,7 +9169,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B212">
         <v>4.8212199999999998E-4</v>
@@ -7941,7 +9195,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B213">
         <v>3.6832299999999999E-4</v>
@@ -7967,7 +9221,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B214">
         <v>3.2732300000000002E-4</v>
@@ -7993,7 +9247,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B215">
         <v>3.2196200000000002E-4</v>
@@ -8019,7 +9273,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B216">
         <v>4.8343099999999999E-4</v>
@@ -8045,7 +9299,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B217">
         <v>4.7872600000000001E-4</v>
@@ -8071,7 +9325,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B218">
         <v>4.4455299999999998E-4</v>
@@ -8097,7 +9351,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B219">
         <v>3.8442400000000002E-4</v>
@@ -8123,7 +9377,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B220">
         <v>3.2228600000000002E-4</v>
@@ -8149,7 +9403,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B221">
         <v>2.9366100000000002E-4</v>
@@ -8175,7 +9429,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B222">
         <v>2.7240599999999999E-4</v>
@@ -8201,7 +9455,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B223">
         <v>5.1822599999999999E-4</v>
@@ -8227,7 +9481,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B224">
         <v>5.0449399999999997E-4</v>
@@ -8253,7 +9507,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B225">
         <v>5.07009E-4</v>
@@ -8279,7 +9533,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B226">
         <v>4.29863E-4</v>
@@ -8305,7 +9559,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B227">
         <v>3.4672300000000001E-4</v>
@@ -8331,7 +9585,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B228">
         <v>3.13467E-4</v>
@@ -8357,7 +9611,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B229">
         <v>3.0008900000000002E-4</v>
@@ -8383,7 +9637,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B230">
         <v>5.6569300000000003E-4</v>
@@ -8409,7 +9663,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B231">
         <v>5.6636299999999996E-4</v>
@@ -8435,7 +9689,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B232">
         <v>5.5780800000000002E-4</v>
@@ -8461,7 +9715,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B233">
         <v>4.9915300000000001E-4</v>
@@ -8487,7 +9741,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B234">
         <v>4.11395E-4</v>
@@ -8513,7 +9767,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B235">
         <v>3.53161E-4</v>
@@ -8539,7 +9793,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B236">
         <v>4.7270299999999999E-4</v>
@@ -8565,7 +9819,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B237">
         <v>4.6852800000000001E-4</v>
@@ -8591,7 +9845,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B238">
         <v>4.1679199999999998E-4</v>
@@ -8617,7 +9871,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B239">
         <v>3.2306400000000002E-4</v>
@@ -8643,7 +9897,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B240">
         <v>2.6293600000000002E-4</v>
@@ -8669,7 +9923,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B241">
         <v>2.2804999999999999E-4</v>
@@ -8695,7 +9949,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B242">
         <v>2.0938099999999999E-4</v>
@@ -8721,7 +9975,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B243">
         <v>5.0179900000000004E-4</v>
@@ -8747,7 +10001,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B244">
         <v>5.1192700000000002E-4</v>
@@ -8773,7 +10027,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B245">
         <v>4.3557999999999997E-4</v>
@@ -8799,7 +10053,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B246">
         <v>3.5768399999999999E-4</v>
@@ -8825,7 +10079,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B247">
         <v>2.76524E-4</v>
@@ -8851,7 +10105,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B248">
         <v>2.5828500000000002E-4</v>
@@ -8877,7 +10131,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B249">
         <v>2.3551900000000001E-4</v>
@@ -8903,7 +10157,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B250">
         <v>6.48955E-4</v>
@@ -8929,7 +10183,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B251">
         <v>6.1183099999999996E-4</v>
@@ -8955,7 +10209,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B252">
         <v>5.1377200000000001E-4</v>
@@ -8981,7 +10235,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B253">
         <v>4.3876499999999998E-4</v>
@@ -9007,7 +10261,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B254">
         <v>3.4390000000000001E-4</v>
@@ -9033,7 +10287,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B255">
         <v>3.10771E-4</v>
@@ -9059,7 +10313,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B256">
         <v>3.0146300000000002E-4</v>
@@ -9085,7 +10339,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B257">
         <v>4.7849500000000001E-4</v>
@@ -9111,7 +10365,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B258">
         <v>5.0275999999999999E-4</v>
@@ -9137,7 +10391,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B259">
         <v>5.1740599999999999E-4</v>
@@ -9163,7 +10417,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B260">
         <v>3.7951899999999998E-4</v>
@@ -9189,7 +10443,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B261">
         <v>3.2461399999999998E-4</v>
@@ -9215,7 +10469,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B262">
         <v>2.92262E-4</v>
@@ -9241,7 +10495,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B263">
         <v>2.7891199999999998E-4</v>
@@ -9267,7 +10521,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B264">
         <v>4.4690600000000001E-4</v>
@@ -9293,7 +10547,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B265">
         <v>4.50968E-4</v>
@@ -9319,7 +10573,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B266">
         <v>4.99166E-4</v>
@@ -9345,7 +10599,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B267">
         <v>4.3689199999999998E-4</v>
@@ -9371,7 +10625,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B268">
         <v>3.6157600000000001E-4</v>
@@ -9397,7 +10651,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B269">
         <v>3.40119E-4</v>
@@ -9423,7 +10677,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B270">
         <v>3.23025E-4</v>
@@ -9449,7 +10703,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B271">
         <v>5.6255699999999999E-4</v>
@@ -9475,7 +10729,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B272">
         <v>5.7886999999999999E-4</v>
@@ -9501,7 +10755,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B273">
         <v>6.3783199999999996E-4</v>
@@ -9527,7 +10781,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B274">
         <v>5.2629499999999997E-4</v>
@@ -9553,7 +10807,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B275">
         <v>4.5853300000000001E-4</v>
@@ -9579,7 +10833,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B276">
         <v>4.09391E-4</v>
@@ -9605,7 +10859,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B277">
         <v>4.1426199999999999E-4</v>
@@ -9631,7 +10885,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B278">
         <v>4.8616099999999998E-4</v>
@@ -9657,7 +10911,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B279">
         <v>4.9223300000000002E-4</v>
@@ -9683,7 +10937,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B280">
         <v>4.8966000000000005E-4</v>
@@ -9709,7 +10963,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B281">
         <v>4.1326699999999999E-4</v>
@@ -9735,7 +10989,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B282">
         <v>3.5472599999999998E-4</v>
@@ -9761,7 +11015,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B283">
         <v>3.0862499999999998E-4</v>
@@ -9787,7 +11041,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B284">
         <v>2.9086800000000001E-4</v>
@@ -9813,7 +11067,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B285">
         <v>5.3141199999999999E-4</v>
@@ -9839,7 +11093,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B286">
         <v>4.9130500000000004E-4</v>
@@ -9865,7 +11119,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B287">
         <v>4.9682100000000005E-4</v>
@@ -9891,7 +11145,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B288">
         <v>4.6433100000000001E-4</v>
@@ -9917,7 +11171,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B289">
         <v>4.0902799999999997E-4</v>
@@ -9943,7 +11197,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B290">
         <v>3.7444099999999999E-4</v>
@@ -9969,7 +11223,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B291">
         <v>3.3825899999999999E-4</v>
@@ -9995,7 +11249,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B292">
         <v>5.5933100000000004E-4</v>
@@ -10021,7 +11275,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B293">
         <v>5.6149699999999999E-4</v>
@@ -10047,7 +11301,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B294">
         <v>5.6852900000000002E-4</v>
@@ -10073,7 +11327,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B295">
         <v>5.5993099999999995E-4</v>
@@ -10099,7 +11353,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B296">
         <v>4.9463399999999998E-4</v>
@@ -10125,7 +11379,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B297">
         <v>4.6393200000000002E-4</v>
@@ -10151,7 +11405,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B298">
         <v>3.34135E-4</v>
@@ -10177,7 +11431,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B299">
         <v>4.2709099999999999E-4</v>
@@ -10203,7 +11457,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B300">
         <v>4.3149099999999999E-4</v>
@@ -10229,7 +11483,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B301">
         <v>3.9097999999999997E-4</v>
@@ -10255,7 +11509,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B302">
         <v>3.3918300000000001E-4</v>
@@ -10281,7 +11535,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B303">
         <v>2.9627499999999998E-4</v>
@@ -10307,7 +11561,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B304">
         <v>2.7603600000000001E-4</v>
@@ -10333,7 +11587,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B305">
         <v>2.64763E-4</v>
@@ -10359,7 +11613,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B306">
         <v>4.6320699999999999E-4</v>
@@ -10385,7 +11639,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B307">
         <v>4.5498799999999997E-4</v>
@@ -10411,7 +11665,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B308">
         <v>4.3629200000000002E-4</v>
@@ -10437,7 +11691,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B309">
         <v>3.9866700000000001E-4</v>
@@ -10463,7 +11717,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B310">
         <v>3.3655799999999999E-4</v>
@@ -10489,7 +11743,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B311">
         <v>3.0972699999999998E-4</v>
@@ -10515,7 +11769,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B312">
         <v>2.9860200000000003E-4</v>
@@ -10541,7 +11795,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B313">
         <v>5.8556899999999998E-4</v>
@@ -10567,7 +11821,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B314">
         <v>5.4085199999999998E-4</v>
@@ -10593,7 +11847,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B315">
         <v>5.2526299999999999E-4</v>
@@ -10619,7 +11873,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B316">
         <v>4.62764E-4</v>
@@ -10645,7 +11899,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B317">
         <v>3.65235E-4</v>
@@ -10671,7 +11925,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B318">
         <v>3.27277E-4</v>
@@ -10697,7 +11951,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B319">
         <v>3.14875E-4</v>
@@ -10723,7 +11977,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B320">
         <v>5.3314300000000003E-4</v>
@@ -10749,7 +12003,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B321">
         <v>5.1531000000000005E-4</v>
@@ -10775,7 +12029,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B322">
         <v>4.7795299999999998E-4</v>
@@ -10801,7 +12055,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B323">
         <v>3.6146000000000003E-4</v>
@@ -10827,7 +12081,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B324">
         <v>2.9615000000000002E-4</v>
@@ -10853,7 +12107,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B325">
         <v>2.6539199999999998E-4</v>
@@ -10879,7 +12133,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B326">
         <v>2.54348E-4</v>
@@ -10905,7 +12159,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B327">
         <v>5.5100500000000003E-4</v>
@@ -10931,7 +12185,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B328">
         <v>5.6732099999999997E-4</v>
@@ -10957,7 +12211,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B329">
         <v>5.3201699999999997E-4</v>
@@ -10983,7 +12237,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B330">
         <v>4.2268500000000001E-4</v>
@@ -11009,7 +12263,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B331">
         <v>3.2515300000000001E-4</v>
@@ -11035,7 +12289,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B332">
         <v>3.0033399999999997E-4</v>
@@ -11061,7 +12315,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B333">
         <v>2.8682499999999999E-4</v>
@@ -11087,7 +12341,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B334">
         <v>6.5962200000000001E-4</v>
@@ -11113,7 +12367,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B335">
         <v>6.4296000000000004E-4</v>
@@ -11139,7 +12393,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B336">
         <v>6.3665800000000002E-4</v>
@@ -11165,7 +12419,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B337">
         <v>6.3738399999999995E-4</v>
@@ -11191,7 +12445,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B338">
         <v>6.19449E-4</v>
@@ -11217,7 +12471,7 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B339">
         <v>4.9860200000000001E-4</v>
@@ -11243,7 +12497,7 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B340">
         <v>3.6904199999999998E-4</v>
@@ -11269,7 +12523,7 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B341">
         <v>3.21902E-4</v>
@@ -11295,7 +12549,7 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B342">
         <v>3.0918599999999998E-4</v>
@@ -11321,7 +12575,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B343">
         <v>4.85129E-4</v>
@@ -11347,7 +12601,7 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B344">
         <v>4.7428800000000001E-4</v>
@@ -11373,7 +12627,7 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B345">
         <v>4.58329E-4</v>
@@ -11399,7 +12653,7 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B346">
         <v>3.9580799999999999E-4</v>
@@ -11425,7 +12679,7 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B347">
         <v>3.3780799999999999E-4</v>
@@ -11451,7 +12705,7 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B348">
         <v>2.9499700000000002E-4</v>
@@ -11477,7 +12731,7 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B349">
         <v>2.7738399999999999E-4</v>
@@ -11503,7 +12757,7 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B350">
         <v>5.13668E-4</v>
@@ -11529,7 +12783,7 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B351">
         <v>5.3114999999999998E-4</v>
@@ -11555,7 +12809,7 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B352">
         <v>5.0897099999999999E-4</v>
@@ -11581,7 +12835,7 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B353">
         <v>4.3509100000000003E-4</v>
@@ -11607,7 +12861,7 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B354">
         <v>3.6169799999999998E-4</v>
@@ -11633,7 +12887,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B355">
         <v>3.3175099999999998E-4</v>
@@ -11659,7 +12913,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B356">
         <v>3.0890699999999998E-4</v>
@@ -11685,7 +12939,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B357">
         <v>5.4922200000000003E-4</v>
@@ -11711,7 +12965,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B358">
         <v>5.5316299999999996E-4</v>
@@ -11737,7 +12991,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B359">
         <v>5.5357200000000001E-4</v>
@@ -11763,7 +13017,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B360">
         <v>5.1459900000000002E-4</v>
@@ -11789,7 +13043,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B361">
         <v>4.2470700000000003E-4</v>
@@ -11815,7 +13069,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B362">
         <v>3.68847E-4</v>
@@ -11841,7 +13095,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B363">
         <v>3.3055999999999998E-4</v>
@@ -11880,30 +13134,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>2.0462099999999999E-4</v>
@@ -11929,7 +13183,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>6.5725699999999996E-4</v>
@@ -11955,7 +13209,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>3.1127999999999999E-4</v>
@@ -11981,7 +13235,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>4.4927699999999999E-4</v>
@@ -12007,7 +13261,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>5.4967899999999997E-4</v>
@@ -12033,7 +13287,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>3.38769E-4</v>
@@ -12059,7 +13313,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>2.4194099999999999E-4</v>
@@ -12085,7 +13339,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>4.9274500000000005E-4</v>
@@ -12111,7 +13365,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>6.1183099999999996E-4</v>
@@ -12137,7 +13391,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>3.9097999999999997E-4</v>
@@ -12163,7 +13417,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>2.2167000000000001E-4</v>
@@ -12189,7 +13443,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>6.7796600000000001E-4</v>
@@ -12215,7 +13469,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>2.54348E-4</v>
@@ -12241,7 +13495,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>8.0239500000000002E-4</v>
@@ -12267,7 +13521,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>5.0275999999999999E-4</v>
@@ -12293,7 +13547,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>5.9944000000000002E-4</v>
@@ -12319,7 +13573,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>7.1244500000000003E-4</v>
@@ -12345,7 +13599,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>3.7785800000000001E-4</v>
@@ -12371,7 +13625,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>5.6844399999999998E-4</v>
@@ -12397,7 +13651,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>6.5962200000000001E-4</v>
@@ -12423,7 +13677,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22">
         <v>7.5361500000000001E-4</v>
@@ -12449,7 +13703,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>3.65507E-4</v>
@@ -12475,7 +13729,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>3.21902E-4</v>
@@ -12501,7 +13755,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>4.4690600000000001E-4</v>
@@ -12527,7 +13781,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26">
         <v>2.6539199999999998E-4</v>
@@ -12553,7 +13807,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27">
         <v>2.7240599999999999E-4</v>
@@ -12579,7 +13833,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28">
         <v>5.6636299999999996E-4</v>
@@ -12605,7 +13859,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29">
         <v>4.4455299999999998E-4</v>
@@ -12631,7 +13885,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30">
         <v>3.4781999999999999E-4</v>
@@ -12657,7 +13911,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31">
         <v>3.0862499999999998E-4</v>
@@ -12683,7 +13937,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32">
         <v>3.9580799999999999E-4</v>
@@ -12709,7 +13963,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>4.85129E-4</v>
@@ -12735,7 +13989,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>4.7428800000000001E-4</v>
@@ -12761,7 +14015,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>3.4672300000000001E-4</v>
@@ -12787,7 +14041,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>5.7827599999999996E-4</v>
@@ -12813,7 +14067,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>4.6433100000000001E-4</v>
@@ -12839,7 +14093,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>4.11395E-4</v>
@@ -12865,7 +14119,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>3.13467E-4</v>
@@ -12891,7 +14145,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>7.2654800000000004E-4</v>
@@ -12917,7 +14171,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41">
         <v>8.1662800000000002E-4</v>
@@ -12943,7 +14197,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42">
         <v>8.5975099999999996E-4</v>
@@ -12969,7 +14223,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43">
         <v>7.0617800000000001E-4</v>
@@ -12995,7 +14249,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44">
         <v>6.3737199999999998E-4</v>
@@ -13021,7 +14275,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45">
         <v>5.2616900000000005E-4</v>
@@ -13047,7 +14301,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46">
         <v>7.4180700000000003E-4</v>
@@ -13073,7 +14327,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47">
         <v>9.1292700000000001E-4</v>
@@ -13099,7 +14353,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48">
         <v>9.4360899999999998E-4</v>
@@ -13125,7 +14379,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49">
         <v>6.1466400000000001E-4</v>
@@ -13151,7 +14405,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50">
         <v>6.6162899999999995E-4</v>
@@ -13177,7 +14431,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51">
         <v>7.2370699999999997E-4</v>
@@ -13203,7 +14457,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52">
         <v>8.0128199999999995E-4</v>
@@ -13229,7 +14483,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53">
         <v>6.8117199999999996E-4</v>
@@ -13255,7 +14509,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54">
         <v>6.1575900000000001E-4</v>
@@ -13281,7 +14535,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55">
         <v>5.7284199999999995E-4</v>
@@ -13307,7 +14561,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56">
         <v>7.3430900000000005E-4</v>
@@ -14243,7 +15497,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92">
         <v>6.9999999999999999E-4</v>
@@ -14269,7 +15523,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93">
         <v>9.0499999999999999E-4</v>
@@ -14295,7 +15549,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B94">
         <v>6.3250000000000003E-4</v>
@@ -14321,7 +15575,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B95">
         <v>6.0749999999999997E-4</v>
@@ -14347,7 +15601,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B96">
         <v>7.3800000000000005E-4</v>
@@ -14373,7 +15627,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B97">
         <v>8.6499999999999999E-4</v>
@@ -14399,7 +15653,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B98">
         <v>6.2750000000000002E-4</v>
@@ -14425,7 +15679,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B99">
         <v>5.8500000000000002E-4</v>
@@ -14451,7 +15705,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B100">
         <v>7.0750000000000001E-4</v>
@@ -14477,7 +15731,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101">
         <v>6.3500000000000004E-4</v>
@@ -14503,7 +15757,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B102">
         <v>6.6750000000000002E-4</v>
@@ -14529,7 +15783,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B103">
         <v>6.3029999999999998E-4</v>
@@ -14555,7 +15809,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B104">
         <v>7.2250000000000005E-4</v>
@@ -14581,7 +15835,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B105">
         <v>6.7250000000000003E-4</v>
@@ -14620,16 +15874,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
         <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
